--- a/potpourri/results/results_multiperiod.xlsx
+++ b/potpourri/results/results_multiperiod.xlsx
@@ -14,13 +14,14 @@
     <sheet name="wind" sheetId="5" r:id="rId5"/>
     <sheet name="branch" sheetId="6" r:id="rId6"/>
     <sheet name="transformer" sheetId="7" r:id="rId7"/>
+    <sheet name="battery" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="73">
   <si>
     <t>Time Periods</t>
   </si>
@@ -218,6 +219,27 @@
   </si>
   <si>
     <t>T3-56</t>
+  </si>
+  <si>
+    <t>pChar(MW)</t>
+  </si>
+  <si>
+    <t>pDis(MW)</t>
+  </si>
+  <si>
+    <t>qChar(MW)</t>
+  </si>
+  <si>
+    <t>qDis(MW)</t>
+  </si>
+  <si>
+    <t>e(MW)</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
   </si>
 </sst>
 </file>
@@ -600,16 +622,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>268.2872058944299</v>
+        <v>218.2194169078938</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>259</v>
+        <v>238.3</v>
       </c>
       <c r="E2">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -617,16 +639,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>268.2872058944299</v>
+        <v>219.1833977281824</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>259</v>
+        <v>239.3</v>
       </c>
       <c r="E3">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -634,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>268.2872058944299</v>
+        <v>220.1476855424526</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>259</v>
+        <v>240.3</v>
       </c>
       <c r="E4">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -651,16 +673,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>268.2872058944299</v>
+        <v>217.2557250942395</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>259</v>
+        <v>237.3</v>
       </c>
       <c r="E5">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -668,16 +690,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>268.2872058944299</v>
+        <v>236.5878946153933</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>259</v>
+        <v>257.3000000000001</v>
       </c>
       <c r="E6">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -685,16 +707,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>268.2872058944299</v>
+        <v>246.3003732410136</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>259</v>
+        <v>267.3</v>
       </c>
       <c r="E7">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -702,7 +724,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>268.2872058944299</v>
+        <v>238.2368334166177</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -711,7 +733,7 @@
         <v>259</v>
       </c>
       <c r="E8">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -719,16 +741,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>268.2872058944299</v>
+        <v>217.2557250942396</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>259</v>
+        <v>237.3</v>
       </c>
       <c r="E9">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -736,16 +758,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>268.2872058944299</v>
+        <v>285.2767358093608</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>259</v>
+        <v>307.3000000000001</v>
       </c>
       <c r="E10">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -753,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>268.2872058944299</v>
+        <v>238.2368334166177</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -762,7 +784,7 @@
         <v>259</v>
       </c>
       <c r="E11">
-        <v>80812.65933569762</v>
+        <v>67214.93328970391</v>
       </c>
     </row>
   </sheetData>
@@ -797,10 +819,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>5.819040026691373E-33</v>
+        <v>-2.387227137948061E-32</v>
       </c>
       <c r="D2">
-        <v>1.059999990344401</v>
+        <v>1.059999995443957</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -811,10 +833,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-4.022317672427867</v>
+        <v>-3.783908901298542</v>
       </c>
       <c r="D3">
-        <v>1.040753121199806</v>
+        <v>1.041573584901182</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -825,10 +847,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>-9.92591953981427</v>
+        <v>-11.181336498646</v>
       </c>
       <c r="D4">
-        <v>1.015625301319841</v>
+        <v>1.010376479960198</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -839,10 +861,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>-8.664889229126631</v>
+        <v>-8.426267875735</v>
       </c>
       <c r="D5">
-        <v>1.014460994891626</v>
+        <v>1.015182596562095</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -853,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-7.428440130543171</v>
+        <v>-6.927132597204023</v>
       </c>
       <c r="D6">
-        <v>1.016362731717993</v>
+        <v>1.018368530330984</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -867,10 +889,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-12.68924062914854</v>
+        <v>-12.44719678538263</v>
       </c>
       <c r="D7">
-        <v>1.0600000106</v>
+        <v>1.059999887018856</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -881,10 +903,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>-11.18789414085687</v>
+        <v>-11.51189252823243</v>
       </c>
       <c r="D8">
-        <v>1.046347066273181</v>
+        <v>1.046165976981982</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -895,10 +917,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>-10.41486300573733</v>
+        <v>-11.51189099950474</v>
       </c>
       <c r="D9">
-        <v>1.059999885001289</v>
+        <v>1.059999879952573</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -909,10 +931,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>-12.99716482341075</v>
+        <v>-13.1267751685248</v>
       </c>
       <c r="D10">
-        <v>1.043699293269938</v>
+        <v>1.043018102379776</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -923,10 +945,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-13.2329069530145</v>
+        <v>-13.29727719926571</v>
       </c>
       <c r="D11">
-        <v>1.039136888782085</v>
+        <v>1.038499531445262</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -937,10 +959,10 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>-13.09096569570679</v>
+        <v>-13.00434015446176</v>
       </c>
       <c r="D12">
-        <v>1.046009687050416</v>
+        <v>1.045605534751784</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -951,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-13.53272942450123</v>
+        <v>-13.3168424571909</v>
       </c>
       <c r="D13">
-        <v>1.044820495860475</v>
+        <v>1.044827292873579</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -965,10 +987,10 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>-13.58257940630953</v>
+        <v>-13.39292702067835</v>
       </c>
       <c r="D14">
-        <v>1.039948970373143</v>
+        <v>1.039778034323604</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -979,10 +1001,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>-14.27411074190679</v>
+        <v>-14.2659186697003</v>
       </c>
       <c r="D15">
-        <v>1.023888831641912</v>
+        <v>1.023407199756832</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -993,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>-1.256343062242342E-33</v>
+        <v>-3.858676097619908E-32</v>
       </c>
       <c r="D16">
-        <v>1.059999990344401</v>
+        <v>1.059999995386288</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1007,10 +1029,10 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>-4.022317672427873</v>
+        <v>-3.793066183977427</v>
       </c>
       <c r="D17">
-        <v>1.040753121199806</v>
+        <v>1.041530172295039</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1021,10 +1043,10 @@
         <v>3</v>
       </c>
       <c r="C18">
-        <v>-9.925919539814275</v>
+        <v>-11.14823814925828</v>
       </c>
       <c r="D18">
-        <v>1.015625301319841</v>
+        <v>1.010480266563974</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1035,10 +1057,10 @@
         <v>4</v>
       </c>
       <c r="C19">
-        <v>-8.664889229126647</v>
+        <v>-8.421111858056143</v>
       </c>
       <c r="D19">
-        <v>1.014460994891626</v>
+        <v>1.015198649948613</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1049,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-7.428440130543184</v>
+        <v>-6.92502585448374</v>
       </c>
       <c r="D20">
-        <v>1.016362731717993</v>
+        <v>1.01837592831542</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1063,10 +1085,10 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-12.68924062914857</v>
+        <v>-12.44402107730145</v>
       </c>
       <c r="D21">
-        <v>1.0600000106</v>
+        <v>1.059999886808202</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1077,10 +1099,10 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>-11.18789414085691</v>
+        <v>-11.50722519742484</v>
       </c>
       <c r="D22">
-        <v>1.046347066273181</v>
+        <v>1.046174406869942</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1091,10 +1113,10 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-10.41486300573742</v>
+        <v>-11.50722362945353</v>
       </c>
       <c r="D23">
-        <v>1.059999885001289</v>
+        <v>1.059999879842276</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1105,10 +1127,10 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>-12.9971648234108</v>
+        <v>-13.12237365671097</v>
       </c>
       <c r="D24">
-        <v>1.043699293269936</v>
+        <v>1.043028000167056</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1119,10 +1141,10 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-13.23290695301455</v>
+        <v>-13.29309215408682</v>
       </c>
       <c r="D25">
-        <v>1.039136888782084</v>
+        <v>1.038508008395779</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1133,10 +1155,10 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>-13.09096569570683</v>
+        <v>-13.00065676466187</v>
       </c>
       <c r="D26">
-        <v>1.046009687050415</v>
+        <v>1.045610161964838</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1147,10 +1169,10 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>-13.53272942450127</v>
+        <v>-13.31357467734125</v>
       </c>
       <c r="D27">
-        <v>1.044820495860475</v>
+        <v>1.044827840312055</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1161,10 +1183,10 @@
         <v>13</v>
       </c>
       <c r="C28">
-        <v>-13.58257940630956</v>
+        <v>-13.38957954122696</v>
       </c>
       <c r="D28">
-        <v>1.039948970373143</v>
+        <v>1.039779754153233</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1175,10 +1197,10 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>-14.27411074190683</v>
+        <v>-14.26196364627751</v>
       </c>
       <c r="D29">
-        <v>1.023888831641912</v>
+        <v>1.023413715172892</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1189,10 +1211,10 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>-1.256343062242342E-33</v>
+        <v>4.297598636325232E-33</v>
       </c>
       <c r="D30">
-        <v>1.059999990344401</v>
+        <v>1.059999995328746</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1203,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>-4.022317672427873</v>
+        <v>-3.802225626458966</v>
       </c>
       <c r="D31">
-        <v>1.040753121199806</v>
+        <v>1.041486775274725</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1217,10 +1239,10 @@
         <v>3</v>
       </c>
       <c r="C32">
-        <v>-9.925919539814275</v>
+        <v>-11.1151493146913</v>
       </c>
       <c r="D32">
-        <v>1.015625301319841</v>
+        <v>1.010584523391366</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1231,10 +1253,10 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>-8.664889229126647</v>
+        <v>-8.415957323502321</v>
       </c>
       <c r="D33">
-        <v>1.014460994891626</v>
+        <v>1.015214737486133</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1245,10 +1267,10 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-7.428440130543184</v>
+        <v>-6.922920267572581</v>
       </c>
       <c r="D34">
-        <v>1.016362731717993</v>
+        <v>1.018383341602367</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1259,10 +1281,10 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-12.68924062914857</v>
+        <v>-12.44084638943172</v>
       </c>
       <c r="D35">
-        <v>1.0600000106</v>
+        <v>1.059999886598551</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1273,10 +1295,10 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>-11.18789414085691</v>
+        <v>-11.50255921270363</v>
       </c>
       <c r="D36">
-        <v>1.046347066273181</v>
+        <v>1.046182852030572</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1287,10 +1309,10 @@
         <v>8</v>
       </c>
       <c r="C37">
-        <v>-10.41486300573742</v>
+        <v>-11.50255760341229</v>
       </c>
       <c r="D37">
-        <v>1.059999885001289</v>
+        <v>1.059999879733176</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1301,10 +1323,10 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>-12.9971648234108</v>
+        <v>-13.11797345549278</v>
       </c>
       <c r="D38">
-        <v>1.043699293269936</v>
+        <v>1.043037912445613</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1315,10 +1337,10 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>-13.23290695301455</v>
+        <v>-13.28890836776332</v>
       </c>
       <c r="D39">
-        <v>1.039136888782084</v>
+        <v>1.038516497273268</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1329,10 +1351,10 @@
         <v>11</v>
       </c>
       <c r="C40">
-        <v>-13.09096569570683</v>
+        <v>-12.99697451996802</v>
       </c>
       <c r="D40">
-        <v>1.046009687050415</v>
+        <v>1.045614795178357</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1343,10 +1365,10 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>-13.53272942450127</v>
+        <v>-13.31030792549097</v>
       </c>
       <c r="D41">
-        <v>1.044820495860475</v>
+        <v>1.044828388829565</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1357,10 +1379,10 @@
         <v>13</v>
       </c>
       <c r="C42">
-        <v>-13.58257940630956</v>
+        <v>-13.38623312174222</v>
       </c>
       <c r="D42">
-        <v>1.039948970373143</v>
+        <v>1.039781476043624</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1371,10 +1393,10 @@
         <v>14</v>
       </c>
       <c r="C43">
-        <v>-14.27411074190683</v>
+        <v>-14.2580098048606</v>
       </c>
       <c r="D43">
-        <v>1.023888831641912</v>
+        <v>1.023420239734857</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1385,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="C44">
-        <v>-1.256343062242342E-33</v>
+        <v>-1.778843792206281E-31</v>
       </c>
       <c r="D44">
-        <v>1.059999990344401</v>
+        <v>1.059999995502134</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1399,10 +1421,10 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>-4.022317672427873</v>
+        <v>-3.774750411999213</v>
       </c>
       <c r="D45">
-        <v>1.040753121199806</v>
+        <v>1.041617027303764</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1413,10 +1435,10 @@
         <v>3</v>
       </c>
       <c r="C46">
-        <v>-9.925919539814275</v>
+        <v>-11.21443063013524</v>
       </c>
       <c r="D46">
-        <v>1.015625301319841</v>
+        <v>1.010273211000312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1427,10 +1449,10 @@
         <v>4</v>
       </c>
       <c r="C47">
-        <v>-8.664889229126647</v>
+        <v>-8.431419311053073</v>
       </c>
       <c r="D47">
-        <v>1.014460994891626</v>
+        <v>1.015166596182245</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1441,10 +1463,10 @@
         <v>5</v>
       </c>
       <c r="C48">
-        <v>-7.428440130543184</v>
+        <v>-6.929235636467731</v>
       </c>
       <c r="D48">
-        <v>1.016362731717993</v>
+        <v>1.018361162962408</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1455,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="C49">
-        <v>-12.68924062914857</v>
+        <v>-12.45036811677451</v>
       </c>
       <c r="D49">
-        <v>1.0600000106</v>
+        <v>1.059999887229557</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1469,10 +1491,10 @@
         <v>7</v>
       </c>
       <c r="C50">
-        <v>-11.18789414085691</v>
+        <v>-11.51655529888543</v>
       </c>
       <c r="D50">
-        <v>1.046347066273181</v>
+        <v>1.046157571373927</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1483,10 +1505,10 @@
         <v>8</v>
       </c>
       <c r="C51">
-        <v>-10.41486300573742</v>
+        <v>-11.51655380583533</v>
       </c>
       <c r="D51">
-        <v>1.059999885001289</v>
+        <v>1.059999880064938</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1497,10 +1519,10 @@
         <v>9</v>
       </c>
       <c r="C52">
-        <v>-12.9971648234108</v>
+        <v>-13.13117218438446</v>
       </c>
       <c r="D52">
-        <v>1.043699293269936</v>
+        <v>1.043008228462937</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1511,10 +1533,10 @@
         <v>10</v>
       </c>
       <c r="C53">
-        <v>-13.23290695301455</v>
+        <v>-13.30145777006035</v>
       </c>
       <c r="D53">
-        <v>1.039136888782084</v>
+        <v>1.038491074304852</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1525,10 +1547,10 @@
         <v>11</v>
       </c>
       <c r="C54">
-        <v>-13.09096569570683</v>
+        <v>-13.00801912657428</v>
       </c>
       <c r="D54">
-        <v>1.046009687050415</v>
+        <v>1.045600917685377</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1539,10 +1561,10 @@
         <v>12</v>
       </c>
       <c r="C55">
-        <v>-13.53272942450127</v>
+        <v>-13.32010583276365</v>
       </c>
       <c r="D55">
-        <v>1.044820495860475</v>
+        <v>1.044826747144961</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1553,10 +1575,10 @@
         <v>13</v>
       </c>
       <c r="C56">
-        <v>-13.58257940630956</v>
+        <v>-13.39627010652957</v>
       </c>
       <c r="D56">
-        <v>1.039948970373143</v>
+        <v>1.039776318039358</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1567,10 +1589,10 @@
         <v>14</v>
       </c>
       <c r="C57">
-        <v>-14.27411074190683</v>
+        <v>-14.26986921133752</v>
       </c>
       <c r="D57">
-        <v>1.023888831641912</v>
+        <v>1.02340069955986</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1581,10 +1603,10 @@
         <v>1</v>
       </c>
       <c r="C58">
-        <v>-1.256343062242342E-33</v>
+        <v>-3.449501369962587E-34</v>
       </c>
       <c r="D58">
-        <v>1.059999990344401</v>
+        <v>1.059999994372007</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1595,10 +1617,10 @@
         <v>2</v>
       </c>
       <c r="C59">
-        <v>-4.022317672427873</v>
+        <v>-3.958332596345134</v>
       </c>
       <c r="D59">
-        <v>1.040753121199806</v>
+        <v>1.040751147911323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1609,10 +1631,10 @@
         <v>3</v>
       </c>
       <c r="C60">
-        <v>-9.925919539814275</v>
+        <v>-10.55439483516053</v>
       </c>
       <c r="D60">
-        <v>1.015625301319841</v>
+        <v>1.012427744728729</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1623,10 +1645,10 @@
         <v>4</v>
       </c>
       <c r="C61">
-        <v>-8.664889229126647</v>
+        <v>-8.328676655892407</v>
       </c>
       <c r="D61">
-        <v>1.014460994891626</v>
+        <v>1.015493089037325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1637,10 +1659,10 @@
         <v>5</v>
       </c>
       <c r="C62">
-        <v>-7.428440130543184</v>
+        <v>-6.88739759254467</v>
       </c>
       <c r="D62">
-        <v>1.016362731717993</v>
+        <v>1.018511416425443</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1651,10 +1673,10 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>-12.68924062914857</v>
+        <v>-12.38713872945861</v>
       </c>
       <c r="D63">
-        <v>1.0600000106</v>
+        <v>1.059999883215963</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1665,10 +1687,10 @@
         <v>7</v>
       </c>
       <c r="C64">
-        <v>-11.18789414085691</v>
+        <v>-11.42355946475735</v>
       </c>
       <c r="D64">
-        <v>1.046347066273181</v>
+        <v>1.046328583644161</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1679,10 +1701,10 @@
         <v>8</v>
       </c>
       <c r="C65">
-        <v>-10.41486300573742</v>
+        <v>-11.42355659727832</v>
       </c>
       <c r="D65">
-        <v>1.059999885001289</v>
+        <v>1.059999878057739</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1693,10 +1715,10 @@
         <v>9</v>
       </c>
       <c r="C66">
-        <v>-12.9971648234108</v>
+        <v>-13.04348465294277</v>
       </c>
       <c r="D66">
-        <v>1.043699293269936</v>
+        <v>1.04320845805231</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1707,10 +1729,10 @@
         <v>10</v>
       </c>
       <c r="C67">
-        <v>-13.23290695301455</v>
+        <v>-13.21808923854511</v>
       </c>
       <c r="D67">
-        <v>1.039136888782084</v>
+        <v>1.038662481480907</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1721,10 +1743,10 @@
         <v>11</v>
       </c>
       <c r="C68">
-        <v>-13.09096569570683</v>
+        <v>-12.93466080101286</v>
       </c>
       <c r="D68">
-        <v>1.046009687050415</v>
+        <v>1.045694398191207</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1735,10 +1757,10 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>-13.53272942450127</v>
+        <v>-13.25503706641493</v>
       </c>
       <c r="D69">
-        <v>1.044820495860475</v>
+        <v>1.044837866662879</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1749,10 +1771,10 @@
         <v>13</v>
       </c>
       <c r="C70">
-        <v>-13.58257940630956</v>
+        <v>-13.32961323165201</v>
       </c>
       <c r="D70">
-        <v>1.039948970373143</v>
+        <v>1.039811034942133</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1763,10 +1785,10 @@
         <v>14</v>
       </c>
       <c r="C71">
-        <v>-14.27411074190683</v>
+        <v>-14.19108658825151</v>
       </c>
       <c r="D71">
-        <v>1.023888831641912</v>
+        <v>1.023532439921184</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1777,10 +1799,10 @@
         <v>1</v>
       </c>
       <c r="C72">
-        <v>-1.256343062242342E-33</v>
+        <v>-4.503397709540988E-34</v>
       </c>
       <c r="D72">
-        <v>1.059999990344401</v>
+        <v>1.059999993839107</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1791,10 +1813,10 @@
         <v>2</v>
       </c>
       <c r="C73">
-        <v>-4.022317672427873</v>
+        <v>-4.050514968763829</v>
       </c>
       <c r="D73">
-        <v>1.040753121199806</v>
+        <v>1.040320298495313</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1805,10 +1827,10 @@
         <v>3</v>
       </c>
       <c r="C74">
-        <v>-9.925919539814275</v>
+        <v>-10.22614914933372</v>
       </c>
       <c r="D74">
-        <v>1.015625301319841</v>
+        <v>1.013574224521179</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1819,10 +1841,10 @@
         <v>4</v>
       </c>
       <c r="C75">
-        <v>-8.664889229126647</v>
+        <v>-8.277650300351803</v>
       </c>
       <c r="D75">
-        <v>1.014460994891626</v>
+        <v>1.015661100474678</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1833,10 +1855,10 @@
         <v>5</v>
       </c>
       <c r="C76">
-        <v>-7.428440130543184</v>
+        <v>-6.866749443135885</v>
       </c>
       <c r="D76">
-        <v>1.016362731717993</v>
+        <v>1.018588551298651</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1847,10 +1869,10 @@
         <v>6</v>
       </c>
       <c r="C77">
-        <v>-12.68924062914857</v>
+        <v>-12.35578495856413</v>
       </c>
       <c r="D77">
-        <v>1.0600000106</v>
+        <v>1.059999881407232</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1861,10 +1883,10 @@
         <v>7</v>
       </c>
       <c r="C78">
-        <v>-11.18789414085691</v>
+        <v>-11.37738142542018</v>
       </c>
       <c r="D78">
-        <v>1.046347066273181</v>
+        <v>1.046416210112301</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1875,10 +1897,10 @@
         <v>8</v>
       </c>
       <c r="C79">
-        <v>-10.41486300573742</v>
+        <v>-11.37737625384865</v>
       </c>
       <c r="D79">
-        <v>1.059999885001289</v>
+        <v>1.059999877238472</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1889,10 +1911,10 @@
         <v>9</v>
       </c>
       <c r="C80">
-        <v>-12.9971648234108</v>
+        <v>-12.99995362768115</v>
       </c>
       <c r="D80">
-        <v>1.043699293269936</v>
+        <v>1.043310568423248</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1903,10 +1925,10 @@
         <v>10</v>
       </c>
       <c r="C81">
-        <v>-13.23290695301455</v>
+        <v>-13.17670846396253</v>
       </c>
       <c r="D81">
-        <v>1.039136888782084</v>
+        <v>1.038749824443535</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1917,10 +1939,10 @@
         <v>11</v>
       </c>
       <c r="C82">
-        <v>-13.09096569570683</v>
+        <v>-12.89826462744006</v>
       </c>
       <c r="D82">
-        <v>1.046009687050415</v>
+        <v>1.045741959862155</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1931,10 +1953,10 @@
         <v>12</v>
       </c>
       <c r="C83">
-        <v>-13.53272942450127</v>
+        <v>-13.22276547367493</v>
       </c>
       <c r="D83">
-        <v>1.044820495860475</v>
+        <v>1.044843576439365</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1945,10 +1967,10 @@
         <v>13</v>
       </c>
       <c r="C84">
-        <v>-13.58257940630956</v>
+        <v>-13.29655281469526</v>
       </c>
       <c r="D84">
-        <v>1.039948970373143</v>
+        <v>1.039828674360602</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1959,10 +1981,10 @@
         <v>14</v>
       </c>
       <c r="C85">
-        <v>-14.27411074190683</v>
+        <v>-14.15198582129883</v>
       </c>
       <c r="D85">
-        <v>1.023888831641912</v>
+        <v>1.023599566801229</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1973,10 +1995,10 @@
         <v>1</v>
       </c>
       <c r="C86">
-        <v>-1.256343062242342E-33</v>
+        <v>-9.36461941843164E-34</v>
       </c>
       <c r="D86">
-        <v>1.059999990344401</v>
+        <v>1.059999994279445</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1987,10 +2009,10 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>-4.022317672427873</v>
+        <v>-3.973985037149002</v>
       </c>
       <c r="D87">
-        <v>1.040753121199806</v>
+        <v>1.04067780502623</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2001,10 +2023,10 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>-9.925919539814275</v>
+        <v>-10.49850741603274</v>
       </c>
       <c r="D88">
-        <v>1.015625301319841</v>
+        <v>1.012619402234711</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2015,10 +2037,10 @@
         <v>4</v>
       </c>
       <c r="C89">
-        <v>-8.664889229126647</v>
+        <v>-8.319985642870186</v>
       </c>
       <c r="D89">
-        <v>1.014460994891626</v>
+        <v>1.015521427237869</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2029,10 +2051,10 @@
         <v>5</v>
       </c>
       <c r="C90">
-        <v>-7.428440130543184</v>
+        <v>-6.883874436660885</v>
       </c>
       <c r="D90">
-        <v>1.016362731717993</v>
+        <v>1.018524435130903</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2043,10 +2065,10 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>-12.68924062914857</v>
+        <v>-12.38179608281069</v>
       </c>
       <c r="D91">
-        <v>1.0600000106</v>
+        <v>1.059999882898307</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2057,10 +2079,10 @@
         <v>7</v>
       </c>
       <c r="C92">
-        <v>-11.18789414085691</v>
+        <v>-11.41569392254287</v>
       </c>
       <c r="D92">
-        <v>1.046347066273181</v>
+        <v>1.046343380561039</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2071,10 +2093,10 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>-10.41486300573742</v>
+        <v>-11.41569081761639</v>
       </c>
       <c r="D93">
-        <v>1.059999885001289</v>
+        <v>1.059999877909497</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2085,10 +2107,10 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>-12.9971648234108</v>
+        <v>-13.03606942913749</v>
       </c>
       <c r="D94">
-        <v>1.043699293269936</v>
+        <v>1.043225723102784</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2099,10 +2121,10 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>-13.23290695301455</v>
+        <v>-13.21103999386349</v>
       </c>
       <c r="D95">
-        <v>1.039136888782084</v>
+        <v>1.038677252799072</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2113,10 +2135,10 @@
         <v>11</v>
       </c>
       <c r="C96">
-        <v>-13.09096569570683</v>
+        <v>-12.92845990576852</v>
       </c>
       <c r="D96">
-        <v>1.046009687050415</v>
+        <v>1.045702445100275</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2127,10 +2149,10 @@
         <v>12</v>
       </c>
       <c r="C97">
-        <v>-13.53272942450127</v>
+        <v>-13.24953830176164</v>
       </c>
       <c r="D97">
-        <v>1.044820495860475</v>
+        <v>1.044838830277052</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2141,10 +2163,10 @@
         <v>13</v>
       </c>
       <c r="C98">
-        <v>-13.58257940630956</v>
+        <v>-13.32398012063111</v>
       </c>
       <c r="D98">
-        <v>1.039948970373143</v>
+        <v>1.039814020448284</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2155,10 +2177,10 @@
         <v>14</v>
       </c>
       <c r="C99">
-        <v>-14.27411074190683</v>
+        <v>-14.18442555506916</v>
       </c>
       <c r="D99">
-        <v>1.023888831641912</v>
+        <v>1.023543792473682</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2169,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="C100">
-        <v>-1.256343062242342E-33</v>
+        <v>-2.484975823604729E-31</v>
       </c>
       <c r="D100">
-        <v>1.059999990344401</v>
+        <v>1.059999995502134</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2183,10 +2205,10 @@
         <v>2</v>
       </c>
       <c r="C101">
-        <v>-4.022317672427873</v>
+        <v>-3.77475041199921</v>
       </c>
       <c r="D101">
-        <v>1.040753121199806</v>
+        <v>1.041617027303764</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2197,10 +2219,10 @@
         <v>3</v>
       </c>
       <c r="C102">
-        <v>-9.925919539814275</v>
+        <v>-11.21443063013524</v>
       </c>
       <c r="D102">
-        <v>1.015625301319841</v>
+        <v>1.010273211000312</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2211,10 +2233,10 @@
         <v>4</v>
       </c>
       <c r="C103">
-        <v>-8.664889229126647</v>
+        <v>-8.431419311053071</v>
       </c>
       <c r="D103">
-        <v>1.014460994891626</v>
+        <v>1.015166596182245</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2225,10 +2247,10 @@
         <v>5</v>
       </c>
       <c r="C104">
-        <v>-7.428440130543184</v>
+        <v>-6.929235636467731</v>
       </c>
       <c r="D104">
-        <v>1.016362731717993</v>
+        <v>1.018361162962408</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2239,10 +2261,10 @@
         <v>6</v>
       </c>
       <c r="C105">
-        <v>-12.68924062914857</v>
+        <v>-12.45036811677452</v>
       </c>
       <c r="D105">
-        <v>1.0600000106</v>
+        <v>1.059999887229557</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2253,10 +2275,10 @@
         <v>7</v>
       </c>
       <c r="C106">
-        <v>-11.18789414085691</v>
+        <v>-11.51655529888544</v>
       </c>
       <c r="D106">
-        <v>1.046347066273181</v>
+        <v>1.046157571373926</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2267,10 +2289,10 @@
         <v>8</v>
       </c>
       <c r="C107">
-        <v>-10.41486300573742</v>
+        <v>-11.51655380583533</v>
       </c>
       <c r="D107">
-        <v>1.059999885001289</v>
+        <v>1.059999880064938</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2281,10 +2303,10 @@
         <v>9</v>
       </c>
       <c r="C108">
-        <v>-12.9971648234108</v>
+        <v>-13.13117218438446</v>
       </c>
       <c r="D108">
-        <v>1.043699293269936</v>
+        <v>1.043008228462936</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2295,10 +2317,10 @@
         <v>10</v>
       </c>
       <c r="C109">
-        <v>-13.23290695301455</v>
+        <v>-13.30145777006036</v>
       </c>
       <c r="D109">
-        <v>1.039136888782084</v>
+        <v>1.038491074304852</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2309,10 +2331,10 @@
         <v>11</v>
       </c>
       <c r="C110">
-        <v>-13.09096569570683</v>
+        <v>-13.0080191265743</v>
       </c>
       <c r="D110">
-        <v>1.046009687050415</v>
+        <v>1.045600917685376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2323,10 +2345,10 @@
         <v>12</v>
       </c>
       <c r="C111">
-        <v>-13.53272942450127</v>
+        <v>-13.32010583276366</v>
       </c>
       <c r="D111">
-        <v>1.044820495860475</v>
+        <v>1.044826747144961</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2337,10 +2359,10 @@
         <v>13</v>
       </c>
       <c r="C112">
-        <v>-13.58257940630956</v>
+        <v>-13.39627010652957</v>
       </c>
       <c r="D112">
-        <v>1.039948970373143</v>
+        <v>1.039776318039358</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2351,10 +2373,10 @@
         <v>14</v>
       </c>
       <c r="C113">
-        <v>-14.27411074190683</v>
+        <v>-14.26986921133753</v>
       </c>
       <c r="D113">
-        <v>1.023888831641912</v>
+        <v>1.023400699559859</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2365,10 +2387,10 @@
         <v>1</v>
       </c>
       <c r="C114">
-        <v>-1.332653804044598E-33</v>
+        <v>9.212412565689684E-34</v>
       </c>
       <c r="D114">
-        <v>1.059999990344401</v>
+        <v>1.059999991748663</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2379,10 +2401,10 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>-4.022317672427873</v>
+        <v>-4.383857735005629</v>
       </c>
       <c r="D115">
-        <v>1.040753121199806</v>
+        <v>1.038550655916745</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2393,10 +2415,10 @@
         <v>3</v>
       </c>
       <c r="C116">
-        <v>-9.925919539814275</v>
+        <v>-9.180791387522644</v>
       </c>
       <c r="D116">
-        <v>1.015625301319841</v>
+        <v>1.017187307126318</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2407,10 +2429,10 @@
         <v>4</v>
       </c>
       <c r="C117">
-        <v>-8.664889229126647</v>
+        <v>-7.818293998658159</v>
       </c>
       <c r="D117">
-        <v>1.014460994891626</v>
+        <v>1.018036669776517</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2421,10 +2443,10 @@
         <v>5</v>
       </c>
       <c r="C118">
-        <v>-7.428440130543184</v>
+        <v>-6.565404828444436</v>
       </c>
       <c r="D118">
-        <v>1.016362731717993</v>
+        <v>1.020214073192802</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2435,10 +2457,10 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>-12.68924062914857</v>
+        <v>-11.73782926743685</v>
       </c>
       <c r="D119">
-        <v>1.0600000106</v>
+        <v>1.059999863318234</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2449,10 +2471,10 @@
         <v>7</v>
       </c>
       <c r="C120">
-        <v>-11.18789414085691</v>
+        <v>-10.13251109091819</v>
       </c>
       <c r="D120">
-        <v>1.046347066273181</v>
+        <v>1.04806370169584</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2463,10 +2485,10 @@
         <v>8</v>
       </c>
       <c r="C121">
-        <v>-10.41486300573742</v>
+        <v>-9.107989336353548</v>
       </c>
       <c r="D121">
-        <v>1.059999885001289</v>
+        <v>1.05999986942796</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2477,10 +2499,10 @@
         <v>9</v>
       </c>
       <c r="C122">
-        <v>-12.9971648234108</v>
+        <v>-11.99336228770798</v>
       </c>
       <c r="D122">
-        <v>1.043699293269936</v>
+        <v>1.045461988797212</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2491,10 +2513,10 @@
         <v>10</v>
       </c>
       <c r="C123">
-        <v>-13.23290695301455</v>
+        <v>-12.23846341898787</v>
       </c>
       <c r="D123">
-        <v>1.039136888782084</v>
+        <v>1.040612578306282</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2505,10 +2527,10 @@
         <v>11</v>
       </c>
       <c r="C124">
-        <v>-13.09096569570683</v>
+        <v>-12.11849861692537</v>
       </c>
       <c r="D124">
-        <v>1.046009687050415</v>
+        <v>1.046779605265629</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2519,10 +2541,10 @@
         <v>12</v>
       </c>
       <c r="C125">
-        <v>-13.53272942450127</v>
+        <v>-12.57632077512742</v>
       </c>
       <c r="D125">
-        <v>1.044820495860475</v>
+        <v>1.044942183754085</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2533,10 +2555,10 @@
         <v>13</v>
       </c>
       <c r="C126">
-        <v>-13.58257940630956</v>
+        <v>-12.62389384834846</v>
       </c>
       <c r="D126">
-        <v>1.039948970373143</v>
+        <v>1.040222526647116</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2547,10 +2569,10 @@
         <v>14</v>
       </c>
       <c r="C127">
-        <v>-14.27411074190683</v>
+        <v>-13.28780031466744</v>
       </c>
       <c r="D127">
-        <v>1.023888831641912</v>
+        <v>1.025025337342892</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2561,10 +2583,10 @@
         <v>1</v>
       </c>
       <c r="C128">
-        <v>-1.332653804044598E-33</v>
+        <v>-9.93759412328483E-34</v>
       </c>
       <c r="D128">
-        <v>1.059999990344401</v>
+        <v>1.059999994279445</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2575,10 +2597,10 @@
         <v>2</v>
       </c>
       <c r="C129">
-        <v>-4.022317672427873</v>
+        <v>-3.973985037148997</v>
       </c>
       <c r="D129">
-        <v>1.040753121199806</v>
+        <v>1.04067780502623</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2589,10 +2611,10 @@
         <v>3</v>
       </c>
       <c r="C130">
-        <v>-9.925919539814275</v>
+        <v>-10.49850741603273</v>
       </c>
       <c r="D130">
-        <v>1.015625301319841</v>
+        <v>1.012619402234711</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2603,10 +2625,10 @@
         <v>4</v>
       </c>
       <c r="C131">
-        <v>-8.664889229126647</v>
+        <v>-8.319985642870178</v>
       </c>
       <c r="D131">
-        <v>1.014460994891626</v>
+        <v>1.015521427237869</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2617,10 +2639,10 @@
         <v>5</v>
       </c>
       <c r="C132">
-        <v>-7.428440130543184</v>
+        <v>-6.88387443666088</v>
       </c>
       <c r="D132">
-        <v>1.016362731717993</v>
+        <v>1.018524435130903</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2631,10 +2653,10 @@
         <v>6</v>
       </c>
       <c r="C133">
-        <v>-12.68924062914857</v>
+        <v>-12.38179608281068</v>
       </c>
       <c r="D133">
-        <v>1.0600000106</v>
+        <v>1.059999882898307</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2645,10 +2667,10 @@
         <v>7</v>
       </c>
       <c r="C134">
-        <v>-11.18789414085691</v>
+        <v>-11.41569392254286</v>
       </c>
       <c r="D134">
-        <v>1.046347066273181</v>
+        <v>1.046343380561039</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2659,10 +2681,10 @@
         <v>8</v>
       </c>
       <c r="C135">
-        <v>-10.41486300573742</v>
+        <v>-11.41569081761638</v>
       </c>
       <c r="D135">
-        <v>1.059999885001289</v>
+        <v>1.059999877909497</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2673,10 +2695,10 @@
         <v>9</v>
       </c>
       <c r="C136">
-        <v>-12.9971648234108</v>
+        <v>-13.03606942913748</v>
       </c>
       <c r="D136">
-        <v>1.043699293269936</v>
+        <v>1.043225723102784</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2687,10 +2709,10 @@
         <v>10</v>
       </c>
       <c r="C137">
-        <v>-13.23290695301455</v>
+        <v>-13.21103999386348</v>
       </c>
       <c r="D137">
-        <v>1.039136888782084</v>
+        <v>1.038677252799072</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2701,10 +2723,10 @@
         <v>11</v>
       </c>
       <c r="C138">
-        <v>-13.09096569570683</v>
+        <v>-12.92845990576851</v>
       </c>
       <c r="D138">
-        <v>1.046009687050415</v>
+        <v>1.045702445100275</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2715,10 +2737,10 @@
         <v>12</v>
       </c>
       <c r="C139">
-        <v>-13.53272942450127</v>
+        <v>-13.24953830176164</v>
       </c>
       <c r="D139">
-        <v>1.044820495860475</v>
+        <v>1.044838830277052</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2729,10 +2751,10 @@
         <v>13</v>
       </c>
       <c r="C140">
-        <v>-13.58257940630956</v>
+        <v>-13.32398012063111</v>
       </c>
       <c r="D140">
-        <v>1.039948970373143</v>
+        <v>1.039814020448284</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2743,10 +2765,10 @@
         <v>14</v>
       </c>
       <c r="C141">
-        <v>-14.27411074190683</v>
+        <v>-14.18442555506915</v>
       </c>
       <c r="D141">
-        <v>1.023888831641912</v>
+        <v>1.023543792473682</v>
       </c>
     </row>
   </sheetData>
@@ -2910,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>21.7</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>12.7</v>
@@ -3190,7 +3212,7 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>21.7</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>12.7</v>
@@ -3470,7 +3492,7 @@
         <v>2</v>
       </c>
       <c r="D36">
-        <v>21.7</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>12.7</v>
@@ -3750,7 +3772,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>12.7</v>
@@ -4030,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="D64">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="E64">
         <v>12.7</v>
@@ -4310,7 +4332,7 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>21.7</v>
+        <v>30</v>
       </c>
       <c r="E78">
         <v>12.7</v>
@@ -4870,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>12.7</v>
@@ -5150,7 +5172,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>21.7</v>
+        <v>70</v>
       </c>
       <c r="E120">
         <v>12.7</v>
@@ -5635,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>194.33</v>
+        <v>182.648</v>
       </c>
       <c r="G2">
         <v>332.4</v>
@@ -5664,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>36.719</v>
+        <v>34.466</v>
       </c>
       <c r="G3">
         <v>140</v>
@@ -5673,7 +5695,7 @@
         <v>-40</v>
       </c>
       <c r="I3">
-        <v>23.685</v>
+        <v>23.787</v>
       </c>
       <c r="J3">
         <v>50</v>
@@ -5693,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>28.743</v>
+        <v>1.105</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -5702,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>24.127</v>
+        <v>28.536</v>
       </c>
       <c r="J4">
         <v>40</v>
@@ -5731,7 +5753,7 @@
         <v>-6</v>
       </c>
       <c r="I5">
-        <v>11.546</v>
+        <v>10.17</v>
       </c>
       <c r="J5">
         <v>24</v>
@@ -5751,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -5760,7 +5782,7 @@
         <v>-6</v>
       </c>
       <c r="I6">
-        <v>8.273</v>
+        <v>8.324999999999999</v>
       </c>
       <c r="J6">
         <v>24</v>
@@ -5780,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>194.33</v>
+        <v>182.924</v>
       </c>
       <c r="G7">
         <v>332.4</v>
@@ -5809,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>36.719</v>
+        <v>34.522</v>
       </c>
       <c r="G8">
         <v>140</v>
@@ -5818,7 +5840,7 @@
         <v>-40</v>
       </c>
       <c r="I8">
-        <v>23.685</v>
+        <v>23.793</v>
       </c>
       <c r="J8">
         <v>50</v>
@@ -5838,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>28.743</v>
+        <v>1.738</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -5847,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>24.127</v>
+        <v>28.406</v>
       </c>
       <c r="J9">
         <v>40</v>
@@ -5876,7 +5898,7 @@
         <v>-6</v>
       </c>
       <c r="I10">
-        <v>11.546</v>
+        <v>10.166</v>
       </c>
       <c r="J10">
         <v>24</v>
@@ -5896,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -5905,7 +5927,7 @@
         <v>-6</v>
       </c>
       <c r="I11">
-        <v>8.273</v>
+        <v>8.32</v>
       </c>
       <c r="J11">
         <v>24</v>
@@ -5925,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>194.33</v>
+        <v>183.199</v>
       </c>
       <c r="G12">
         <v>332.4</v>
@@ -5954,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>36.719</v>
+        <v>34.579</v>
       </c>
       <c r="G13">
         <v>140</v>
@@ -5963,7 +5985,7 @@
         <v>-40</v>
       </c>
       <c r="I13">
-        <v>23.685</v>
+        <v>23.799</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -5983,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>28.743</v>
+        <v>2.37</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -5992,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>24.127</v>
+        <v>28.277</v>
       </c>
       <c r="J14">
         <v>40</v>
@@ -6021,7 +6043,7 @@
         <v>-6</v>
       </c>
       <c r="I15">
-        <v>11.546</v>
+        <v>10.161</v>
       </c>
       <c r="J15">
         <v>24</v>
@@ -6041,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -6050,7 +6072,7 @@
         <v>-6</v>
       </c>
       <c r="I16">
-        <v>8.273</v>
+        <v>8.315</v>
       </c>
       <c r="J16">
         <v>24</v>
@@ -6070,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>194.33</v>
+        <v>182.373</v>
       </c>
       <c r="G17">
         <v>332.4</v>
@@ -6099,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>36.719</v>
+        <v>34.41</v>
       </c>
       <c r="G18">
         <v>140</v>
@@ -6108,7 +6130,7 @@
         <v>-40</v>
       </c>
       <c r="I18">
-        <v>23.685</v>
+        <v>23.782</v>
       </c>
       <c r="J18">
         <v>50</v>
@@ -6128,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>28.743</v>
+        <v>0.473</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -6137,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>24.127</v>
+        <v>28.668</v>
       </c>
       <c r="J19">
         <v>40</v>
@@ -6166,7 +6188,7 @@
         <v>-6</v>
       </c>
       <c r="I20">
-        <v>11.546</v>
+        <v>10.175</v>
       </c>
       <c r="J20">
         <v>24</v>
@@ -6186,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -6195,7 +6217,7 @@
         <v>-6</v>
       </c>
       <c r="I21">
-        <v>8.273</v>
+        <v>8.33</v>
       </c>
       <c r="J21">
         <v>24</v>
@@ -6215,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>194.33</v>
+        <v>187.891</v>
       </c>
       <c r="G22">
         <v>332.4</v>
@@ -6244,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>36.719</v>
+        <v>35.538</v>
       </c>
       <c r="G23">
         <v>140</v>
@@ -6253,7 +6275,7 @@
         <v>-40</v>
       </c>
       <c r="I23">
-        <v>23.685</v>
+        <v>23.925</v>
       </c>
       <c r="J23">
         <v>50</v>
@@ -6273,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>28.743</v>
+        <v>13.158</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -6282,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>24.127</v>
+        <v>26.21</v>
       </c>
       <c r="J24">
         <v>40</v>
@@ -6311,7 +6333,7 @@
         <v>-6</v>
       </c>
       <c r="I25">
-        <v>11.546</v>
+        <v>10.086</v>
       </c>
       <c r="J25">
         <v>24</v>
@@ -6331,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -6340,7 +6362,7 @@
         <v>-6</v>
       </c>
       <c r="I26">
-        <v>8.273</v>
+        <v>8.227</v>
       </c>
       <c r="J26">
         <v>24</v>
@@ -6360,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>194.33</v>
+        <v>190.662</v>
       </c>
       <c r="G27">
         <v>332.4</v>
@@ -6389,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>36.719</v>
+        <v>36.107</v>
       </c>
       <c r="G28">
         <v>140</v>
@@ -6398,7 +6420,7 @@
         <v>-40</v>
       </c>
       <c r="I28">
-        <v>23.685</v>
+        <v>24.026</v>
       </c>
       <c r="J28">
         <v>50</v>
@@ -6418,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>28.743</v>
+        <v>19.531</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -6427,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>24.127</v>
+        <v>25.111</v>
       </c>
       <c r="J29">
         <v>40</v>
@@ -6456,7 +6478,7 @@
         <v>-6</v>
       </c>
       <c r="I30">
-        <v>11.546</v>
+        <v>10.04</v>
       </c>
       <c r="J30">
         <v>24</v>
@@ -6476,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -6485,7 +6507,7 @@
         <v>-6</v>
       </c>
       <c r="I31">
-        <v>8.273</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="J31">
         <v>24</v>
@@ -6505,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>194.33</v>
+        <v>188.362</v>
       </c>
       <c r="G32">
         <v>332.4</v>
@@ -6534,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>36.719</v>
+        <v>35.635</v>
       </c>
       <c r="G33">
         <v>140</v>
@@ -6543,7 +6565,7 @@
         <v>-40</v>
       </c>
       <c r="I33">
-        <v>23.685</v>
+        <v>23.941</v>
       </c>
       <c r="J33">
         <v>50</v>
@@ -6563,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>28.743</v>
+        <v>14.24</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -6572,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>24.127</v>
+        <v>26.017</v>
       </c>
       <c r="J34">
         <v>40</v>
@@ -6601,7 +6623,7 @@
         <v>-6</v>
       </c>
       <c r="I35">
-        <v>11.546</v>
+        <v>10.078</v>
       </c>
       <c r="J35">
         <v>24</v>
@@ -6621,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -6630,7 +6652,7 @@
         <v>-6</v>
       </c>
       <c r="I36">
-        <v>8.273</v>
+        <v>8.218</v>
       </c>
       <c r="J36">
         <v>24</v>
@@ -6650,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>194.33</v>
+        <v>182.373</v>
       </c>
       <c r="G37">
         <v>332.4</v>
@@ -6679,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>36.719</v>
+        <v>34.41</v>
       </c>
       <c r="G38">
         <v>140</v>
@@ -6688,7 +6710,7 @@
         <v>-40</v>
       </c>
       <c r="I38">
-        <v>23.685</v>
+        <v>23.782</v>
       </c>
       <c r="J38">
         <v>50</v>
@@ -6708,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>28.743</v>
+        <v>0.473</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6717,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>24.127</v>
+        <v>28.668</v>
       </c>
       <c r="J39">
         <v>40</v>
@@ -6746,7 +6768,7 @@
         <v>-6</v>
       </c>
       <c r="I40">
-        <v>11.546</v>
+        <v>10.175</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -6766,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -6775,7 +6797,7 @@
         <v>-6</v>
       </c>
       <c r="I41">
-        <v>8.273</v>
+        <v>8.33</v>
       </c>
       <c r="J41">
         <v>24</v>
@@ -6795,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>194.33</v>
+        <v>198.831</v>
       </c>
       <c r="G42">
         <v>332.4</v>
@@ -6824,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>36.719</v>
+        <v>37.853</v>
       </c>
       <c r="G43">
         <v>140</v>
@@ -6833,7 +6855,7 @@
         <v>-40</v>
       </c>
       <c r="I43">
-        <v>23.685</v>
+        <v>23.745</v>
       </c>
       <c r="J43">
         <v>50</v>
@@ -6853,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>28.743</v>
+        <v>37.316</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -6862,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>24.127</v>
+        <v>22.077</v>
       </c>
       <c r="J44">
         <v>40</v>
@@ -6891,7 +6913,7 @@
         <v>-6</v>
       </c>
       <c r="I45">
-        <v>11.546</v>
+        <v>9.33</v>
       </c>
       <c r="J45">
         <v>24</v>
@@ -6911,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>8.494999999999999</v>
+        <v>11.277</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -6920,7 +6942,7 @@
         <v>-6</v>
       </c>
       <c r="I46">
-        <v>8.273</v>
+        <v>7.284</v>
       </c>
       <c r="J46">
         <v>24</v>
@@ -6940,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>194.33</v>
+        <v>188.362</v>
       </c>
       <c r="G47">
         <v>332.4</v>
@@ -6969,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>36.719</v>
+        <v>35.635</v>
       </c>
       <c r="G48">
         <v>140</v>
@@ -6978,7 +7000,7 @@
         <v>-40</v>
       </c>
       <c r="I48">
-        <v>23.685</v>
+        <v>23.941</v>
       </c>
       <c r="J48">
         <v>50</v>
@@ -6998,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>28.743</v>
+        <v>14.24</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -7007,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>24.127</v>
+        <v>26.017</v>
       </c>
       <c r="J49">
         <v>40</v>
@@ -7036,7 +7058,7 @@
         <v>-6</v>
       </c>
       <c r="I50">
-        <v>11.546</v>
+        <v>10.078</v>
       </c>
       <c r="J50">
         <v>24</v>
@@ -7056,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>8.494999999999999</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -7065,7 +7087,7 @@
         <v>-6</v>
       </c>
       <c r="I51">
-        <v>8.273</v>
+        <v>8.218</v>
       </c>
       <c r="J51">
         <v>24</v>
@@ -7160,13 +7182,13 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>-126.7671118236151</v>
+        <v>-119.6005029559071</v>
       </c>
       <c r="F2">
-        <v>129.6692230777651</v>
+        <v>122.1766441897816</v>
       </c>
       <c r="G2">
-        <v>2.902111254149964</v>
+        <v>2.576141233874507</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -7183,13 +7205,13 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>-62.61040441253709</v>
+        <v>-58.67698466603682</v>
       </c>
       <c r="F3">
-        <v>64.66099683920643</v>
+        <v>60.47155808885147</v>
       </c>
       <c r="G3">
-        <v>2.05059242666934</v>
+        <v>1.794573422814649</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7206,13 +7228,13 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>-54.24843958851137</v>
+        <v>-67.37547734508183</v>
       </c>
       <c r="F4">
-        <v>55.59269706495207</v>
+        <v>69.47427754931374</v>
       </c>
       <c r="G4">
-        <v>1.344257476440702</v>
+        <v>2.09880020423191</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7229,13 +7251,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>-47.63101375117414</v>
+        <v>-47.71389736342753</v>
       </c>
       <c r="F5">
-        <v>48.91567450887781</v>
+        <v>49.00108161793185</v>
       </c>
       <c r="G5">
-        <v>1.284660757703665</v>
+        <v>1.287184254504314</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7252,13 +7274,13 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>-36.54096555700751</v>
+        <v>-33.95680870067802</v>
       </c>
       <c r="F6">
-        <v>37.27791102353811</v>
+        <v>34.59132505647051</v>
       </c>
       <c r="G6">
-        <v>0.736945466530603</v>
+        <v>0.6345163557924804</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7275,13 +7297,13 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>11.30824654176329</v>
+        <v>26.19501392498996</v>
       </c>
       <c r="F7">
-        <v>-11.20886424883511</v>
+        <v>-25.71951732048063</v>
       </c>
       <c r="G7">
-        <v>0.09938229292818235</v>
+        <v>0.475496604509329</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -7298,13 +7320,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>49.49590120942007</v>
+        <v>60.82493608104718</v>
       </c>
       <c r="F8">
-        <v>-49.16495929329883</v>
+        <v>-60.33384329410252</v>
       </c>
       <c r="G8">
-        <v>0.3309419161212412</v>
+        <v>0.491092786944658</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7321,13 +7343,13 @@
         <v>11</v>
       </c>
       <c r="E9">
-        <v>-6.038395488324693</v>
+        <v>-7.344551943980407</v>
       </c>
       <c r="F9">
-        <v>6.087317356238095</v>
+        <v>7.405548211754631</v>
       </c>
       <c r="G9">
-        <v>0.04892186791340195</v>
+        <v>0.06099626777422429</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -7344,13 +7366,13 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>-7.579875620281057</v>
+        <v>-7.738228661934075</v>
       </c>
       <c r="F10">
-        <v>7.651663352956437</v>
+        <v>7.812291383248354</v>
       </c>
       <c r="G10">
-        <v>0.07178773267537963</v>
+        <v>0.07406272131427888</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7367,13 +7389,13 @@
         <v>13</v>
       </c>
       <c r="E11">
-        <v>-16.90903540980751</v>
+        <v>-17.57125222028311</v>
       </c>
       <c r="F11">
-        <v>17.11666986637343</v>
+        <v>17.79102906962576</v>
       </c>
       <c r="G11">
-        <v>0.2076344565659166</v>
+        <v>0.2197768493426483</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7390,13 +7412,13 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>8.494935878662762</v>
+        <v>1.679698296951188E-05</v>
       </c>
       <c r="F12">
-        <v>-8.494935878662762</v>
+        <v>-1.67969829695119E-05</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-1.588186776101813E-20</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7413,10 +7435,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-31.34207305001579</v>
+        <v>-27.9525288943663</v>
       </c>
       <c r="F13">
-        <v>31.34207305001579</v>
+        <v>27.9525288943663</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -7436,13 +7458,13 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>-6.471743754349888</v>
+        <v>-5.170284501481671</v>
       </c>
       <c r="F14">
-        <v>6.48703030168723</v>
+        <v>5.181994372175615</v>
       </c>
       <c r="G14">
-        <v>0.01528654733734119</v>
+        <v>0.01170987069394475</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7459,13 +7481,13 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>-10.06416303194612</v>
+        <v>-9.25590153558929</v>
       </c>
       <c r="F15">
-        <v>10.1956313067123</v>
+        <v>9.370749684559206</v>
       </c>
       <c r="G15">
-        <v>0.1314682747661763</v>
+        <v>0.1148481489699163</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7482,13 +7504,13 @@
         <v>11</v>
       </c>
       <c r="E16">
-        <v>2.538395453338237</v>
+        <v>3.844551908989501</v>
       </c>
       <c r="F16">
-        <v>-2.528256335636567</v>
+        <v>-3.829715588509234</v>
       </c>
       <c r="G16">
-        <v>0.01013911770167027</v>
+        <v>0.01483632048026734</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -7505,13 +7527,13 @@
         <v>13</v>
       </c>
       <c r="E17">
-        <v>-1.473763942971532</v>
+        <v>-1.631406001398522</v>
       </c>
       <c r="F17">
-        <v>1.479875559294601</v>
+        <v>1.63822860094317</v>
       </c>
       <c r="G17">
-        <v>0.006111616323069453</v>
+        <v>0.006822599544648381</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7528,13 +7550,13 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>-4.835837117040334</v>
+        <v>-5.644098613401615</v>
       </c>
       <c r="F18">
-        <v>4.882799217792589</v>
+        <v>5.702658086690731</v>
       </c>
       <c r="G18">
-        <v>0.04696210075225485</v>
+        <v>0.05855947328911593</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7551,13 +7573,13 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>-126.7671118236153</v>
+        <v>-119.8810221875865</v>
       </c>
       <c r="F19">
-        <v>129.6692230777652</v>
+        <v>122.4695204931146</v>
       </c>
       <c r="G19">
-        <v>2.902111254149964</v>
+        <v>2.58849830552812</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7574,13 +7596,13 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-62.61040441253722</v>
+        <v>-58.66044222477751</v>
       </c>
       <c r="F20">
-        <v>64.66099683920655</v>
+        <v>60.45398213251639</v>
       </c>
       <c r="G20">
-        <v>2.050592426669329</v>
+        <v>1.793539907738884</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7597,13 +7619,13 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>-54.24843958851137</v>
+        <v>-67.006080420061</v>
       </c>
       <c r="F21">
-        <v>55.59269706495206</v>
+        <v>69.08134107119467</v>
       </c>
       <c r="G21">
-        <v>1.344257476440691</v>
+        <v>2.07526065113367</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7620,13 +7642,13 @@
         <v>4</v>
       </c>
       <c r="E22">
-        <v>-47.63101375117429</v>
+        <v>-47.57158222114393</v>
       </c>
       <c r="F22">
-        <v>48.91567450887793</v>
+        <v>48.85100967027088</v>
       </c>
       <c r="G22">
-        <v>1.284660757703648</v>
+        <v>1.279427449126952</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7643,13 +7665,13 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>-36.54096555700757</v>
+        <v>-33.84080449882066</v>
       </c>
       <c r="F23">
-        <v>37.27791102353818</v>
+        <v>34.47101836738081</v>
       </c>
       <c r="G23">
-        <v>0.7369454665306086</v>
+        <v>0.6302138685601477</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7666,13 +7688,13 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>11.30824654176312</v>
+        <v>25.92228355456552</v>
       </c>
       <c r="F24">
-        <v>-11.20886424883492</v>
+        <v>-25.45640004304418</v>
       </c>
       <c r="G24">
-        <v>0.09938229292820178</v>
+        <v>0.4658835115213367</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7689,13 +7711,13 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>49.49590120942013</v>
+        <v>60.70060294006001</v>
       </c>
       <c r="F25">
-        <v>-49.16495929329889</v>
+        <v>-60.21150412825818</v>
       </c>
       <c r="G25">
-        <v>0.3309419161212523</v>
+        <v>0.4890988118018358</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7712,13 +7734,13 @@
         <v>11</v>
       </c>
       <c r="E26">
-        <v>-6.038395488324845</v>
+        <v>-7.339636673041267</v>
       </c>
       <c r="F26">
-        <v>6.087317356238203</v>
+        <v>7.400569669063184</v>
       </c>
       <c r="G26">
-        <v>0.04892186791335823</v>
+        <v>0.06093299602191737</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7735,13 +7757,13 @@
         <v>12</v>
       </c>
       <c r="E27">
-        <v>-7.579875620281064</v>
+        <v>-7.737584350242408</v>
       </c>
       <c r="F27">
-        <v>7.651663352956444</v>
+        <v>7.811636312599285</v>
       </c>
       <c r="G27">
-        <v>0.07178773267537963</v>
+        <v>0.07405196235687611</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -7758,13 +7780,13 @@
         <v>13</v>
       </c>
       <c r="E28">
-        <v>-16.90903540980757</v>
+        <v>-17.56872770969234</v>
       </c>
       <c r="F28">
-        <v>17.11666986637344</v>
+        <v>17.7884493573497</v>
       </c>
       <c r="G28">
-        <v>0.2076344565658722</v>
+        <v>0.2197216476573671</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7781,13 +7803,13 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>8.49493587866235</v>
+        <v>1.722831396518244E-05</v>
       </c>
       <c r="F29">
-        <v>-8.49493587866235</v>
+        <v>-1.722831396518244E-05</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>-5.293955920339377E-21</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7804,10 +7826,10 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-31.34207305001566</v>
+        <v>-27.95761940156307</v>
       </c>
       <c r="F30">
-        <v>31.34207305001566</v>
+        <v>27.95761940156307</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7827,13 +7849,13 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>-6.471743754349784</v>
+        <v>-5.175171281881261</v>
       </c>
       <c r="F31">
-        <v>6.487030301687302</v>
+        <v>5.186895739745792</v>
       </c>
       <c r="G31">
-        <v>0.01528654733751883</v>
+        <v>0.01172445786453147</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -7850,13 +7872,13 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>-10.06416303194601</v>
+        <v>-9.259009709186895</v>
       </c>
       <c r="F32">
-        <v>10.19563130671219</v>
+        <v>9.373924811050893</v>
       </c>
       <c r="G32">
-        <v>0.1314682747661763</v>
+        <v>0.1149151018639979</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7873,13 +7895,13 @@
         <v>11</v>
       </c>
       <c r="E33">
-        <v>2.538395453338389</v>
+        <v>3.83963663805036</v>
       </c>
       <c r="F33">
-        <v>-2.528256335636673</v>
+        <v>-3.824828808109642</v>
       </c>
       <c r="G33">
-        <v>0.01013911770171641</v>
+        <v>0.01480782994071755</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7896,13 +7918,13 @@
         <v>13</v>
       </c>
       <c r="E34">
-        <v>-1.473763942971583</v>
+        <v>-1.630765633632137</v>
       </c>
       <c r="F34">
-        <v>1.479875559294608</v>
+        <v>1.637584289251504</v>
       </c>
       <c r="G34">
-        <v>0.006111616323024871</v>
+        <v>0.006818655619367231</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7919,13 +7941,13 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>-4.835837117040442</v>
+        <v>-5.64099043980401</v>
       </c>
       <c r="F35">
-        <v>4.8827992177927</v>
+        <v>5.699493208333567</v>
       </c>
       <c r="G35">
-        <v>0.04696210075225762</v>
+        <v>0.05850276852955721</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7942,13 +7964,13 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>-126.7671118236153</v>
+        <v>-120.161556386395</v>
       </c>
       <c r="F36">
-        <v>129.6692230777652</v>
+        <v>122.7624433163723</v>
       </c>
       <c r="G36">
-        <v>2.902111254149964</v>
+        <v>2.600886929977242</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7965,13 +7987,13 @@
         <v>5</v>
       </c>
       <c r="E37">
-        <v>-62.61040441253722</v>
+        <v>-58.64390748196452</v>
       </c>
       <c r="F37">
-        <v>64.66099683920655</v>
+        <v>60.43641460099221</v>
       </c>
       <c r="G37">
-        <v>2.050592426669329</v>
+        <v>1.792507119027686</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7988,13 +8010,13 @@
         <v>3</v>
       </c>
       <c r="E38">
-        <v>-54.24843958851137</v>
+        <v>-66.63657838243772</v>
       </c>
       <c r="F38">
-        <v>55.59269706495206</v>
+        <v>68.68843215207129</v>
       </c>
       <c r="G38">
-        <v>1.344257476440691</v>
+        <v>2.051853769633571</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -8011,13 +8033,13 @@
         <v>4</v>
       </c>
       <c r="E39">
-        <v>-47.63101375117429</v>
+        <v>-47.42925253157308</v>
       </c>
       <c r="F39">
-        <v>48.91567450887793</v>
+        <v>48.70094646965836</v>
       </c>
       <c r="G39">
-        <v>1.284660757703648</v>
+        <v>1.271693938085289</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -8034,13 +8056,13 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>-36.54096555700757</v>
+        <v>-33.72479086887031</v>
       </c>
       <c r="F40">
-        <v>37.27791102353818</v>
+        <v>34.350716995616</v>
       </c>
       <c r="G40">
-        <v>0.7369454665306086</v>
+        <v>0.6259261267456906</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8057,13 +8079,13 @@
         <v>4</v>
       </c>
       <c r="E41">
-        <v>11.30824654176312</v>
+        <v>25.64953266271714</v>
       </c>
       <c r="F41">
-        <v>-11.20886424883492</v>
+        <v>-25.1931625140314</v>
       </c>
       <c r="G41">
-        <v>0.09938229292820178</v>
+        <v>0.4563701486857308</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -8080,13 +8102,13 @@
         <v>5</v>
       </c>
       <c r="E42">
-        <v>49.49590120942013</v>
+        <v>60.57626862734343</v>
       </c>
       <c r="F42">
-        <v>-49.16495929329889</v>
+        <v>-60.08915962154008</v>
       </c>
       <c r="G42">
-        <v>0.3309419161212523</v>
+        <v>0.4871090058033545</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -8103,13 +8125,13 @@
         <v>11</v>
       </c>
       <c r="E43">
-        <v>-6.038395488324845</v>
+        <v>-7.334721141137216</v>
       </c>
       <c r="F43">
-        <v>6.087317356238203</v>
+        <v>7.39559088301402</v>
       </c>
       <c r="G43">
-        <v>0.04892186791335823</v>
+        <v>0.06086974187680533</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -8126,13 +8148,13 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>-7.579875620281064</v>
+        <v>-7.736939920994811</v>
       </c>
       <c r="F44">
-        <v>7.651663352956444</v>
+        <v>7.810981121095778</v>
       </c>
       <c r="G44">
-        <v>0.07178773267537963</v>
+        <v>0.07404120010096743</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8149,13 +8171,13 @@
         <v>13</v>
       </c>
       <c r="E45">
-        <v>-16.90903540980757</v>
+        <v>-17.56620302134807</v>
       </c>
       <c r="F45">
-        <v>17.11666986637344</v>
+        <v>17.78586945737455</v>
       </c>
       <c r="G45">
-        <v>0.2076344565658722</v>
+        <v>0.2196664360264805</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -8172,13 +8194,13 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>8.49493587866235</v>
+        <v>1.768246649083972E-05</v>
       </c>
       <c r="F46">
-        <v>-8.49493587866235</v>
+        <v>-1.768246649083971E-05</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1.058791184067875E-20</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -8195,10 +8217,10 @@
         <v>9</v>
       </c>
       <c r="E47">
-        <v>-31.34207305001566</v>
+        <v>-27.96271025639713</v>
       </c>
       <c r="F47">
-        <v>31.34207305001566</v>
+        <v>27.96271025639713</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -8218,13 +8240,13 @@
         <v>10</v>
       </c>
       <c r="E48">
-        <v>-6.471743754349784</v>
+        <v>-5.180058348073397</v>
       </c>
       <c r="F48">
-        <v>6.487030301687302</v>
+        <v>5.191797413953079</v>
       </c>
       <c r="G48">
-        <v>0.01528654733751883</v>
+        <v>0.01173906587968246</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -8241,13 +8263,13 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>-10.06416303194601</v>
+        <v>-9.262118191350449</v>
       </c>
       <c r="F49">
-        <v>10.19563130671219</v>
+        <v>9.377100286990036</v>
       </c>
       <c r="G49">
-        <v>0.1314682747661763</v>
+        <v>0.1149820956395875</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -8264,13 +8286,13 @@
         <v>11</v>
       </c>
       <c r="E50">
-        <v>2.538395453338389</v>
+        <v>3.83472110614631</v>
       </c>
       <c r="F50">
-        <v>-2.528256335636673</v>
+        <v>-3.819941741917507</v>
       </c>
       <c r="G50">
-        <v>0.01013911770171641</v>
+        <v>0.01477936422880285</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8287,13 +8309,13 @@
         <v>13</v>
       </c>
       <c r="E51">
-        <v>-1.473763942971583</v>
+        <v>-1.630125148648656</v>
       </c>
       <c r="F51">
-        <v>1.479875559294608</v>
+        <v>1.636939860003906</v>
       </c>
       <c r="G51">
-        <v>0.006111616323024871</v>
+        <v>0.006814711355249484</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8310,13 +8332,13 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>-4.835837117040442</v>
+        <v>-5.637881957640457</v>
       </c>
       <c r="F52">
-        <v>4.8827992177927</v>
+        <v>5.696328035005822</v>
       </c>
       <c r="G52">
-        <v>0.04696210075225762</v>
+        <v>0.058446077365365</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8333,13 +8355,13 @@
         <v>2</v>
       </c>
       <c r="E53">
-        <v>-126.7671118236153</v>
+        <v>-119.3198962680993</v>
       </c>
       <c r="F53">
-        <v>129.6692230777652</v>
+        <v>121.8837074676544</v>
       </c>
       <c r="G53">
-        <v>2.902111254149964</v>
+        <v>2.563811199555133</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -8356,13 +8378,13 @@
         <v>5</v>
       </c>
       <c r="E54">
-        <v>-62.61040441253722</v>
+        <v>-58.69349673559316</v>
       </c>
       <c r="F54">
-        <v>64.66099683920655</v>
+        <v>60.48910202655906</v>
       </c>
       <c r="G54">
-        <v>2.050592426669329</v>
+        <v>1.795605290965896</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8379,13 +8401,13 @@
         <v>3</v>
       </c>
       <c r="E55">
-        <v>-54.24843958851137</v>
+        <v>-67.74468224602683</v>
       </c>
       <c r="F55">
-        <v>55.59269706495206</v>
+        <v>69.86714897664947</v>
       </c>
       <c r="G55">
-        <v>1.344257476440691</v>
+        <v>2.122466730622652</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -8402,13 +8424,13 @@
         <v>4</v>
       </c>
       <c r="E56">
-        <v>-47.63101375117429</v>
+        <v>-47.85617393974655</v>
       </c>
       <c r="F56">
-        <v>48.91567450887793</v>
+        <v>49.15113692431601</v>
       </c>
       <c r="G56">
-        <v>1.284660757703648</v>
+        <v>1.294962984569453</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8425,13 +8447,13 @@
         <v>5</v>
       </c>
       <c r="E57">
-        <v>-36.54096555700757</v>
+        <v>-34.072790138003</v>
       </c>
       <c r="F57">
-        <v>37.27791102353818</v>
+        <v>34.71162321370447</v>
       </c>
       <c r="G57">
-        <v>0.7369454665306086</v>
+        <v>0.6388330757014726</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8448,13 +8470,13 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>11.30824654176312</v>
+        <v>26.46764922682701</v>
       </c>
       <c r="F58">
-        <v>-11.20886424883492</v>
+        <v>-25.98244246024623</v>
       </c>
       <c r="G58">
-        <v>0.09938229292820178</v>
+        <v>0.4852067665807758</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -8471,13 +8493,13 @@
         <v>5</v>
       </c>
       <c r="E59">
-        <v>49.49590120942013</v>
+        <v>60.94922027076425</v>
       </c>
       <c r="F59">
-        <v>-49.16495929329889</v>
+        <v>-60.45613011909007</v>
       </c>
       <c r="G59">
-        <v>0.3309419161212523</v>
+        <v>0.4930901516741804</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -8494,13 +8516,13 @@
         <v>11</v>
       </c>
       <c r="E60">
-        <v>-6.038395488324845</v>
+        <v>-7.349464827797641</v>
       </c>
       <c r="F60">
-        <v>6.087317356238203</v>
+        <v>7.410524349438121</v>
       </c>
       <c r="G60">
-        <v>0.04892186791335823</v>
+        <v>0.06105952164047884</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8517,13 +8539,13 @@
         <v>12</v>
       </c>
       <c r="E61">
-        <v>-7.579875620281064</v>
+        <v>-7.738872544447431</v>
       </c>
       <c r="F61">
-        <v>7.651663352956444</v>
+        <v>7.812946015350235</v>
       </c>
       <c r="G61">
-        <v>0.07178773267537963</v>
+        <v>0.07407347090280375</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8540,13 +8562,13 @@
         <v>13</v>
       </c>
       <c r="E62">
-        <v>-16.90903540980757</v>
+        <v>-17.57377543997768</v>
       </c>
       <c r="F62">
-        <v>17.11666986637344</v>
+        <v>17.79360745141587</v>
       </c>
       <c r="G62">
-        <v>0.2076344565658722</v>
+        <v>0.2198320114381924</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8563,13 +8585,13 @@
         <v>8</v>
       </c>
       <c r="E63">
-        <v>8.49493587866235</v>
+        <v>1.640483037162738E-05</v>
       </c>
       <c r="F63">
-        <v>-8.49493587866235</v>
+        <v>-1.64048303716273E-05</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>7.940933880509066E-20</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8586,10 +8608,10 @@
         <v>9</v>
       </c>
       <c r="E64">
-        <v>-31.34207305001566</v>
+        <v>-27.94744095141281</v>
       </c>
       <c r="F64">
-        <v>31.34207305001566</v>
+        <v>27.94744095141281</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8609,13 +8631,13 @@
         <v>10</v>
       </c>
       <c r="E65">
-        <v>-6.471743754349784</v>
+        <v>-5.165400116865585</v>
       </c>
       <c r="F65">
-        <v>6.487030301687302</v>
+        <v>5.177095429780356</v>
       </c>
       <c r="G65">
-        <v>0.01528654733751883</v>
+        <v>0.01169531291477094</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8632,13 +8654,13 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>-10.06416303194601</v>
+        <v>-9.252795062482075</v>
       </c>
       <c r="F66">
-        <v>10.19563130671219</v>
+        <v>9.367576333843049</v>
       </c>
       <c r="G66">
-        <v>0.1314682747661763</v>
+        <v>0.1147812713609725</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -8655,13 +8677,13 @@
         <v>11</v>
       </c>
       <c r="E67">
-        <v>2.538395453338389</v>
+        <v>3.849464792806736</v>
       </c>
       <c r="F67">
-        <v>-2.528256335636673</v>
+        <v>-3.834599973125319</v>
       </c>
       <c r="G67">
-        <v>0.01013911770171641</v>
+        <v>0.01486481968141704</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8678,13 +8700,13 @@
         <v>13</v>
       </c>
       <c r="E68">
-        <v>-1.473763942971583</v>
+        <v>-1.632045942738864</v>
       </c>
       <c r="F68">
-        <v>1.479875559294608</v>
+        <v>1.638872483456526</v>
       </c>
       <c r="G68">
-        <v>0.006111616323024871</v>
+        <v>0.006826540717662019</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8701,13 +8723,13 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>-4.835837117040442</v>
+        <v>-5.647205086508828</v>
       </c>
       <c r="F69">
-        <v>4.8827992177927</v>
+        <v>5.70582124772564</v>
       </c>
       <c r="G69">
-        <v>0.04696210075225762</v>
+        <v>0.05861616121681235</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -8724,13 +8746,13 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>-126.7671118236153</v>
+        <v>-124.9349137455801</v>
       </c>
       <c r="F70">
-        <v>129.6692230777652</v>
+        <v>127.7513407880341</v>
       </c>
       <c r="G70">
-        <v>2.902111254149964</v>
+        <v>2.816427042454039</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -8747,13 +8769,13 @@
         <v>5</v>
       </c>
       <c r="E71">
-        <v>-62.61040441253722</v>
+        <v>-58.36474246491061</v>
       </c>
       <c r="F71">
-        <v>64.66099683920655</v>
+        <v>60.13984917230838</v>
       </c>
       <c r="G71">
-        <v>2.050592426669329</v>
+        <v>1.775106707397767</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8770,13 +8792,13 @@
         <v>3</v>
       </c>
       <c r="E72">
-        <v>-54.24843958851137</v>
+        <v>-60.3406642063282</v>
       </c>
       <c r="F72">
-        <v>55.59269706495206</v>
+        <v>62.01500057587146</v>
       </c>
       <c r="G72">
-        <v>1.344257476440691</v>
+        <v>1.674336369543261</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -8793,13 +8815,13 @@
         <v>4</v>
       </c>
       <c r="E73">
-        <v>-47.63101375117429</v>
+        <v>-45.00789169738754</v>
       </c>
       <c r="F73">
-        <v>48.91567450887793</v>
+        <v>46.15170751005892</v>
       </c>
       <c r="G73">
-        <v>1.284660757703648</v>
+        <v>1.143815812671384</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -8816,13 +8838,13 @@
         <v>5</v>
       </c>
       <c r="E74">
-        <v>-36.54096555700757</v>
+        <v>-31.75137781332458</v>
       </c>
       <c r="F74">
-        <v>37.27791102353818</v>
+        <v>32.30667988342915</v>
       </c>
       <c r="G74">
-        <v>0.7369454665306086</v>
+        <v>0.5553020701045686</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8839,13 +8861,13 @@
         <v>4</v>
       </c>
       <c r="E75">
-        <v>11.30824654176312</v>
+        <v>21.0110933310728</v>
       </c>
       <c r="F75">
-        <v>-11.20886424883492</v>
+        <v>-20.70115298441415</v>
       </c>
       <c r="G75">
-        <v>0.09938229292820178</v>
+        <v>0.3099403466586464</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -8862,13 +8884,13 @@
         <v>5</v>
       </c>
       <c r="E76">
-        <v>49.49590120942013</v>
+        <v>58.46334431054731</v>
       </c>
       <c r="F76">
-        <v>-49.16495929329889</v>
+        <v>-58.00940977419457</v>
       </c>
       <c r="G76">
-        <v>0.3309419161212523</v>
+        <v>0.4539345363527403</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -8885,13 +8907,13 @@
         <v>11</v>
       </c>
       <c r="E77">
-        <v>-6.038395488324845</v>
+        <v>-7.251158844408306</v>
       </c>
       <c r="F77">
-        <v>6.087317356238203</v>
+        <v>7.310956649893813</v>
       </c>
       <c r="G77">
-        <v>0.04892186791335823</v>
+        <v>0.05979780548550639</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -8908,13 +8930,13 @@
         <v>12</v>
       </c>
       <c r="E78">
-        <v>-7.579875620281064</v>
+        <v>-7.72597272087715</v>
       </c>
       <c r="F78">
-        <v>7.651663352956444</v>
+        <v>7.799830576004495</v>
       </c>
       <c r="G78">
-        <v>0.07178773267537963</v>
+        <v>0.07385785512734472</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -8931,13 +8953,13 @@
         <v>13</v>
       </c>
       <c r="E79">
-        <v>-16.90903540980757</v>
+        <v>-17.52327792569723</v>
       </c>
       <c r="F79">
-        <v>17.11666986637344</v>
+        <v>17.74200481995227</v>
       </c>
       <c r="G79">
-        <v>0.2076344565658722</v>
+        <v>0.2187268942550336</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -8954,10 +8976,10 @@
         <v>8</v>
       </c>
       <c r="E80">
-        <v>8.49493587866235</v>
+        <v>3.151148813182176E-05</v>
       </c>
       <c r="F80">
-        <v>-8.49493587866235</v>
+        <v>-3.151148813182176E-05</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -8977,10 +8999,10 @@
         <v>9</v>
       </c>
       <c r="E81">
-        <v>-31.34207305001566</v>
+        <v>-28.04926521519637</v>
       </c>
       <c r="F81">
-        <v>31.34207305001566</v>
+        <v>28.04926521519637</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -9000,13 +9022,13 @@
         <v>10</v>
       </c>
       <c r="E82">
-        <v>-6.471743754349784</v>
+        <v>-5.263140839927423</v>
       </c>
       <c r="F82">
-        <v>6.487030301687302</v>
+        <v>5.275131263320679</v>
       </c>
       <c r="G82">
-        <v>0.01528654733751883</v>
+        <v>0.01199042339325648</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -9023,13 +9045,13 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>-10.06416303194601</v>
+        <v>-9.31498235392521</v>
       </c>
       <c r="F83">
-        <v>10.19563130671219</v>
+        <v>9.431108924090232</v>
       </c>
       <c r="G83">
-        <v>0.1314682747661763</v>
+        <v>0.1161265701650219</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -9046,13 +9068,13 @@
         <v>11</v>
       </c>
       <c r="E84">
-        <v>2.538395453338389</v>
+        <v>3.7511588094174</v>
       </c>
       <c r="F84">
-        <v>-2.528256335636673</v>
+        <v>-3.736859250063482</v>
       </c>
       <c r="G84">
-        <v>0.01013911770171641</v>
+        <v>0.01429955935391761</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -9069,13 +9091,13 @@
         <v>13</v>
       </c>
       <c r="E85">
-        <v>-1.473763942971583</v>
+        <v>-1.619225005940853</v>
       </c>
       <c r="F85">
-        <v>1.479875559294608</v>
+        <v>1.625972659886245</v>
       </c>
       <c r="G85">
-        <v>0.006111616323024871</v>
+        <v>0.006747653945391938</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -9092,13 +9114,13 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>-4.835837117040442</v>
+        <v>-5.585017795065696</v>
       </c>
       <c r="F86">
-        <v>4.8827992177927</v>
+        <v>5.642502796647182</v>
       </c>
       <c r="G86">
-        <v>0.04696210075225762</v>
+        <v>0.05748500158148651</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -9115,13 +9137,13 @@
         <v>2</v>
       </c>
       <c r="E87">
-        <v>-126.7671118236153</v>
+        <v>-127.7466649342304</v>
       </c>
       <c r="F87">
-        <v>129.6692230777652</v>
+        <v>130.694263218182</v>
       </c>
       <c r="G87">
-        <v>2.902111254149964</v>
+        <v>2.947598283951569</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -9138,13 +9160,13 @@
         <v>5</v>
       </c>
       <c r="E88">
-        <v>-62.61040441253722</v>
+        <v>-58.20228354083585</v>
       </c>
       <c r="F88">
-        <v>64.66099683920655</v>
+        <v>59.96729580234624</v>
       </c>
       <c r="G88">
-        <v>2.050592426669329</v>
+        <v>1.76501226151039</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -9161,13 +9183,13 @@
         <v>3</v>
       </c>
       <c r="E89">
-        <v>-54.24843958851137</v>
+        <v>-56.62462601905089</v>
       </c>
       <c r="F89">
-        <v>55.59269706495206</v>
+        <v>58.09488691072202</v>
       </c>
       <c r="G89">
-        <v>1.344257476440691</v>
+        <v>1.470260891671127</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -9184,13 +9206,13 @@
         <v>4</v>
       </c>
       <c r="E90">
-        <v>-47.63101375117429</v>
+        <v>-43.58204443306322</v>
       </c>
       <c r="F90">
-        <v>48.91567450887793</v>
+        <v>44.65380965461227</v>
       </c>
       <c r="G90">
-        <v>1.284660757703648</v>
+        <v>1.071765221549054</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -9207,13 +9229,13 @@
         <v>5</v>
       </c>
       <c r="E91">
-        <v>-36.54096555700757</v>
+        <v>-30.58952209820193</v>
       </c>
       <c r="F91">
-        <v>37.27791102353818</v>
+        <v>31.10528400788313</v>
       </c>
       <c r="G91">
-        <v>0.7369454665306086</v>
+        <v>0.5157619096812061</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -9230,13 +9252,13 @@
         <v>4</v>
       </c>
       <c r="E92">
-        <v>11.30824654176312</v>
+        <v>18.28124182338229</v>
       </c>
       <c r="F92">
-        <v>-11.20886424883492</v>
+        <v>-18.04395295630816</v>
       </c>
       <c r="G92">
-        <v>0.09938229292820178</v>
+        <v>0.2372888670741286</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -9253,13 +9275,13 @@
         <v>5</v>
       </c>
       <c r="E93">
-        <v>49.49590120942013</v>
+        <v>57.22118895579467</v>
       </c>
       <c r="F93">
-        <v>-49.16495929329889</v>
+        <v>-56.78619341130017</v>
       </c>
       <c r="G93">
-        <v>0.3309419161212523</v>
+        <v>0.4349955444944986</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -9276,13 +9298,13 @@
         <v>11</v>
       </c>
       <c r="E94">
-        <v>-6.038395488324845</v>
+        <v>-7.202008373883649</v>
       </c>
       <c r="F94">
-        <v>6.087317356238203</v>
+        <v>7.261178649804396</v>
       </c>
       <c r="G94">
-        <v>0.04892186791335823</v>
+        <v>0.05917027592074742</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -9299,13 +9321,13 @@
         <v>12</v>
       </c>
       <c r="E95">
-        <v>-7.579875620281064</v>
+        <v>-7.71951124159975</v>
       </c>
       <c r="F95">
-        <v>7.651663352956444</v>
+        <v>7.793260911578749</v>
       </c>
       <c r="G95">
-        <v>0.07178773267537963</v>
+        <v>0.0737496699789994</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -9322,13 +9344,13 @@
         <v>13</v>
       </c>
       <c r="E96">
-        <v>-16.90903540980757</v>
+        <v>-17.49802429453177</v>
       </c>
       <c r="F96">
-        <v>17.11666986637344</v>
+        <v>17.71619771434555</v>
       </c>
       <c r="G96">
-        <v>0.2076344565658722</v>
+        <v>0.2181734198137747</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -9345,10 +9367,10 @@
         <v>8</v>
       </c>
       <c r="E97">
-        <v>8.49493587866235</v>
+        <v>5.683653296539279E-05</v>
       </c>
       <c r="F97">
-        <v>-8.49493587866235</v>
+        <v>-5.683653296539279E-05</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9368,10 +9390,10 @@
         <v>9</v>
       </c>
       <c r="E98">
-        <v>-31.34207305001566</v>
+        <v>-28.1001895224334</v>
       </c>
       <c r="F98">
-        <v>31.34207305001566</v>
+        <v>28.1001895224334</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9391,13 +9413,13 @@
         <v>10</v>
       </c>
       <c r="E99">
-        <v>-6.471743754349784</v>
+        <v>-5.312012716066285</v>
       </c>
       <c r="F99">
-        <v>6.487030301687302</v>
+        <v>5.324153652047523</v>
       </c>
       <c r="G99">
-        <v>0.01528654733751883</v>
+        <v>0.01214093598123911</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -9414,13 +9436,13 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>-10.06416303194601</v>
+        <v>-9.346095070311382</v>
       </c>
       <c r="F100">
-        <v>10.19563130671219</v>
+        <v>9.462899745145279</v>
       </c>
       <c r="G100">
-        <v>0.1314682747661763</v>
+        <v>0.1168046748338966</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -9437,13 +9459,13 @@
         <v>11</v>
       </c>
       <c r="E101">
-        <v>2.538395453338389</v>
+        <v>3.702008338892743</v>
       </c>
       <c r="F101">
-        <v>-2.528256335636673</v>
+        <v>-3.68798737392462</v>
       </c>
       <c r="G101">
-        <v>0.01013911770171641</v>
+        <v>0.01402096496812347</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -9460,13 +9482,13 @@
         <v>13</v>
       </c>
       <c r="E102">
-        <v>-1.473763942971583</v>
+        <v>-1.61280297408395</v>
       </c>
       <c r="F102">
-        <v>1.479875559294608</v>
+        <v>1.619511180608845</v>
       </c>
       <c r="G102">
-        <v>0.006111616323024871</v>
+        <v>0.006708206524894816</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -9483,13 +9505,13 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>-4.835837117040442</v>
+        <v>-5.553905078679524</v>
       </c>
       <c r="F103">
-        <v>4.8827992177927</v>
+        <v>5.610827133624819</v>
       </c>
       <c r="G103">
-        <v>0.04696210075225762</v>
+        <v>0.05692205494529576</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -9506,13 +9528,13 @@
         <v>2</v>
       </c>
       <c r="E104">
-        <v>-126.7671118236153</v>
+        <v>-125.4127082413875</v>
       </c>
       <c r="F104">
-        <v>129.6692230777652</v>
+        <v>128.2512045007337</v>
       </c>
       <c r="G104">
-        <v>2.902111254149964</v>
+        <v>2.838496259346157</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -9529,13 +9551,13 @@
         <v>5</v>
       </c>
       <c r="E105">
-        <v>-62.61040441253722</v>
+        <v>-58.33703243469044</v>
       </c>
       <c r="F105">
-        <v>64.66099683920655</v>
+        <v>60.1104157308343</v>
       </c>
       <c r="G105">
-        <v>2.050592426669329</v>
+        <v>1.77338329614386</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9552,13 +9574,13 @@
         <v>3</v>
       </c>
       <c r="E106">
-        <v>-54.24843958851137</v>
+        <v>-59.70959326695237</v>
       </c>
       <c r="F106">
-        <v>55.59269706495206</v>
+        <v>61.3482969302953</v>
       </c>
       <c r="G106">
-        <v>1.344257476440691</v>
+        <v>1.638703663342922</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -9575,13 +9597,13 @@
         <v>4</v>
       </c>
       <c r="E107">
-        <v>-47.63101375117429</v>
+        <v>-44.76557696357164</v>
       </c>
       <c r="F107">
-        <v>48.91567450887793</v>
+        <v>45.89697838372966</v>
       </c>
       <c r="G107">
-        <v>1.284660757703648</v>
+        <v>1.131401420158018</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -9598,13 +9620,13 @@
         <v>5</v>
       </c>
       <c r="E108">
-        <v>-36.54096555700757</v>
+        <v>-31.55391590889541</v>
       </c>
       <c r="F108">
-        <v>37.27791102353818</v>
+        <v>32.10239138874032</v>
       </c>
       <c r="G108">
-        <v>0.7369454665306086</v>
+        <v>0.5484754798449065</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -9621,13 +9643,13 @@
         <v>4</v>
       </c>
       <c r="E109">
-        <v>11.30824654176312</v>
+        <v>20.54708842568411</v>
       </c>
       <c r="F109">
-        <v>-11.20886424883492</v>
+        <v>-20.25020287823525</v>
       </c>
       <c r="G109">
-        <v>0.09938229292820178</v>
+        <v>0.2968855474488608</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -9644,13 +9666,13 @@
         <v>5</v>
       </c>
       <c r="E110">
-        <v>49.49590120942013</v>
+        <v>58.25213879438705</v>
       </c>
       <c r="F110">
-        <v>-49.16495929329889</v>
+        <v>-57.80145391860735</v>
       </c>
       <c r="G110">
-        <v>0.3309419161212523</v>
+        <v>0.4506848757797055</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -9667,13 +9689,13 @@
         <v>11</v>
       </c>
       <c r="E111">
-        <v>-6.038395488324845</v>
+        <v>-7.242803119175104</v>
       </c>
       <c r="F111">
-        <v>6.087317356238203</v>
+        <v>7.302494087539695</v>
       </c>
       <c r="G111">
-        <v>0.04892186791335823</v>
+        <v>0.05969096836459103</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -9690,13 +9712,13 @@
         <v>12</v>
       </c>
       <c r="E112">
-        <v>-7.579875620281064</v>
+        <v>-7.724874809459213</v>
       </c>
       <c r="F112">
-        <v>7.651663352956444</v>
+        <v>7.798714290767177</v>
       </c>
       <c r="G112">
-        <v>0.07178773267537963</v>
+        <v>0.07383948130796347</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -9713,13 +9735,13 @@
         <v>13</v>
       </c>
       <c r="E113">
-        <v>-16.90903540980757</v>
+        <v>-17.51898502358608</v>
       </c>
       <c r="F113">
-        <v>17.11666986637344</v>
+        <v>17.73761786981683</v>
       </c>
       <c r="G113">
-        <v>0.2076344565658722</v>
+        <v>0.2186328462307568</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -9736,13 +9758,13 @@
         <v>8</v>
       </c>
       <c r="E114">
-        <v>8.49493587866235</v>
+        <v>3.41213438105902E-05</v>
       </c>
       <c r="F114">
-        <v>-8.49493587866235</v>
+        <v>-3.412134381059021E-05</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>-1.588186776101813E-20</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -9759,10 +9781,10 @@
         <v>9</v>
       </c>
       <c r="E115">
-        <v>-31.34207305001566</v>
+        <v>-28.05792159778716</v>
       </c>
       <c r="F115">
-        <v>31.34207305001566</v>
+        <v>28.05792159778716</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -9782,13 +9804,13 @@
         <v>10</v>
       </c>
       <c r="E116">
-        <v>-6.471743754349784</v>
+        <v>-5.27144901406961</v>
       </c>
       <c r="F116">
-        <v>6.487030301687302</v>
+        <v>5.283464885719395</v>
       </c>
       <c r="G116">
-        <v>0.01528654733751883</v>
+        <v>0.01201587164978563</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -9805,13 +9827,13 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>-10.06416303194601</v>
+        <v>-9.320270636229219</v>
       </c>
       <c r="F117">
-        <v>10.19563130671219</v>
+        <v>9.436512228260378</v>
       </c>
       <c r="G117">
-        <v>0.1314682747661763</v>
+        <v>0.1162415920311591</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -9828,13 +9850,13 @@
         <v>11</v>
       </c>
       <c r="E118">
-        <v>2.538395453338389</v>
+        <v>3.742803084184198</v>
       </c>
       <c r="F118">
-        <v>-2.528256335636673</v>
+        <v>-3.728551075921295</v>
       </c>
       <c r="G118">
-        <v>0.01013911770171641</v>
+        <v>0.01425200826290288</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -9851,13 +9873,13 @@
         <v>13</v>
       </c>
       <c r="E119">
-        <v>-1.473763942971583</v>
+        <v>-1.618133800437021</v>
       </c>
       <c r="F119">
-        <v>1.479875559294608</v>
+        <v>1.624874748468309</v>
       </c>
       <c r="G119">
-        <v>0.006111616323024871</v>
+        <v>0.006740948031288066</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -9874,13 +9896,13 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>-4.835837117040442</v>
+        <v>-5.579729512761687</v>
       </c>
       <c r="F120">
-        <v>4.8827992177927</v>
+        <v>5.637118689032192</v>
       </c>
       <c r="G120">
-        <v>0.04696210075225762</v>
+        <v>0.05738917627050588</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -9897,13 +9919,13 @@
         <v>2</v>
       </c>
       <c r="E121">
-        <v>-126.7671118236153</v>
+        <v>-119.3198962680993</v>
       </c>
       <c r="F121">
-        <v>129.6692230777652</v>
+        <v>121.8837074676544</v>
       </c>
       <c r="G121">
-        <v>2.902111254149964</v>
+        <v>2.56381119955511</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -9920,13 +9942,13 @@
         <v>5</v>
       </c>
       <c r="E122">
-        <v>-62.61040441253722</v>
+        <v>-58.69349673559316</v>
       </c>
       <c r="F122">
-        <v>64.66099683920655</v>
+        <v>60.48910202655905</v>
       </c>
       <c r="G122">
-        <v>2.050592426669329</v>
+        <v>1.795605290965885</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -9943,13 +9965,13 @@
         <v>3</v>
       </c>
       <c r="E123">
-        <v>-54.24843958851137</v>
+        <v>-67.74468224602678</v>
       </c>
       <c r="F123">
-        <v>55.59269706495206</v>
+        <v>69.86714897664942</v>
       </c>
       <c r="G123">
-        <v>1.344257476440691</v>
+        <v>2.122466730622641</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -9966,13 +9988,13 @@
         <v>4</v>
       </c>
       <c r="E124">
-        <v>-47.63101375117429</v>
+        <v>-47.85617393974659</v>
       </c>
       <c r="F124">
-        <v>48.91567450887793</v>
+        <v>49.15113692431602</v>
       </c>
       <c r="G124">
-        <v>1.284660757703648</v>
+        <v>1.294962984569431</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -9989,13 +10011,13 @@
         <v>5</v>
       </c>
       <c r="E125">
-        <v>-36.54096555700757</v>
+        <v>-34.07279013800302</v>
       </c>
       <c r="F125">
-        <v>37.27791102353818</v>
+        <v>34.7116232137045</v>
       </c>
       <c r="G125">
-        <v>0.7369454665306086</v>
+        <v>0.6388330757014726</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -10012,13 +10034,13 @@
         <v>4</v>
       </c>
       <c r="E126">
-        <v>11.30824654176312</v>
+        <v>26.46764922682695</v>
       </c>
       <c r="F126">
-        <v>-11.20886424883492</v>
+        <v>-25.98244246024615</v>
       </c>
       <c r="G126">
-        <v>0.09938229292820178</v>
+        <v>0.485206766580798</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -10035,13 +10057,13 @@
         <v>5</v>
       </c>
       <c r="E127">
-        <v>49.49590120942013</v>
+        <v>60.94922027076419</v>
       </c>
       <c r="F127">
-        <v>-49.16495929329889</v>
+        <v>-60.45613011909001</v>
       </c>
       <c r="G127">
-        <v>0.3309419161212523</v>
+        <v>0.4930901516741804</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -10058,13 +10080,13 @@
         <v>11</v>
       </c>
       <c r="E128">
-        <v>-6.038395488324845</v>
+        <v>-7.349464827797668</v>
       </c>
       <c r="F128">
-        <v>6.087317356238203</v>
+        <v>7.410524349438193</v>
       </c>
       <c r="G128">
-        <v>0.04892186791335823</v>
+        <v>0.06105952164052464</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -10081,13 +10103,13 @@
         <v>12</v>
       </c>
       <c r="E129">
-        <v>-7.579875620281064</v>
+        <v>-7.738872544447455</v>
       </c>
       <c r="F129">
-        <v>7.651663352956444</v>
+        <v>7.812946015350258</v>
       </c>
       <c r="G129">
-        <v>0.07178773267537963</v>
+        <v>0.07407347090280375</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -10104,13 +10126,13 @@
         <v>13</v>
       </c>
       <c r="E130">
-        <v>-16.90903540980757</v>
+        <v>-17.57377543997762</v>
       </c>
       <c r="F130">
-        <v>17.11666986637344</v>
+        <v>17.79360745141586</v>
       </c>
       <c r="G130">
-        <v>0.2076344565658722</v>
+        <v>0.2198320114382396</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -10127,13 +10149,13 @@
         <v>8</v>
       </c>
       <c r="E131">
-        <v>8.49493587866235</v>
+        <v>1.640483037162699E-05</v>
       </c>
       <c r="F131">
-        <v>-8.49493587866235</v>
+        <v>-1.640483037162689E-05</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>9.529120656610879E-20</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -10150,10 +10172,10 @@
         <v>9</v>
       </c>
       <c r="E132">
-        <v>-31.34207305001566</v>
+        <v>-27.94744095141283</v>
       </c>
       <c r="F132">
-        <v>31.34207305001566</v>
+        <v>27.94744095141283</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -10173,13 +10195,13 @@
         <v>10</v>
       </c>
       <c r="E133">
-        <v>-6.471743754349784</v>
+        <v>-5.165400116865648</v>
       </c>
       <c r="F133">
-        <v>6.487030301687302</v>
+        <v>5.177095429780419</v>
       </c>
       <c r="G133">
-        <v>0.01528654733751883</v>
+        <v>0.01169531291477094</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -10196,13 +10218,13 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>-10.06416303194601</v>
+        <v>-9.25279506248207</v>
       </c>
       <c r="F134">
-        <v>10.19563130671219</v>
+        <v>9.367576333843022</v>
       </c>
       <c r="G134">
-        <v>0.1314682747661763</v>
+        <v>0.1147812713609517</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10219,13 +10241,13 @@
         <v>11</v>
       </c>
       <c r="E135">
-        <v>2.538395453338389</v>
+        <v>3.849464792806762</v>
       </c>
       <c r="F135">
-        <v>-2.528256335636673</v>
+        <v>-3.834599973125257</v>
       </c>
       <c r="G135">
-        <v>0.01013911770171641</v>
+        <v>0.01486481968150516</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -10242,13 +10264,13 @@
         <v>13</v>
       </c>
       <c r="E136">
-        <v>-1.473763942971583</v>
+        <v>-1.632045942738931</v>
       </c>
       <c r="F136">
-        <v>1.479875559294608</v>
+        <v>1.638872483456549</v>
       </c>
       <c r="G136">
-        <v>0.006111616323024871</v>
+        <v>0.006826540717618304</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10265,13 +10287,13 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>-4.835837117040442</v>
+        <v>-5.647205086508833</v>
       </c>
       <c r="F137">
-        <v>4.8827992177927</v>
+        <v>5.705821247725646</v>
       </c>
       <c r="G137">
-        <v>0.04696210075225762</v>
+        <v>0.05861616121681165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -10288,13 +10310,13 @@
         <v>2</v>
       </c>
       <c r="E138">
-        <v>-126.7671118236153</v>
+        <v>-137.9618172706419</v>
       </c>
       <c r="F138">
-        <v>129.6692230777652</v>
+        <v>141.4120219466132</v>
       </c>
       <c r="G138">
-        <v>2.902111254149964</v>
+        <v>3.450204675971258</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -10311,13 +10333,13 @@
         <v>5</v>
       </c>
       <c r="E139">
-        <v>-62.61040441253722</v>
+        <v>-55.80106599847289</v>
       </c>
       <c r="F139">
-        <v>64.66099683920655</v>
+        <v>57.41859341513662</v>
       </c>
       <c r="G139">
-        <v>2.050592426669329</v>
+        <v>1.617527416663733</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -10334,13 +10356,13 @@
         <v>3</v>
       </c>
       <c r="E140">
-        <v>-54.24843958851137</v>
+        <v>-44.28992318003962</v>
       </c>
       <c r="F140">
-        <v>55.59269706495206</v>
+        <v>45.18168787576803</v>
       </c>
       <c r="G140">
-        <v>1.344257476440691</v>
+        <v>0.8917646957284087</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -10357,13 +10379,13 @@
         <v>4</v>
       </c>
       <c r="E141">
-        <v>-47.63101375117429</v>
+        <v>-35.60361128894712</v>
       </c>
       <c r="F141">
-        <v>48.91567450887793</v>
+        <v>36.31487730277718</v>
       </c>
       <c r="G141">
-        <v>1.284660757703648</v>
+        <v>0.7112660138300642</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -10380,13 +10402,13 @@
         <v>5</v>
       </c>
       <c r="E142">
-        <v>-36.54096555700757</v>
+        <v>-24.00017727883202</v>
       </c>
       <c r="F142">
-        <v>37.27791102353818</v>
+        <v>24.31864526851874</v>
       </c>
       <c r="G142">
-        <v>0.7369454665306086</v>
+        <v>0.3184679896867187</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -10403,13 +10425,13 @@
         <v>4</v>
       </c>
       <c r="E143">
-        <v>11.30824654176312</v>
+        <v>12.71068781170511</v>
       </c>
       <c r="F143">
-        <v>-11.20886424883492</v>
+        <v>-12.59425412707953</v>
       </c>
       <c r="G143">
-        <v>0.09938229292820178</v>
+        <v>0.1164336846255776</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -10426,13 +10448,13 @@
         <v>5</v>
       </c>
       <c r="E144">
-        <v>49.49590120942013</v>
+        <v>50.69364047740748</v>
       </c>
       <c r="F144">
-        <v>-49.16495929329889</v>
+        <v>-50.35066559584458</v>
       </c>
       <c r="G144">
-        <v>0.3309419161212523</v>
+        <v>0.3429748815628963</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -10449,13 +10471,13 @@
         <v>11</v>
       </c>
       <c r="E145">
-        <v>-6.038395488324845</v>
+        <v>-5.718853366966443</v>
       </c>
       <c r="F145">
-        <v>6.087317356238203</v>
+        <v>5.762597958991775</v>
       </c>
       <c r="G145">
-        <v>0.04892186791335823</v>
+        <v>0.04374459202533196</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -10472,13 +10494,13 @@
         <v>12</v>
       </c>
       <c r="E146">
-        <v>-7.579875620281064</v>
+        <v>-7.530868012619288</v>
       </c>
       <c r="F146">
-        <v>7.651663352956444</v>
+        <v>7.601665096127788</v>
       </c>
       <c r="G146">
-        <v>0.07178773267537963</v>
+        <v>0.07079708350850034</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -10495,13 +10517,13 @@
         <v>13</v>
       </c>
       <c r="E147">
-        <v>-16.90903540980757</v>
+        <v>-16.74050320602231</v>
       </c>
       <c r="F147">
-        <v>17.11666986637344</v>
+        <v>16.94343407998871</v>
       </c>
       <c r="G147">
-        <v>0.2076344565658722</v>
+        <v>0.2029308739664032</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -10518,10 +10540,10 @@
         <v>8</v>
       </c>
       <c r="E148">
-        <v>8.49493587866235</v>
+        <v>11.27680972655411</v>
       </c>
       <c r="F148">
-        <v>-8.49493587866235</v>
+        <v>-11.27680972655411</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10541,10 +10563,10 @@
         <v>9</v>
       </c>
       <c r="E149">
-        <v>-31.34207305001566</v>
+        <v>-32.34271123241701</v>
       </c>
       <c r="F149">
-        <v>31.34207305001566</v>
+        <v>32.34271123241701</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10564,13 +10586,13 @@
         <v>10</v>
       </c>
       <c r="E150">
-        <v>-6.471743754349784</v>
+        <v>-6.789198371717791</v>
       </c>
       <c r="F150">
-        <v>6.487030301687302</v>
+        <v>6.806143194285238</v>
       </c>
       <c r="G150">
-        <v>0.01528654733751883</v>
+        <v>0.01694482256744817</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -10587,13 +10609,13 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>-10.06416303194601</v>
+        <v>-10.2768967025783</v>
       </c>
       <c r="F151">
-        <v>10.19563130671219</v>
+        <v>10.41425615488809</v>
       </c>
       <c r="G151">
-        <v>0.1314682747661763</v>
+        <v>0.1373594523097862</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -10610,13 +10632,13 @@
         <v>11</v>
       </c>
       <c r="E152">
-        <v>2.538395453338389</v>
+        <v>2.218853331975537</v>
       </c>
       <c r="F152">
-        <v>-2.528256335636673</v>
+        <v>-2.210801718273115</v>
       </c>
       <c r="G152">
-        <v>0.01013911770171641</v>
+        <v>0.0080516137024228</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -10633,13 +10655,13 @@
         <v>13</v>
       </c>
       <c r="E153">
-        <v>-1.473763942971583</v>
+        <v>-1.425137088987038</v>
       </c>
       <c r="F153">
-        <v>1.479875559294608</v>
+        <v>1.430867951628382</v>
       </c>
       <c r="G153">
-        <v>0.006111616323024871</v>
+        <v>0.005730862641344439</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -10656,13 +10678,13 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>-4.835837117040442</v>
+        <v>-4.623103446412602</v>
       </c>
       <c r="F154">
-        <v>4.8827992177927</v>
+        <v>4.665640160018436</v>
       </c>
       <c r="G154">
-        <v>0.04696210075225762</v>
+        <v>0.04253671360583272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -10679,13 +10701,13 @@
         <v>2</v>
       </c>
       <c r="E155">
-        <v>-126.7671118236153</v>
+        <v>-125.4127082413875</v>
       </c>
       <c r="F155">
-        <v>129.6692230777652</v>
+        <v>128.2512045007336</v>
       </c>
       <c r="G155">
-        <v>2.902111254149964</v>
+        <v>2.838496259346068</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -10702,13 +10724,13 @@
         <v>5</v>
       </c>
       <c r="E156">
-        <v>-62.61040441253722</v>
+        <v>-58.33703243469041</v>
       </c>
       <c r="F156">
-        <v>64.66099683920655</v>
+        <v>60.11041573083426</v>
       </c>
       <c r="G156">
-        <v>2.050592426669329</v>
+        <v>1.773383296143849</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10725,13 +10747,13 @@
         <v>3</v>
       </c>
       <c r="E157">
-        <v>-54.24843958851137</v>
+        <v>-59.70959326695232</v>
       </c>
       <c r="F157">
-        <v>55.59269706495206</v>
+        <v>61.34829693029524</v>
       </c>
       <c r="G157">
-        <v>1.344257476440691</v>
+        <v>1.638703663342922</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -10748,13 +10770,13 @@
         <v>4</v>
       </c>
       <c r="E158">
-        <v>-47.63101375117429</v>
+        <v>-44.76557696357163</v>
       </c>
       <c r="F158">
-        <v>48.91567450887793</v>
+        <v>45.89697838372964</v>
       </c>
       <c r="G158">
-        <v>1.284660757703648</v>
+        <v>1.131401420158018</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -10771,13 +10793,13 @@
         <v>5</v>
       </c>
       <c r="E159">
-        <v>-36.54096555700757</v>
+        <v>-31.55391590889545</v>
       </c>
       <c r="F159">
-        <v>37.27791102353818</v>
+        <v>32.10239138874036</v>
       </c>
       <c r="G159">
-        <v>0.7369454665306086</v>
+        <v>0.5484754798449065</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -10794,13 +10816,13 @@
         <v>4</v>
       </c>
       <c r="E160">
-        <v>11.30824654176312</v>
+        <v>20.54708842568409</v>
       </c>
       <c r="F160">
-        <v>-11.20886424883492</v>
+        <v>-20.25020287823519</v>
       </c>
       <c r="G160">
-        <v>0.09938229292820178</v>
+        <v>0.2968855474489024</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -10817,13 +10839,13 @@
         <v>5</v>
       </c>
       <c r="E161">
-        <v>49.49590120942013</v>
+        <v>58.25213879438702</v>
       </c>
       <c r="F161">
-        <v>-49.16495929329889</v>
+        <v>-57.80145391860733</v>
       </c>
       <c r="G161">
-        <v>0.3309419161212523</v>
+        <v>0.4506848757796944</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -10840,13 +10862,13 @@
         <v>11</v>
       </c>
       <c r="E162">
-        <v>-6.038395488324845</v>
+        <v>-7.24280311917507</v>
       </c>
       <c r="F162">
-        <v>6.087317356238203</v>
+        <v>7.302494087539663</v>
       </c>
       <c r="G162">
-        <v>0.04892186791335823</v>
+        <v>0.05969096836459242</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -10863,13 +10885,13 @@
         <v>12</v>
       </c>
       <c r="E163">
-        <v>-7.579875620281064</v>
+        <v>-7.724874809459219</v>
       </c>
       <c r="F163">
-        <v>7.651663352956444</v>
+        <v>7.798714290767182</v>
       </c>
       <c r="G163">
-        <v>0.07178773267537963</v>
+        <v>0.07383948130796347</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -10886,13 +10908,13 @@
         <v>13</v>
       </c>
       <c r="E164">
-        <v>-16.90903540980757</v>
+        <v>-17.51898502358604</v>
       </c>
       <c r="F164">
-        <v>17.11666986637344</v>
+        <v>17.73761786981688</v>
       </c>
       <c r="G164">
-        <v>0.2076344565658722</v>
+        <v>0.2186328462308457</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -10909,13 +10931,13 @@
         <v>8</v>
       </c>
       <c r="E165">
-        <v>8.49493587866235</v>
+        <v>3.412134381059715E-05</v>
       </c>
       <c r="F165">
-        <v>-8.49493587866235</v>
+        <v>-3.412134381059713E-05</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>1.058791184067875E-20</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -10932,10 +10954,10 @@
         <v>9</v>
       </c>
       <c r="E166">
-        <v>-31.34207305001566</v>
+        <v>-28.05792159778713</v>
       </c>
       <c r="F166">
-        <v>31.34207305001566</v>
+        <v>28.05792159778713</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -10955,13 +10977,13 @@
         <v>10</v>
       </c>
       <c r="E167">
-        <v>-6.471743754349784</v>
+        <v>-5.271449014069598</v>
       </c>
       <c r="F167">
-        <v>6.487030301687302</v>
+        <v>5.283464885719295</v>
       </c>
       <c r="G167">
-        <v>0.01528654733751883</v>
+        <v>0.0120158716496975</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -10978,13 +11000,13 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>-10.06416303194601</v>
+        <v>-9.320270636229251</v>
       </c>
       <c r="F168">
-        <v>10.19563130671219</v>
+        <v>9.436512228260431</v>
       </c>
       <c r="G168">
-        <v>0.1314682747661763</v>
+        <v>0.1162415920311799</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -11001,13 +11023,13 @@
         <v>11</v>
       </c>
       <c r="E169">
-        <v>2.538395453338389</v>
+        <v>3.742803084184164</v>
       </c>
       <c r="F169">
-        <v>-2.528256335636673</v>
+        <v>-3.728551075921306</v>
       </c>
       <c r="G169">
-        <v>0.01013911770171641</v>
+        <v>0.01425200826285847</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -11024,13 +11046,13 @@
         <v>13</v>
       </c>
       <c r="E170">
-        <v>-1.473763942971583</v>
+        <v>-1.618133800437027</v>
       </c>
       <c r="F170">
-        <v>1.479875559294608</v>
+        <v>1.624874748468315</v>
       </c>
       <c r="G170">
-        <v>0.006111616323024871</v>
+        <v>0.006740948031287719</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -11047,13 +11069,13 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>-4.835837117040442</v>
+        <v>-5.579729512761654</v>
       </c>
       <c r="F171">
-        <v>4.8827992177927</v>
+        <v>5.637118689032159</v>
       </c>
       <c r="G171">
-        <v>0.04696210075225762</v>
+        <v>0.05738917627050519</v>
       </c>
     </row>
   </sheetData>
@@ -11103,10 +11125,10 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>-22.84713717135303</v>
+        <v>-27.95251209738333</v>
       </c>
       <c r="F2">
-        <v>22.84713717135303</v>
+        <v>27.95251209738333</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -11126,10 +11148,10 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>-14.8405888533702</v>
+        <v>-16.10021545735942</v>
       </c>
       <c r="F3">
-        <v>14.8405888533702</v>
+        <v>16.10021545735942</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -11149,10 +11171,10 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>-42.05546868413807</v>
+        <v>-44.20885849857881</v>
       </c>
       <c r="F4">
-        <v>42.05546868413807</v>
+        <v>44.20885849857881</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -11172,10 +11194,10 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>-22.84713717135331</v>
+        <v>-27.9576021732491</v>
       </c>
       <c r="F5">
-        <v>22.84713717135331</v>
+        <v>27.9576021732491</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -11195,10 +11217,10 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-14.84058885337028</v>
+        <v>-16.10320144422452</v>
       </c>
       <c r="F6">
-        <v>14.84058885337028</v>
+        <v>16.10320144422452</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -11218,10 +11240,10 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-42.0554686841382</v>
+        <v>-44.20064499691021</v>
       </c>
       <c r="F7">
-        <v>42.0554686841382</v>
+        <v>44.20064499691021</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -11241,10 +11263,10 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>-22.84713717135331</v>
+        <v>-27.96269257393065</v>
       </c>
       <c r="F8">
-        <v>22.84713717135331</v>
+        <v>27.96269257393065</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -11264,10 +11286,10 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-14.84058885337028</v>
+        <v>-16.10618773953689</v>
       </c>
       <c r="F9">
-        <v>14.84058885337028</v>
+        <v>16.10618773953689</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -11287,10 +11309,10 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-42.0554686841382</v>
+        <v>-44.1924309373244</v>
       </c>
       <c r="F10">
-        <v>42.0554686841382</v>
+        <v>44.1924309373244</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -11310,10 +11332,10 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-22.84713717135331</v>
+        <v>-27.94742454658244</v>
       </c>
       <c r="F11">
-        <v>22.84713717135331</v>
+        <v>27.94742454658244</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -11333,10 +11355,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>-14.84058885337028</v>
+        <v>-16.09723110720149</v>
       </c>
       <c r="F12">
-        <v>14.84058885337028</v>
+        <v>16.09723110720149</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -11356,10 +11378,10 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-42.0554686841382</v>
+        <v>-44.21706781528806</v>
       </c>
       <c r="F13">
-        <v>42.0554686841382</v>
+        <v>44.21706781528806</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -11379,10 +11401,10 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <v>-22.84713717135331</v>
+        <v>-28.04923370370824</v>
       </c>
       <c r="F14">
-        <v>22.84713717135331</v>
+        <v>28.04923370370824</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -11402,10 +11424,10 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-14.84058885337028</v>
+        <v>-16.15697526720544</v>
       </c>
       <c r="F15">
-        <v>14.84058885337028</v>
+        <v>16.15697526720544</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -11425,10 +11447,10 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-42.0554686841382</v>
+        <v>-44.05277718929605</v>
       </c>
       <c r="F16">
-        <v>42.0554686841382</v>
+        <v>44.05277718929605</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -11448,10 +11470,10 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-22.84713717135331</v>
+        <v>-28.10013268590044</v>
       </c>
       <c r="F17">
-        <v>22.84713717135331</v>
+        <v>28.10013268590044</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -11471,10 +11493,10 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>-14.84058885337028</v>
+        <v>-16.18686416975029</v>
       </c>
       <c r="F18">
-        <v>14.84058885337028</v>
+        <v>16.18686416975029</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -11494,10 +11516,10 @@
         <v>6</v>
       </c>
       <c r="E19">
-        <v>-42.0554686841382</v>
+        <v>-43.97061790937</v>
       </c>
       <c r="F19">
-        <v>42.0554686841382</v>
+        <v>43.97061790937</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -11517,10 +11539,10 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>-22.84713717135331</v>
+        <v>-28.05788747644335</v>
       </c>
       <c r="F20">
-        <v>22.84713717135331</v>
+        <v>28.05788747644335</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -11540,10 +11562,10 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-14.84058885337028</v>
+        <v>-16.16205581118352</v>
       </c>
       <c r="F21">
-        <v>14.84058885337028</v>
+        <v>16.16205581118352</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -11563,10 +11585,10 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-42.0554686841382</v>
+        <v>-44.03881077157801</v>
       </c>
       <c r="F22">
-        <v>42.0554686841382</v>
+        <v>44.03881077157801</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -11586,10 +11608,10 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-22.84713717135331</v>
+        <v>-27.94742454658245</v>
       </c>
       <c r="F23">
-        <v>22.84713717135331</v>
+        <v>27.94742454658245</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -11609,10 +11631,10 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-14.84058885337028</v>
+        <v>-16.09723110720151</v>
       </c>
       <c r="F24">
-        <v>14.84058885337028</v>
+        <v>16.09723110720151</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -11632,10 +11654,10 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-42.0554686841382</v>
+        <v>-44.21706781528814</v>
       </c>
       <c r="F25">
-        <v>42.0554686841382</v>
+        <v>44.21706781528814</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -11655,10 +11677,10 @@
         <v>7</v>
       </c>
       <c r="E26">
-        <v>-22.84713717135331</v>
+        <v>-21.0659015058629</v>
       </c>
       <c r="F26">
-        <v>22.84713717135331</v>
+        <v>21.0659015058629</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -11678,10 +11700,10 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-14.84058885337028</v>
+        <v>-14.37768841174722</v>
       </c>
       <c r="F27">
-        <v>14.84058885337028</v>
+        <v>14.37768841174722</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -11701,10 +11723,10 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-42.0554686841382</v>
+        <v>-41.50760403729845</v>
       </c>
       <c r="F28">
-        <v>42.0554686841382</v>
+        <v>41.50760403729845</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -11724,10 +11746,10 @@
         <v>7</v>
       </c>
       <c r="E29">
-        <v>-22.84713717135331</v>
+        <v>-28.05788747644332</v>
       </c>
       <c r="F29">
-        <v>22.84713717135331</v>
+        <v>28.05788747644332</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -11747,10 +11769,10 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-14.84058885337028</v>
+        <v>-16.1620558111835</v>
       </c>
       <c r="F30">
-        <v>14.84058885337028</v>
+        <v>16.1620558111835</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -11770,13 +11792,449 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-42.0554686841382</v>
+        <v>-44.03881077157804</v>
       </c>
       <c r="F31">
-        <v>42.0554686841382</v>
+        <v>44.03881077157804</v>
       </c>
       <c r="G31">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>-7.667311885526099E-07</v>
+      </c>
+      <c r="E2">
+        <v>10.00000053346237</v>
+      </c>
+      <c r="H2">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>-7.629673533994482E-07</v>
+      </c>
+      <c r="E3">
+        <v>20.0000005259347</v>
+      </c>
+      <c r="H3">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>-7.668759771593371E-07</v>
+      </c>
+      <c r="E4">
+        <v>10.00000053375194</v>
+      </c>
+      <c r="H4">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>-7.631209868481369E-07</v>
+      </c>
+      <c r="E5">
+        <v>20.00000052624197</v>
+      </c>
+      <c r="H5">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>-7.670208042850423E-07</v>
+      </c>
+      <c r="E6">
+        <v>10.0000005340416</v>
+      </c>
+      <c r="H6">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>-7.632746394318579E-07</v>
+      </c>
+      <c r="E7">
+        <v>20.00000052654928</v>
+      </c>
+      <c r="H7">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>-7.665884109900143E-07</v>
+      </c>
+      <c r="E8">
+        <v>10.0000005331768</v>
+      </c>
+      <c r="H8">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>-7.628156862553962E-07</v>
+      </c>
+      <c r="E9">
+        <v>20.00000052563136</v>
+      </c>
+      <c r="H9">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>-7.694650964736404E-07</v>
+      </c>
+      <c r="E10">
+        <v>10.00000053893018</v>
+      </c>
+      <c r="H10">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>-7.658663613856102E-07</v>
+      </c>
+      <c r="E11">
+        <v>20.00000053173272</v>
+      </c>
+      <c r="H11">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>-7.708868500108387E-07</v>
+      </c>
+      <c r="E12">
+        <v>10.00000054177369</v>
+      </c>
+      <c r="H12">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>-7.673725984313552E-07</v>
+      </c>
+      <c r="E13">
+        <v>20.00000053474519</v>
+      </c>
+      <c r="H13">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>-7.697076292242944E-07</v>
+      </c>
+      <c r="E14">
+        <v>10.00000053941525</v>
+      </c>
+      <c r="H14">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>-7.661233716910779E-07</v>
+      </c>
+      <c r="E15">
+        <v>20.00000053224674</v>
+      </c>
+      <c r="H15">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>-7.665884109900143E-07</v>
+      </c>
+      <c r="E16">
+        <v>10.0000005331768</v>
+      </c>
+      <c r="H16">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>-7.62815686255396E-07</v>
+      </c>
+      <c r="E17">
+        <v>20.00000052563136</v>
+      </c>
+      <c r="H17">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>-7.741714835111718E-07</v>
+      </c>
+      <c r="E18">
+        <v>10.00000054834296</v>
+      </c>
+      <c r="H18">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>-7.71130647843275E-07</v>
+      </c>
+      <c r="E19">
+        <v>20.00000054226129</v>
+      </c>
+      <c r="H19">
+        <v>1.107625505137085</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>-7.697076292242946E-07</v>
+      </c>
+      <c r="E20">
+        <v>10.00000053941525</v>
+      </c>
+      <c r="H20">
+        <v>1.485946803066674</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>-7.661233716910781E-07</v>
+      </c>
+      <c r="E21">
+        <v>20.00000053224674</v>
+      </c>
+      <c r="H21">
+        <v>1.107625505137085</v>
       </c>
     </row>
   </sheetData>

--- a/potpourri/results/results_multiperiod.xlsx
+++ b/potpourri/results/results_multiperiod.xlsx
@@ -631,16 +631,16 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>207.4058610632133</v>
+        <v>189.4511305302721</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>248.4</v>
+        <v>200.6</v>
       </c>
       <c r="F2">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>196.1793661384493</v>
+        <v>189.4133918445117</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -660,7 +660,7 @@
         <v>201.6</v>
       </c>
       <c r="F3">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>195.5680723451231</v>
+        <v>190.2826884132005</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -680,7 +680,7 @@
         <v>200</v>
       </c>
       <c r="F4">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>180.5341469665927</v>
+        <v>180.5339835357611</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -700,7 +700,7 @@
         <v>178</v>
       </c>
       <c r="F5">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -708,10 +708,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>82.52677133647713</v>
+        <v>33.5125495394492</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>132</v>
       </c>
       <c r="F6">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -728,10 +728,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C7">
-        <v>15.65655233046931</v>
+        <v>9.16049800305146E-07</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -751,7 +751,7 @@
         <v>200</v>
       </c>
       <c r="C8">
-        <v>2.199101524555801E-06</v>
+        <v>2.32389989617701E-06</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>126.7</v>
       </c>
       <c r="F8">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -768,10 +768,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>2.197500957737473E-06</v>
+        <v>21.77349769156195</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>119.9</v>
       </c>
       <c r="F9">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -788,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>147.7230871469162</v>
+        <v>183.0562869251766</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>213.4</v>
       </c>
       <c r="F10">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>-8.013510093927372E-07</v>
+        <v>58.39591304564379</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>155.1</v>
       </c>
       <c r="F11">
-        <v>23263.82968818684</v>
+        <v>23477.5175338981</v>
       </c>
     </row>
   </sheetData>
@@ -855,10 +855,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>-2.5746087894667E-36</v>
+        <v>9.353667441299527E-29</v>
       </c>
       <c r="D2">
-        <v>1.059999977402385</v>
+        <v>1.059999945233511</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -869,10 +869,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-1.756756111815141</v>
+        <v>-1.073090861161872</v>
       </c>
       <c r="D3">
-        <v>1.051637987576872</v>
+        <v>1.054728924576194</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -883,10 +883,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>-6.953052412095213</v>
+        <v>-5.655925281620772</v>
       </c>
       <c r="D4">
-        <v>1.030560565370533</v>
+        <v>1.034096736338463</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -897,10 +897,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>-2.135828076149457</v>
+        <v>-0.5206295495559683</v>
       </c>
       <c r="D5">
-        <v>1.03314459684351</v>
+        <v>1.044586226688565</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -911,10 +911,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-2.053987795848139</v>
+        <v>-0.7985737235869256</v>
       </c>
       <c r="D6">
-        <v>1.032793013686204</v>
+        <v>1.04017014317395</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -925,10 +925,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-3.900860581672898</v>
+        <v>-2.674221635483804</v>
       </c>
       <c r="D7">
-        <v>1.059999909225559</v>
+        <v>1.059999913120423</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -939,10 +939,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>6.052748836910154</v>
+        <v>6.216243664867309</v>
       </c>
       <c r="D8">
-        <v>1.023828001311311</v>
+        <v>1.047861839296648</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -953,10 +953,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>21.48758570627382</v>
+        <v>19.43055233234666</v>
       </c>
       <c r="D9">
-        <v>1.028025839206722</v>
+        <v>1.059999396584834</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -967,10 +967,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>0.9783902077762437</v>
+        <v>1.570273888300898</v>
       </c>
       <c r="D10">
-        <v>1.036964761713697</v>
+        <v>1.054516400436037</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -981,10 +981,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-0.1719242433078507</v>
+        <v>0.5411657608092303</v>
       </c>
       <c r="D11">
-        <v>1.03385007573658</v>
+        <v>1.048479844606105</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -995,10 +995,10 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>-2.132352777300044</v>
+        <v>-1.161334742218066</v>
       </c>
       <c r="D12">
-        <v>1.043560842419821</v>
+        <v>1.051141065996321</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1009,10 +1009,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>-4.397067052144029</v>
+        <v>-3.194487246830267</v>
       </c>
       <c r="D13">
-        <v>1.043224739668715</v>
+        <v>1.044668090436298</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1023,10 +1023,10 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>-4.065489018427296</v>
+        <v>-2.919735070140004</v>
       </c>
       <c r="D14">
-        <v>1.039318856675635</v>
+        <v>1.041964835239482</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1037,10 +1037,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>-2.250195070899086</v>
+        <v>-1.382349211790727</v>
       </c>
       <c r="D15">
-        <v>1.019087291312775</v>
+        <v>1.030517736642491</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1051,10 +1051,10 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>-2.528680156419962E-36</v>
+        <v>-7.633980640696788E-30</v>
       </c>
       <c r="D16">
-        <v>1.059999954265018</v>
+        <v>1.059999947614415</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1065,10 +1065,10 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>-1.012946806209927</v>
+        <v>-1.099416337542524</v>
       </c>
       <c r="D17">
-        <v>1.055227057781702</v>
+        <v>1.054573484619137</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1079,10 +1079,10 @@
         <v>3</v>
       </c>
       <c r="C18">
-        <v>-5.538209308180948</v>
+        <v>-5.682623113669678</v>
       </c>
       <c r="D18">
-        <v>1.035267889868383</v>
+        <v>1.034056769525899</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1093,10 +1093,10 @@
         <v>4</v>
       </c>
       <c r="C19">
-        <v>-0.3247290264302132</v>
+        <v>-0.5442100244097698</v>
       </c>
       <c r="D19">
-        <v>1.044541610049859</v>
+        <v>1.044519114588771</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1107,10 +1107,10 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-0.6430543657442015</v>
+        <v>-0.8198627538907616</v>
       </c>
       <c r="D20">
-        <v>1.040247112007624</v>
+        <v>1.040107032998973</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1121,10 +1121,10 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-2.447142683652338</v>
+        <v>-2.697448753678253</v>
       </c>
       <c r="D21">
-        <v>1.059999925337427</v>
+        <v>1.05999991582038</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1135,10 +1135,10 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>6.722106426291417</v>
+        <v>6.189947100134093</v>
       </c>
       <c r="D22">
-        <v>1.044612601012299</v>
+        <v>1.047841473450312</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1149,10 +1149,10 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>20.42373482256944</v>
+        <v>19.39961066145804</v>
       </c>
       <c r="D23">
-        <v>1.054958988642089</v>
+        <v>1.05999900259499</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1163,10 +1163,10 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>1.973214837178469</v>
+        <v>1.545046541038563</v>
       </c>
       <c r="D24">
-        <v>1.052433848259713</v>
+        <v>1.05449162614723</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1177,10 +1177,10 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>0.9123669713496072</v>
+        <v>0.516274097939505</v>
       </c>
       <c r="D25">
-        <v>1.046741464859125</v>
+        <v>1.048459297695004</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1191,10 +1191,10 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>-0.8612827628132613</v>
+        <v>-1.185418700172298</v>
       </c>
       <c r="D26">
-        <v>1.050235274382055</v>
+        <v>1.051130593519219</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1205,10 +1205,10 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>-2.95759063224325</v>
+        <v>-3.217877945407405</v>
       </c>
       <c r="D27">
-        <v>1.044470893534513</v>
+        <v>1.04466680398029</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1219,10 +1219,10 @@
         <v>13</v>
       </c>
       <c r="C28">
-        <v>-2.66862160708483</v>
+        <v>-2.943258450929459</v>
       </c>
       <c r="D28">
-        <v>1.041650695134926</v>
+        <v>1.041961130304798</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1233,10 +1233,10 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>-1.049194966628417</v>
+        <v>-1.406886922450674</v>
       </c>
       <c r="D29">
-        <v>1.02913791191462</v>
+        <v>1.030502330957773</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1247,10 +1247,10 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>2.413693506317396E-37</v>
+        <v>1.410174249381131E-30</v>
       </c>
       <c r="D30">
-        <v>1.059999945685425</v>
+        <v>1.059999902720915</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1261,10 +1261,10 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>-0.9343407920666499</v>
+        <v>-0.9936542366123624</v>
       </c>
       <c r="D31">
-        <v>1.055649723868768</v>
+        <v>1.055251236642144</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1275,10 +1275,10 @@
         <v>3</v>
       </c>
       <c r="C32">
-        <v>-4.767570978850526</v>
+        <v>-4.850594110118937</v>
       </c>
       <c r="D32">
-        <v>1.038486405206344</v>
+        <v>1.036743772928347</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1289,10 +1289,10 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>-0.3332415987288415</v>
+        <v>-0.471871806062146</v>
       </c>
       <c r="D33">
-        <v>1.044924039263813</v>
+        <v>1.044651596538348</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1303,10 +1303,10 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-0.7662498563035552</v>
+        <v>-0.8793444295795553</v>
       </c>
       <c r="D34">
-        <v>1.039822786547586</v>
+        <v>1.039575287651346</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1317,10 +1317,10 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-3.311270783405376</v>
+        <v>-3.471644692167528</v>
       </c>
       <c r="D35">
-        <v>1.059999920306542</v>
+        <v>1.059999866111655</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1331,10 +1331,10 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>6.438568028273886</v>
+        <v>6.105995623967869</v>
       </c>
       <c r="D36">
-        <v>1.046393895205502</v>
+        <v>1.048203729519209</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1345,10 +1345,10 @@
         <v>8</v>
       </c>
       <c r="C37">
-        <v>20.03670466961444</v>
+        <v>19.39953484066602</v>
       </c>
       <c r="D37">
-        <v>1.057056122070624</v>
+        <v>1.059999868792108</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1359,10 +1359,10 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>1.599810649744597</v>
+        <v>1.331432158685044</v>
       </c>
       <c r="D38">
-        <v>1.054326821316324</v>
+        <v>1.055443117113545</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1373,10 +1373,10 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>0.4545085797412541</v>
+        <v>0.2055948122959048</v>
       </c>
       <c r="D39">
-        <v>1.048291602298481</v>
+        <v>1.049226506692003</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1387,10 +1387,10 @@
         <v>11</v>
       </c>
       <c r="C40">
-        <v>-1.517382986178612</v>
+        <v>-1.722560310174738</v>
       </c>
       <c r="D40">
-        <v>1.050995532999866</v>
+        <v>1.051486518153401</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1401,10 +1401,10 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>-3.786083453934171</v>
+        <v>-3.952618971567585</v>
       </c>
       <c r="D41">
-        <v>1.044477869838827</v>
+        <v>1.044588175380582</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1415,10 +1415,10 @@
         <v>13</v>
       </c>
       <c r="C42">
-        <v>-3.461986816912542</v>
+        <v>-3.637142333291166</v>
       </c>
       <c r="D42">
-        <v>1.041923734361161</v>
+        <v>1.042094457209353</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1429,10 +1429,10 @@
         <v>14</v>
       </c>
       <c r="C43">
-        <v>-1.600653714225206</v>
+        <v>-1.826426008400894</v>
       </c>
       <c r="D43">
-        <v>1.030217233077868</v>
+        <v>1.030964540549865</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1443,10 +1443,10 @@
         <v>1</v>
       </c>
       <c r="C44">
-        <v>-2.182061507098107E-34</v>
+        <v>-1.364503233628171E-30</v>
       </c>
       <c r="D44">
-        <v>1.05444177958309</v>
+        <v>1.054441773638887</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1457,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>-0.3818112869620244</v>
+        <v>-0.3818122958557532</v>
       </c>
       <c r="D45">
-        <v>1.051824155429126</v>
+        <v>1.051824144419312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1471,10 +1471,10 @@
         <v>3</v>
       </c>
       <c r="C46">
-        <v>-2.626004751966819</v>
+        <v>-2.626007576640734</v>
       </c>
       <c r="D46">
-        <v>1.039389204827813</v>
+        <v>1.039389186386376</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1485,10 +1485,10 @@
         <v>4</v>
       </c>
       <c r="C47">
-        <v>0.256892885152373</v>
+        <v>0.2568883216667648</v>
       </c>
       <c r="D47">
-        <v>1.043201761954184</v>
+        <v>1.043201746247886</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1499,10 +1499,10 @@
         <v>5</v>
       </c>
       <c r="C48">
-        <v>-0.3073520397327147</v>
+        <v>-0.3073557275199588</v>
       </c>
       <c r="D48">
-        <v>1.037224310150917</v>
+        <v>1.037224296870246</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1513,10 +1513,10 @@
         <v>6</v>
       </c>
       <c r="C49">
-        <v>-3.167088022450223</v>
+        <v>-3.167094122817008</v>
       </c>
       <c r="D49">
-        <v>1.059999456110016</v>
+        <v>1.059999456109829</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1527,10 +1527,10 @@
         <v>7</v>
       </c>
       <c r="C50">
-        <v>6.170400612308815</v>
+        <v>6.170388278058143</v>
       </c>
       <c r="D50">
-        <v>1.050377846187323</v>
+        <v>1.050377862840677</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1541,10 +1541,10 @@
         <v>8</v>
       </c>
       <c r="C51">
-        <v>18.68349951533905</v>
+        <v>18.68347652551706</v>
       </c>
       <c r="D51">
-        <v>1.059999931437076</v>
+        <v>1.05999993143697</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1555,10 +1555,10 @@
         <v>9</v>
       </c>
       <c r="C52">
-        <v>1.811387086086294</v>
+        <v>1.811377143708406</v>
       </c>
       <c r="D52">
-        <v>1.057568655153921</v>
+        <v>1.057568661519558</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1569,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="C53">
-        <v>0.9787316127833009</v>
+        <v>0.9787223383511024</v>
       </c>
       <c r="D53">
-        <v>1.053323338541726</v>
+        <v>1.053323344072127</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1583,10 +1583,10 @@
         <v>11</v>
       </c>
       <c r="C54">
-        <v>-1.176370495100399</v>
+        <v>-1.176378217066954</v>
       </c>
       <c r="D54">
-        <v>1.053539145293787</v>
+        <v>1.053539148590661</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1597,10 +1597,10 @@
         <v>12</v>
       </c>
       <c r="C55">
-        <v>-3.633693076633338</v>
+        <v>-3.633699433424662</v>
       </c>
       <c r="D55">
-        <v>1.044694519786044</v>
+        <v>1.044694521301163</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1611,10 +1611,10 @@
         <v>13</v>
       </c>
       <c r="C56">
-        <v>-3.30643546201958</v>
+        <v>-3.306442107118962</v>
       </c>
       <c r="D56">
-        <v>1.042407439962907</v>
+        <v>1.042407441053743</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1625,10 +1625,10 @@
         <v>14</v>
       </c>
       <c r="C57">
-        <v>-1.406690343096788</v>
+        <v>-1.406698847391102</v>
       </c>
       <c r="D57">
-        <v>1.032276395727385</v>
+        <v>1.032276400960185</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1639,10 +1639,10 @@
         <v>1</v>
       </c>
       <c r="C58">
-        <v>4.672726366401778E-36</v>
+        <v>2.848356717962129E-32</v>
       </c>
       <c r="D58">
-        <v>1.012771453231648</v>
+        <v>1.01296048637752</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1653,10 +1653,10 @@
         <v>2</v>
       </c>
       <c r="C59">
-        <v>-0.04651317455994464</v>
+        <v>0.1846634181322708</v>
       </c>
       <c r="D59">
-        <v>1.011099681153593</v>
+        <v>1.012340099065699</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1667,10 +1667,10 @@
         <v>3</v>
       </c>
       <c r="C60">
-        <v>0.2676593662479231</v>
+        <v>0.8580094634341808</v>
       </c>
       <c r="D60">
-        <v>1.012586766119317</v>
+        <v>1.015529963195118</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1681,10 +1681,10 @@
         <v>4</v>
       </c>
       <c r="C61">
-        <v>0.569203206027143</v>
+        <v>1.427864726486695</v>
       </c>
       <c r="D61">
-        <v>1.013198898827843</v>
+        <v>1.02019187511303</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1695,10 +1695,10 @@
         <v>5</v>
       </c>
       <c r="C62">
-        <v>0.6506876948752882</v>
+        <v>0.6746279624104755</v>
       </c>
       <c r="D62">
-        <v>1.008470413656406</v>
+        <v>1.00981722914824</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1709,10 +1709,10 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>-3.150588043017723</v>
+        <v>-1.570739904748325</v>
       </c>
       <c r="D63">
-        <v>1.041507700712564</v>
+        <v>1.035064219311698</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1723,10 +1723,10 @@
         <v>7</v>
       </c>
       <c r="C64">
-        <v>1.991569969249031</v>
+        <v>2.04220555498679</v>
       </c>
       <c r="D64">
-        <v>1.044371839636296</v>
+        <v>1.041554856816411</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1737,10 +1737,10 @@
         <v>8</v>
       </c>
       <c r="C65">
-        <v>7.634530197963833</v>
+        <v>4.042490283381716</v>
       </c>
       <c r="D65">
-        <v>1.0599996369235</v>
+        <v>1.030668133187734</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1751,10 +1751,10 @@
         <v>9</v>
       </c>
       <c r="C66">
-        <v>-0.5515773215556709</v>
+        <v>1.424277969584095</v>
       </c>
       <c r="D66">
-        <v>1.043424563297825</v>
+        <v>1.048004200997847</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1765,10 +1765,10 @@
         <v>10</v>
       </c>
       <c r="C67">
-        <v>-0.9707330314397609</v>
+        <v>2.591701064989038</v>
       </c>
       <c r="D67">
-        <v>1.038367779106676</v>
+        <v>1.059999855955731</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1779,10 +1779,10 @@
         <v>11</v>
       </c>
       <c r="C68">
-        <v>-2.170734928021373</v>
+        <v>0.4395273909705954</v>
       </c>
       <c r="D68">
-        <v>1.036930638741953</v>
+        <v>1.044805767057855</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1793,10 +1793,10 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>-3.169015157370253</v>
+        <v>-1.554780908062656</v>
       </c>
       <c r="D69">
-        <v>1.033227285724682</v>
+        <v>1.027433751241404</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1807,10 +1807,10 @@
         <v>13</v>
       </c>
       <c r="C70">
-        <v>-3.194784764199293</v>
+        <v>-1.562268476005292</v>
       </c>
       <c r="D70">
-        <v>1.028141851024913</v>
+        <v>1.023244565744333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1821,10 +1821,10 @@
         <v>14</v>
       </c>
       <c r="C71">
-        <v>-1.500089284102657</v>
+        <v>0.331944230490184</v>
       </c>
       <c r="D71">
-        <v>1.029305101179637</v>
+        <v>1.029714587289954</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1835,10 +1835,10 @@
         <v>1</v>
       </c>
       <c r="C72">
-        <v>-1.829724604588518E-30</v>
+        <v>3.745392469436971E-27</v>
       </c>
       <c r="D72">
-        <v>1.022053994035914</v>
+        <v>0.9730491404331554</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1849,10 +1849,10 @@
         <v>2</v>
       </c>
       <c r="C73">
-        <v>0.04754337349217052</v>
+        <v>1.991453589632473</v>
       </c>
       <c r="D73">
-        <v>1.02104681077566</v>
+        <v>0.9822795816753113</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1863,10 +1863,10 @@
         <v>3</v>
       </c>
       <c r="C74">
-        <v>0.5278857797440862</v>
+        <v>4.439639328358334</v>
       </c>
       <c r="D74">
-        <v>1.022930910852473</v>
+        <v>0.9910904025137659</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1877,10 +1877,10 @@
         <v>4</v>
       </c>
       <c r="C75">
-        <v>0.9876337774112298</v>
+        <v>6.491361070223722</v>
       </c>
       <c r="D75">
-        <v>1.02370655578642</v>
+        <v>1.006355445444564</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1891,10 +1891,10 @@
         <v>5</v>
       </c>
       <c r="C76">
-        <v>1.743737722436096</v>
+        <v>4.980879036270395</v>
       </c>
       <c r="D76">
-        <v>1.022384289338344</v>
+        <v>0.9884586971831447</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1905,10 +1905,10 @@
         <v>6</v>
       </c>
       <c r="C77">
-        <v>-2.127643633235792</v>
+        <v>5.858394730082217</v>
       </c>
       <c r="D77">
-        <v>1.059948523339812</v>
+        <v>0.9957836400888085</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1919,10 +1919,10 @@
         <v>7</v>
       </c>
       <c r="C78">
-        <v>-0.1364882991865325</v>
+        <v>8.763702621228065</v>
       </c>
       <c r="D78">
-        <v>1.054539235138208</v>
+        <v>1.027172231238604</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1933,10 +1933,10 @@
         <v>8</v>
       </c>
       <c r="C79">
-        <v>-0.2341240828711052</v>
+        <v>7.797163119472754</v>
       </c>
       <c r="D79">
-        <v>1.059999670306245</v>
+        <v>1.016630140727665</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1947,10 +1947,10 @@
         <v>9</v>
       </c>
       <c r="C80">
-        <v>-0.3785545867706481</v>
+        <v>10.84364957476847</v>
       </c>
       <c r="D80">
-        <v>1.055351071842481</v>
+        <v>1.033995270692904</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="C81">
-        <v>-0.5861890012805271</v>
+        <v>13.45777966780002</v>
       </c>
       <c r="D81">
-        <v>1.05194407827636</v>
+        <v>1.059999938686775</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1975,10 +1975,10 @@
         <v>11</v>
       </c>
       <c r="C82">
-        <v>-1.293675686277728</v>
+        <v>9.884775043548968</v>
       </c>
       <c r="D82">
-        <v>1.054370407692111</v>
+        <v>1.026207366498882</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1989,10 +1989,10 @@
         <v>12</v>
       </c>
       <c r="C83">
-        <v>-1.873914023497671</v>
+        <v>6.394543229446477</v>
       </c>
       <c r="D83">
-        <v>1.053448115572857</v>
+        <v>0.9911537046788991</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2003,10 +2003,10 @@
         <v>13</v>
       </c>
       <c r="C84">
-        <v>-1.668004668031529</v>
+        <v>6.816010295429028</v>
       </c>
       <c r="D84">
-        <v>1.052044604050084</v>
+        <v>0.9936453440624728</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2017,10 +2017,10 @@
         <v>14</v>
       </c>
       <c r="C85">
-        <v>-0.7501005313060695</v>
+        <v>9.324460831239559</v>
       </c>
       <c r="D85">
-        <v>1.04667078514461</v>
+        <v>1.008568908004513</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2031,10 +2031,10 @@
         <v>1</v>
       </c>
       <c r="C86">
-        <v>1.747160154936632E-29</v>
+        <v>7.080761161571807E-29</v>
       </c>
       <c r="D86">
-        <v>1.019923696902684</v>
+        <v>0.9755329395597315</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2045,10 +2045,10 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>1.601012667129228</v>
+        <v>1.968818498706403</v>
       </c>
       <c r="D87">
-        <v>1.026534476916964</v>
+        <v>0.9849469541043651</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2059,10 +2059,10 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>2.810783731596706</v>
+        <v>4.124049812479955</v>
       </c>
       <c r="D88">
-        <v>1.028999042523854</v>
+        <v>0.9928636498196763</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2073,10 +2073,10 @@
         <v>4</v>
       </c>
       <c r="C89">
-        <v>4.04238515342838</v>
+        <v>5.927682619717245</v>
       </c>
       <c r="D89">
-        <v>1.026640146378639</v>
+        <v>1.006610163426724</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2087,10 +2087,10 @@
         <v>5</v>
       </c>
       <c r="C90">
-        <v>5.454432028863413</v>
+        <v>4.24156059912796</v>
       </c>
       <c r="D90">
-        <v>1.025675528530089</v>
+        <v>0.9878332198571637</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2101,10 +2101,10 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>1.210277997878342</v>
+        <v>5.176353428812511</v>
       </c>
       <c r="D91">
-        <v>1.059999804211918</v>
+        <v>0.995119872521511</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2115,10 +2115,10 @@
         <v>7</v>
       </c>
       <c r="C92">
-        <v>2.40704082121313</v>
+        <v>8.166871214483258</v>
       </c>
       <c r="D92">
-        <v>1.055101255849039</v>
+        <v>1.027372960235724</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2129,10 +2129,10 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>1.504590404710989</v>
+        <v>7.200713426679827</v>
       </c>
       <c r="D93">
-        <v>1.05999962449828</v>
+        <v>1.016833009709945</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2143,10 +2143,10 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>2.400535058288946</v>
+        <v>10.22929883298679</v>
       </c>
       <c r="D94">
-        <v>1.055172494880398</v>
+        <v>1.03413963724751</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2157,10 +2157,10 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>2.290325072753042</v>
+        <v>12.83219624357798</v>
       </c>
       <c r="D95">
-        <v>1.051745028398593</v>
+        <v>1.059999950470926</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2171,10 +2171,10 @@
         <v>11</v>
       </c>
       <c r="C96">
-        <v>1.808293920410259</v>
+        <v>9.233510067859365</v>
       </c>
       <c r="D96">
-        <v>1.054252776515495</v>
+        <v>1.025861084905779</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2185,10 +2185,10 @@
         <v>12</v>
       </c>
       <c r="C97">
-        <v>1.424622989875049</v>
+        <v>5.718350959818308</v>
       </c>
       <c r="D97">
-        <v>1.053613924056427</v>
+        <v>0.9905239175363135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2199,10 +2199,10 @@
         <v>13</v>
       </c>
       <c r="C98">
-        <v>1.589597912357529</v>
+        <v>6.144472180942999</v>
       </c>
       <c r="D98">
-        <v>1.052027021263115</v>
+        <v>0.9930899437282936</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2213,10 +2213,10 @@
         <v>14</v>
       </c>
       <c r="C99">
-        <v>2.236916133412968</v>
+        <v>8.686383535410339</v>
       </c>
       <c r="D99">
-        <v>1.046564215791637</v>
+        <v>1.008394193744242</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2227,10 +2227,10 @@
         <v>1</v>
       </c>
       <c r="C100">
-        <v>2.72652258153329E-30</v>
+        <v>-4.206970058293562E-33</v>
       </c>
       <c r="D100">
-        <v>1.018207445722267</v>
+        <v>1.013255472084818</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2241,10 +2241,10 @@
         <v>2</v>
       </c>
       <c r="C101">
-        <v>1.888355365035845</v>
+        <v>0.3793320249602455</v>
       </c>
       <c r="D101">
-        <v>1.026496326557824</v>
+        <v>1.013893559795799</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2255,10 +2255,10 @@
         <v>3</v>
       </c>
       <c r="C102">
-        <v>2.82748627411218</v>
+        <v>0.8031523174833243</v>
       </c>
       <c r="D102">
-        <v>1.027784792275845</v>
+        <v>1.01606087472749</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2269,10 +2269,10 @@
         <v>4</v>
       </c>
       <c r="C103">
-        <v>3.813826168496116</v>
+        <v>1.156420949911797</v>
       </c>
       <c r="D103">
-        <v>1.024260609804342</v>
+        <v>1.019351623364733</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2283,10 +2283,10 @@
         <v>5</v>
       </c>
       <c r="C104">
-        <v>5.24467439630236</v>
+        <v>0.2248180391273708</v>
       </c>
       <c r="D104">
-        <v>1.023496334217833</v>
+        <v>1.007721795650203</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2297,10 +2297,10 @@
         <v>6</v>
       </c>
       <c r="C105">
-        <v>0.1834670806137526</v>
+        <v>-1.760568571357646</v>
       </c>
       <c r="D105">
-        <v>1.059999793911917</v>
+        <v>1.031158921880084</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2311,10 +2311,10 @@
         <v>7</v>
       </c>
       <c r="C106">
-        <v>1.581976051954408</v>
+        <v>1.557248020533599</v>
       </c>
       <c r="D106">
-        <v>1.053490808618841</v>
+        <v>1.041943898162923</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2325,10 +2325,10 @@
         <v>8</v>
       </c>
       <c r="C107">
-        <v>0.6781459737253367</v>
+        <v>1.778184995619351</v>
       </c>
       <c r="D107">
-        <v>1.059999633071379</v>
+        <v>1.031693525770276</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2339,10 +2339,10 @@
         <v>9</v>
       </c>
       <c r="C108">
-        <v>1.266881590420546</v>
+        <v>1.919668276770202</v>
       </c>
       <c r="D108">
-        <v>1.053198209856206</v>
+        <v>1.048206915102553</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2353,10 +2353,10 @@
         <v>10</v>
       </c>
       <c r="C109">
-        <v>1.176278567890211</v>
+        <v>3.034062984194918</v>
       </c>
       <c r="D109">
-        <v>1.05009388122373</v>
+        <v>1.059999885835449</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2367,10 +2367,10 @@
         <v>11</v>
       </c>
       <c r="C110">
-        <v>0.7374783582829201</v>
+        <v>0.7594835626846973</v>
       </c>
       <c r="D110">
-        <v>1.0533939746426</v>
+        <v>1.044281073828475</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2381,10 +2381,10 @@
         <v>12</v>
       </c>
       <c r="C111">
-        <v>0.2299385684058161</v>
+        <v>-1.513801586727128</v>
       </c>
       <c r="D111">
-        <v>1.052576037424881</v>
+        <v>1.024710489127146</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2395,10 +2395,10 @@
         <v>13</v>
       </c>
       <c r="C112">
-        <v>0.2529799068268976</v>
+        <v>-1.322277613009768</v>
       </c>
       <c r="D112">
-        <v>1.048740432812011</v>
+        <v>1.023340483679353</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2409,10 +2409,10 @@
         <v>14</v>
       </c>
       <c r="C113">
-        <v>-0.178037581310469</v>
+        <v>-0.5095186567644283</v>
       </c>
       <c r="D113">
-        <v>1.033254145420944</v>
+        <v>1.018923909665208</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2423,10 +2423,10 @@
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2.917975496903385E-37</v>
+        <v>1.097235820060879E-26</v>
       </c>
       <c r="D114">
-        <v>1.038944026759525</v>
+        <v>1.052734462456492</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2437,10 +2437,10 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>-0.9637077478877984</v>
+        <v>-1.239683583672878</v>
       </c>
       <c r="D115">
-        <v>1.032987336773463</v>
+        <v>1.045147787141732</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2451,10 +2451,10 @@
         <v>3</v>
       </c>
       <c r="C116">
-        <v>-0.1654051925495017</v>
+        <v>-0.5971305395684557</v>
       </c>
       <c r="D116">
-        <v>1.036275920504583</v>
+        <v>1.047499548680382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2465,10 +2465,10 @@
         <v>4</v>
       </c>
       <c r="C117">
-        <v>0.6893825725524317</v>
+        <v>0.1902475115937355</v>
       </c>
       <c r="D117">
-        <v>1.033624997742598</v>
+        <v>1.04069979188375</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2479,10 +2479,10 @@
         <v>5</v>
       </c>
       <c r="C118">
-        <v>0.2238110193762154</v>
+        <v>-0.8732029972365768</v>
       </c>
       <c r="D118">
-        <v>1.02607047693235</v>
+        <v>1.031517704609757</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2493,10 +2493,10 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>-3.915948971500738</v>
+        <v>-4.275153437830669</v>
       </c>
       <c r="D119">
-        <v>1.053574651973236</v>
+        <v>1.051137627953441</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2507,10 +2507,10 @@
         <v>7</v>
       </c>
       <c r="C120">
-        <v>5.211617932407452</v>
+        <v>6.537846163627736</v>
       </c>
       <c r="D120">
-        <v>1.053938044176618</v>
+        <v>1.052111865747944</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2521,10 +2521,10 @@
         <v>8</v>
       </c>
       <c r="C121">
-        <v>14.25738846358086</v>
+        <v>18.17635811615802</v>
       </c>
       <c r="D121">
-        <v>1.059999887126614</v>
+        <v>1.059999917437936</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2535,10 +2535,10 @@
         <v>9</v>
       </c>
       <c r="C122">
-        <v>2.236016582885033</v>
+        <v>2.944750918253191</v>
       </c>
       <c r="D122">
-        <v>1.059999831348225</v>
+        <v>1.059999893929332</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2549,10 +2549,10 @@
         <v>10</v>
       </c>
       <c r="C123">
-        <v>1.264672186028088</v>
+        <v>1.790367334958524</v>
       </c>
       <c r="D123">
-        <v>1.054650754516041</v>
+        <v>1.054081134263481</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2563,10 +2563,10 @@
         <v>11</v>
       </c>
       <c r="C124">
-        <v>-1.214170135812345</v>
+        <v>-1.117019704604414</v>
       </c>
       <c r="D124">
-        <v>1.05237320050748</v>
+        <v>1.050663526142069</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2577,10 +2577,10 @@
         <v>12</v>
       </c>
       <c r="C125">
-        <v>-3.840751727213133</v>
+        <v>-4.125194398558992</v>
       </c>
       <c r="D125">
-        <v>1.043870237243342</v>
+        <v>1.04126142207212</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2591,10 +2591,10 @@
         <v>13</v>
       </c>
       <c r="C126">
-        <v>-3.741046174940304</v>
+        <v>-3.948469859656007</v>
       </c>
       <c r="D126">
-        <v>1.038052802725435</v>
+        <v>1.035833393193325</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2605,10 +2605,10 @@
         <v>14</v>
       </c>
       <c r="C127">
-        <v>-1.346536247923766</v>
+        <v>-1.031221426773906</v>
       </c>
       <c r="D127">
-        <v>1.031432430131329</v>
+        <v>1.030051636370388</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2619,10 +2619,10 @@
         <v>1</v>
       </c>
       <c r="C128">
-        <v>-2.025923354217084E-29</v>
+        <v>2.060559138375921E-34</v>
       </c>
       <c r="D128">
-        <v>1.057513361496015</v>
+        <v>1.049163554873946</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2633,10 +2633,10 @@
         <v>2</v>
       </c>
       <c r="C129">
-        <v>-0.1638963537208358</v>
+        <v>-0.8782077416120294</v>
       </c>
       <c r="D129">
-        <v>1.056862956213592</v>
+        <v>1.04414035400976</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2647,10 +2647,10 @@
         <v>3</v>
       </c>
       <c r="C130">
-        <v>-1.781622285700216</v>
+        <v>-1.620952588057022</v>
       </c>
       <c r="D130">
-        <v>1.048615758260302</v>
+        <v>1.040490523567518</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2661,10 +2661,10 @@
         <v>4</v>
       </c>
       <c r="C131">
-        <v>-3.105410092411791</v>
+        <v>-2.188861356162009</v>
       </c>
       <c r="D131">
-        <v>1.033519760633793</v>
+        <v>1.032023062896725</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2675,10 +2675,10 @@
         <v>5</v>
       </c>
       <c r="C132">
-        <v>-3.346897726984062</v>
+        <v>-2.706350237168221</v>
       </c>
       <c r="D132">
-        <v>1.02751791699073</v>
+        <v>1.024224607882628</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2689,10 +2689,10 @@
         <v>6</v>
       </c>
       <c r="C133">
-        <v>-9.548445398649244</v>
+        <v>-7.856711204505525</v>
       </c>
       <c r="D133">
-        <v>1.055304562086444</v>
+        <v>1.050403447558779</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2703,10 +2703,10 @@
         <v>7</v>
       </c>
       <c r="C134">
-        <v>-5.501349192840627</v>
+        <v>-1.312045633997788</v>
       </c>
       <c r="D134">
-        <v>1.058909152018111</v>
+        <v>1.057643206087024</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2717,10 +2717,10 @@
         <v>8</v>
       </c>
       <c r="C135">
-        <v>-5.501349186166262</v>
+        <v>3.00801987156357</v>
       </c>
       <c r="D135">
-        <v>1.059990572018907</v>
+        <v>1.059999609635234</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2731,10 +2731,10 @@
         <v>9</v>
       </c>
       <c r="C136">
-        <v>-6.476823773047735</v>
+        <v>-3.267574488792933</v>
       </c>
       <c r="D136">
-        <v>1.059999417193116</v>
+        <v>1.059999883291434</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2745,10 +2745,10 @@
         <v>10</v>
       </c>
       <c r="C137">
-        <v>-6.916159774618095</v>
+        <v>-3.968601267395318</v>
       </c>
       <c r="D137">
-        <v>1.055072716064106</v>
+        <v>1.054212187449124</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2759,10 +2759,10 @@
         <v>11</v>
       </c>
       <c r="C138">
-        <v>-8.155962738043746</v>
+        <v>-5.817825452665319</v>
       </c>
       <c r="D138">
-        <v>1.053743140181608</v>
+        <v>1.050824326291503</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2773,10 +2773,10 @@
         <v>12</v>
       </c>
       <c r="C139">
-        <v>-9.687595098978733</v>
+        <v>-7.88868303139449</v>
       </c>
       <c r="D139">
-        <v>1.046304803137355</v>
+        <v>1.041344197381526</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2787,10 +2787,10 @@
         <v>13</v>
       </c>
       <c r="C140">
-        <v>-9.814410094572553</v>
+        <v>-7.909214554293264</v>
       </c>
       <c r="D140">
-        <v>1.039603281107338</v>
+        <v>1.035378111067584</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2801,10 +2801,10 @@
         <v>14</v>
       </c>
       <c r="C141">
-        <v>-8.922475171115014</v>
+        <v>-6.275005953179493</v>
       </c>
       <c r="D141">
-        <v>1.032894193560106</v>
+        <v>1.03070971137625</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="D10">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>-3.9</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>40.457</v>
+        <v>38.149</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>7.925</v>
+        <v>7.159</v>
       </c>
       <c r="G3">
         <v>140</v>
@@ -5731,7 +5731,7 @@
         <v>-40</v>
       </c>
       <c r="I3">
-        <v>27.707</v>
+        <v>24.141</v>
       </c>
       <c r="J3">
         <v>50</v>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>37.192</v>
+        <v>33.231</v>
       </c>
       <c r="J4">
         <v>40</v>
@@ -5789,7 +5789,7 @@
         <v>-6</v>
       </c>
       <c r="I5">
-        <v>18.115</v>
+        <v>7.774</v>
       </c>
       <c r="J5">
         <v>24</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>159.024</v>
+        <v>144.142</v>
       </c>
       <c r="G6">
         <v>300</v>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>40.457</v>
+        <v>38.149</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>7.535</v>
+        <v>7.174</v>
       </c>
       <c r="G8">
         <v>140</v>
@@ -5876,7 +5876,7 @@
         <v>-40</v>
       </c>
       <c r="I8">
-        <v>25.353</v>
+        <v>24.031</v>
       </c>
       <c r="J8">
         <v>50</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>34.413</v>
+        <v>33.315</v>
       </c>
       <c r="J9">
         <v>40</v>
@@ -5934,7 +5934,7 @@
         <v>-6</v>
       </c>
       <c r="I10">
-        <v>8.842000000000001</v>
+        <v>7.805</v>
       </c>
       <c r="J10">
         <v>24</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>148.187</v>
+        <v>144.09</v>
       </c>
       <c r="G11">
         <v>300</v>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>40.457</v>
+        <v>38.149</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -5992,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>7.478</v>
+        <v>7.095</v>
       </c>
       <c r="G13">
         <v>140</v>
@@ -6021,7 +6021,7 @@
         <v>-40</v>
       </c>
       <c r="I13">
-        <v>24.356</v>
+        <v>24.382</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>31.836</v>
+        <v>30.189</v>
       </c>
       <c r="J14">
         <v>40</v>
@@ -6079,7 +6079,7 @@
         <v>-6</v>
       </c>
       <c r="I15">
-        <v>10.122</v>
+        <v>9.606</v>
       </c>
       <c r="J15">
         <v>24</v>
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>147.633</v>
+        <v>145.039</v>
       </c>
       <c r="G16">
         <v>300</v>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>17.657</v>
+        <v>10.506</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>3.074</v>
+        <v>1.735</v>
       </c>
       <c r="G23">
         <v>140</v>
@@ -6311,7 +6311,7 @@
         <v>-40</v>
       </c>
       <c r="I23">
-        <v>6.349</v>
+        <v>4.162</v>
       </c>
       <c r="J23">
         <v>50</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>16.954</v>
+        <v>15.966</v>
       </c>
       <c r="J24">
         <v>40</v>
@@ -6369,7 +6369,7 @@
         <v>-6</v>
       </c>
       <c r="I25">
-        <v>8.282</v>
+        <v>1.58</v>
       </c>
       <c r="J25">
         <v>24</v>
@@ -6389,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>61.796</v>
+        <v>21.272</v>
       </c>
       <c r="G26">
         <v>300</v>
@@ -6398,7 +6398,7 @@
         <v>-6</v>
       </c>
       <c r="I26">
-        <v>12.45</v>
+        <v>-5.999</v>
       </c>
       <c r="J26">
         <v>24</v>
@@ -6418,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>5.742</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -6427,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.001</v>
+        <v>2.703</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0.996</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>140</v>
@@ -6456,7 +6456,7 @@
         <v>-40</v>
       </c>
       <c r="I28">
-        <v>8.537000000000001</v>
+        <v>12.536</v>
       </c>
       <c r="J28">
         <v>50</v>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>17.268</v>
+        <v>15.848</v>
       </c>
       <c r="J29">
         <v>40</v>
@@ -6514,7 +6514,7 @@
         <v>-6</v>
       </c>
       <c r="I30">
-        <v>9.481</v>
+        <v>-6</v>
       </c>
       <c r="J30">
         <v>24</v>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>8.919</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -6543,7 +6543,7 @@
         <v>-6</v>
       </c>
       <c r="I31">
-        <v>3.287</v>
+        <v>-6</v>
       </c>
       <c r="J31">
         <v>24</v>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>9.374000000000001</v>
+        <v>1.846</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -6601,7 +6601,7 @@
         <v>-40</v>
       </c>
       <c r="I33">
-        <v>23.522</v>
+        <v>11.299</v>
       </c>
       <c r="J33">
         <v>50</v>
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>20.661</v>
+        <v>15.705</v>
       </c>
       <c r="J34">
         <v>40</v>
@@ -6659,7 +6659,7 @@
         <v>-6</v>
       </c>
       <c r="I35">
-        <v>6.78</v>
+        <v>-6</v>
       </c>
       <c r="J35">
         <v>24</v>
@@ -6688,7 +6688,7 @@
         <v>-6</v>
       </c>
       <c r="I36">
-        <v>3.026</v>
+        <v>-6</v>
       </c>
       <c r="J36">
         <v>24</v>
@@ -6708,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8.186</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>9.255000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="J37">
         <v>10</v>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1.234</v>
       </c>
       <c r="G38">
         <v>140</v>
@@ -6746,7 +6746,7 @@
         <v>-40</v>
       </c>
       <c r="I38">
-        <v>22.463</v>
+        <v>4.022</v>
       </c>
       <c r="J38">
         <v>50</v>
@@ -6775,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>20.263</v>
+        <v>15.863</v>
       </c>
       <c r="J39">
         <v>40</v>
@@ -6804,7 +6804,7 @@
         <v>-6</v>
       </c>
       <c r="I40">
-        <v>8.584</v>
+        <v>1.665</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>12.353</v>
       </c>
       <c r="G41">
         <v>300</v>
@@ -6833,7 +6833,7 @@
         <v>-6</v>
       </c>
       <c r="I41">
-        <v>3.996</v>
+        <v>-5.999</v>
       </c>
       <c r="J41">
         <v>24</v>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>32.014</v>
+        <v>38.149</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>1.244</v>
+        <v>2.846</v>
       </c>
       <c r="J42">
         <v>10</v>
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>5.995</v>
+        <v>7.184</v>
       </c>
       <c r="G43">
         <v>140</v>
@@ -6891,7 +6891,7 @@
         <v>-40</v>
       </c>
       <c r="I43">
-        <v>16.518</v>
+        <v>19.83</v>
       </c>
       <c r="J43">
         <v>50</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>20.574</v>
+        <v>22.35</v>
       </c>
       <c r="J44">
         <v>40</v>
@@ -6949,7 +6949,7 @@
         <v>-6</v>
       </c>
       <c r="I45">
-        <v>14.628</v>
+        <v>13.38</v>
       </c>
       <c r="J45">
         <v>24</v>
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>109.714</v>
+        <v>137.723</v>
       </c>
       <c r="G46">
         <v>300</v>
@@ -6978,7 +6978,7 @@
         <v>-6</v>
       </c>
       <c r="I46">
-        <v>11.536</v>
+        <v>17.764</v>
       </c>
       <c r="J46">
         <v>24</v>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>8.621</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>1.465</v>
+        <v>0.616</v>
       </c>
       <c r="J47">
         <v>10</v>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="G48">
         <v>140</v>
@@ -7036,7 +7036,7 @@
         <v>-40</v>
       </c>
       <c r="I48">
-        <v>15.486</v>
+        <v>12.288</v>
       </c>
       <c r="J48">
         <v>50</v>
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>18.713</v>
+        <v>18.141</v>
       </c>
       <c r="J49">
         <v>40</v>
@@ -7094,7 +7094,7 @@
         <v>-6</v>
       </c>
       <c r="I50">
-        <v>7.686</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="J50">
         <v>24</v>
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>47.942</v>
       </c>
       <c r="G51">
         <v>300</v>
@@ -7123,7 +7123,7 @@
         <v>-6</v>
       </c>
       <c r="I51">
-        <v>0.651</v>
+        <v>3.226</v>
       </c>
       <c r="J51">
         <v>24</v>
@@ -7218,13 +7218,13 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>-56.29392567959094</v>
+        <v>-34.63909245132641</v>
       </c>
       <c r="F2">
-        <v>56.85273514594169</v>
+        <v>34.84902710744248</v>
       </c>
       <c r="G2">
-        <v>0.5588094663507515</v>
+        <v>0.2099346561160786</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -7241,13 +7241,13 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>-19.42754377340933</v>
+        <v>-8.612958582220037</v>
       </c>
       <c r="F3">
-        <v>19.64780281260282</v>
+        <v>8.675272159124582</v>
       </c>
       <c r="G3">
-        <v>0.2202590391934905</v>
+        <v>0.06231357690454631</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7264,13 +7264,13 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>-48.89661049603261</v>
+        <v>-43.69815358469152</v>
       </c>
       <c r="F4">
-        <v>49.95812000852314</v>
+        <v>44.53805341812473</v>
       </c>
       <c r="G4">
-        <v>1.061509512490533</v>
+        <v>0.8398998334332164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>-6.89477721885665</v>
+        <v>3.656982391172132</v>
       </c>
       <c r="F5">
-        <v>6.960458921583534</v>
+        <v>-3.622366881648289</v>
       </c>
       <c r="G5">
-        <v>0.06568170272688439</v>
+        <v>0.03461550952384221</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7310,13 +7310,13 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>-6.234917345408272</v>
+        <v>0.1561511951900806</v>
       </c>
       <c r="F6">
-        <v>6.300302806356783</v>
+        <v>-0.1158098774204474</v>
       </c>
       <c r="G6">
-        <v>0.06538546094851175</v>
+        <v>0.04034131776963323</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7333,13 +7333,13 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>46.59854634960203</v>
+        <v>52.0458619149715</v>
       </c>
       <c r="F7">
-        <v>-45.10339020923671</v>
+        <v>-50.30184716373943</v>
       </c>
       <c r="G7">
-        <v>1.495156140365328</v>
+        <v>1.74401475123207</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -7356,13 +7356,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>3.041167286723529</v>
+        <v>-14.50740879529521</v>
       </c>
       <c r="F8">
-        <v>-3.03959342675339</v>
+        <v>14.53824179792461</v>
       </c>
       <c r="G8">
-        <v>0.001573859970139049</v>
+        <v>0.03083300262940181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7379,13 +7379,13 @@
         <v>11</v>
       </c>
       <c r="E9">
-        <v>10.72550674584509</v>
+        <v>10.29901943994609</v>
       </c>
       <c r="F9">
-        <v>-10.46665275175737</v>
+        <v>-10.1318099051609</v>
       </c>
       <c r="G9">
-        <v>0.258853994087721</v>
+        <v>0.1672095347851899</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -7402,13 +7402,13 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>-5.705697084201327</v>
+        <v>-5.630546286378891</v>
       </c>
       <c r="F10">
-        <v>5.761295044586467</v>
+        <v>5.680348983422763</v>
       </c>
       <c r="G10">
-        <v>0.05559796038513976</v>
+        <v>0.04980269704387211</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7425,13 +7425,13 @@
         <v>13</v>
       </c>
       <c r="E11">
-        <v>-8.591289983967043</v>
+        <v>-8.708595523871173</v>
       </c>
       <c r="F11">
-        <v>8.726651526919424</v>
+        <v>8.815677046947053</v>
       </c>
       <c r="G11">
-        <v>0.1353615429523808</v>
+        <v>0.1070815230758818</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7448,10 +7448,10 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>159.0238340092913</v>
+        <v>144.1424231730849</v>
       </c>
       <c r="F12">
-        <v>-159.0238340092913</v>
+        <v>-144.1424231730849</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -7471,10 +7471,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-85.35903030459723</v>
+        <v>-81.35849659248342</v>
       </c>
       <c r="F13">
-        <v>85.35903030459723</v>
+        <v>81.35849659248342</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -7494,13 +7494,13 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>-23.48079171994188</v>
+        <v>-22.98336404203696</v>
       </c>
       <c r="F14">
-        <v>23.65318887752521</v>
+        <v>23.1367613339864</v>
       </c>
       <c r="G14">
-        <v>0.1723971575833205</v>
+        <v>0.1533972919494364</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7517,13 +7517,13 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>-20.38326111197993</v>
+        <v>-20.27170066126043</v>
       </c>
       <c r="F15">
-        <v>20.90646864988324</v>
+        <v>20.76457543504845</v>
       </c>
       <c r="G15">
-        <v>0.5232075379033113</v>
+        <v>0.4928747737880157</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7540,13 +7540,13 @@
         <v>11</v>
       </c>
       <c r="E16">
-        <v>-14.2255067808269</v>
+        <v>-13.7990194749279</v>
       </c>
       <c r="F16">
-        <v>14.4807916299722</v>
+        <v>13.98336395206727</v>
       </c>
       <c r="G16">
-        <v>0.2552848491452958</v>
+        <v>0.1843444771393754</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -7563,13 +7563,13 @@
         <v>13</v>
       </c>
       <c r="E17">
-        <v>0.407138391421016</v>
+        <v>0.4775027764469026</v>
       </c>
       <c r="F17">
-        <v>-0.39430297677594</v>
+        <v>-0.4694537745983755</v>
       </c>
       <c r="G17">
-        <v>0.01283541464507602</v>
+        <v>0.008049001848527138</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7586,13 +7586,13 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>5.483260962992918</v>
+        <v>5.371700512273422</v>
       </c>
       <c r="F18">
-        <v>-5.315848542440981</v>
+        <v>-5.268907387562741</v>
       </c>
       <c r="G18">
-        <v>0.1674124205519371</v>
+        <v>0.1027931247106803</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7609,13 +7609,13 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>-32.61155445862084</v>
+        <v>-35.49486010305126</v>
       </c>
       <c r="F19">
-        <v>32.79771120181657</v>
+        <v>35.71533229428558</v>
       </c>
       <c r="G19">
-        <v>0.1861567431957256</v>
+        <v>0.2204721912343222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7632,13 +7632,13 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-7.341823131989497</v>
+        <v>-8.792047335108727</v>
       </c>
       <c r="F20">
-        <v>7.396100308820651</v>
+        <v>8.855803848232711</v>
       </c>
       <c r="G20">
-        <v>0.05427717683115368</v>
+        <v>0.0637565131239845</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7655,13 +7655,13 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>-43.17471751874211</v>
+        <v>-43.68014279846612</v>
       </c>
       <c r="F21">
-        <v>43.99300232188127</v>
+        <v>44.51948461314435</v>
       </c>
       <c r="G21">
-        <v>0.8182848031391632</v>
+        <v>0.8393418146782294</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7678,13 +7678,13 @@
         <v>4</v>
       </c>
       <c r="E22">
-        <v>4.904561446590992</v>
+        <v>3.69858329604706</v>
       </c>
       <c r="F22">
-        <v>-4.858497915275622</v>
+        <v>-3.664100211428219</v>
       </c>
       <c r="G22">
-        <v>0.04606353131536983</v>
+        <v>0.03448308461884153</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7701,13 +7701,13 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>1.033712170640507</v>
+        <v>0.2222329430763379</v>
       </c>
       <c r="F23">
-        <v>-0.9877561719056722</v>
+        <v>-0.1821897918077124</v>
       </c>
       <c r="G23">
-        <v>0.04595599873483472</v>
+        <v>0.04004315126862558</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7724,13 +7724,13 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>52.61926285790406</v>
+        <v>52.06567242870407</v>
       </c>
       <c r="F24">
-        <v>-50.82528321500786</v>
+        <v>-50.31985794934929</v>
       </c>
       <c r="G24">
-        <v>1.793979642896193</v>
+        <v>1.745814479354779</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7747,13 +7747,13 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-16.07122195746438</v>
+        <v>-14.40933868242275</v>
       </c>
       <c r="F25">
-        <v>16.10678297998304</v>
+        <v>14.43985814113299</v>
       </c>
       <c r="G25">
-        <v>0.03556102251865978</v>
+        <v>0.03051945871023753</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7770,13 +7770,13 @@
         <v>11</v>
       </c>
       <c r="E26">
-        <v>10.69192490183864</v>
+        <v>10.28985887811373</v>
       </c>
       <c r="F26">
-        <v>-10.50655845051989</v>
+        <v>-10.12278651221361</v>
       </c>
       <c r="G26">
-        <v>0.1853664513187497</v>
+        <v>0.1670723659001241</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7793,13 +7793,13 @@
         <v>12</v>
       </c>
       <c r="E27">
-        <v>-5.600927189625362</v>
+        <v>-5.631744524720019</v>
       </c>
       <c r="F27">
-        <v>5.651135201266621</v>
+        <v>5.681561999663477</v>
       </c>
       <c r="G27">
-        <v>0.05020801164125899</v>
+        <v>0.0498174749434574</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -7816,13 +7816,13 @@
         <v>13</v>
       </c>
       <c r="E28">
-        <v>-8.525304225667563</v>
+        <v>-8.71323940545933</v>
       </c>
       <c r="F28">
-        <v>8.634756123785255</v>
+        <v>8.820377530261897</v>
       </c>
       <c r="G28">
-        <v>0.109451898117692</v>
+        <v>0.1071381248025666</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7839,10 +7839,10 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>148.1871250763639</v>
+        <v>144.0898011281853</v>
       </c>
       <c r="F29">
-        <v>-148.1871250763639</v>
+        <v>-144.0898011281853</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -7862,10 +7862,10 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-82.73517024769471</v>
+        <v>-81.33632208460293</v>
       </c>
       <c r="F30">
-        <v>82.73517024769471</v>
+        <v>81.33632208460293</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7885,13 +7885,13 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>-23.39234811412542</v>
+        <v>-22.97403458349322</v>
       </c>
       <c r="F31">
-        <v>23.55235063879086</v>
+        <v>23.12731519427872</v>
       </c>
       <c r="G31">
-        <v>0.1600025246654424</v>
+        <v>0.1532806107854973</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -7908,13 +7908,13 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>-20.49780351398969</v>
+        <v>-20.26576866466315</v>
       </c>
       <c r="F32">
-        <v>21.00416685311312</v>
+        <v>20.7583717680407</v>
       </c>
       <c r="G32">
-        <v>0.5063633391234251</v>
+        <v>0.4926031033775508</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7931,13 +7931,13 @@
         <v>11</v>
       </c>
       <c r="E33">
-        <v>-14.19192493682045</v>
+        <v>-13.78985891309555</v>
       </c>
       <c r="F33">
-        <v>14.39234802415573</v>
+        <v>13.97403449352353</v>
       </c>
       <c r="G33">
-        <v>0.2004230873352719</v>
+        <v>0.1841755804279838</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7954,13 +7954,13 @@
         <v>13</v>
       </c>
       <c r="E34">
-        <v>0.5079406946428563</v>
+        <v>0.4763017485067835</v>
       </c>
       <c r="F34">
-        <v>-0.499072871351905</v>
+        <v>-0.4682555362572472</v>
       </c>
       <c r="G34">
-        <v>0.008867823290951288</v>
+        <v>0.008046212249536357</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7977,13 +7977,13 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>5.597803365002685</v>
+        <v>5.365768515676139</v>
       </c>
       <c r="F35">
-        <v>-5.482636603962303</v>
+        <v>-5.263062478034463</v>
       </c>
       <c r="G35">
-        <v>0.115166761040382</v>
+        <v>0.1027060376416755</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -8000,13 +8000,13 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>-30.07178070162583</v>
+        <v>-32.02803048351161</v>
       </c>
       <c r="F36">
-        <v>30.22999778353807</v>
+        <v>32.20748202424174</v>
       </c>
       <c r="G36">
-        <v>0.1582170819122486</v>
+        <v>0.17945154073013</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -8023,13 +8023,13 @@
         <v>5</v>
       </c>
       <c r="E37">
-        <v>-8.384691919741215</v>
+        <v>-9.326942436423428</v>
       </c>
       <c r="F37">
-        <v>8.446681613772496</v>
+        <v>9.396366751403097</v>
       </c>
       <c r="G37">
-        <v>0.06198969403128085</v>
+        <v>0.06942431497966861</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -8046,13 +8046,13 @@
         <v>3</v>
       </c>
       <c r="E38">
-        <v>-36.79048237438148</v>
+        <v>-37.08636467278353</v>
       </c>
       <c r="F38">
-        <v>37.38064998711491</v>
+        <v>37.68772191532296</v>
       </c>
       <c r="G38">
-        <v>0.5901676127334332</v>
+        <v>0.6013572425394298</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -8069,13 +8069,13 @@
         <v>4</v>
       </c>
       <c r="E39">
-        <v>4.040816247062795</v>
+        <v>3.276537231115217</v>
       </c>
       <c r="F39">
-        <v>-4.000950264151404</v>
+        <v>-3.242179939052307</v>
       </c>
       <c r="G39">
-        <v>0.03986598291138982</v>
+        <v>0.03435729206290941</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -8092,13 +8092,13 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>-1.126182331497926</v>
+        <v>-1.63510316160477</v>
       </c>
       <c r="F40">
-        <v>1.170401681131208</v>
+        <v>1.677648983816211</v>
       </c>
       <c r="G40">
-        <v>0.04421934963328104</v>
+        <v>0.04254582221144068</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8115,13 +8115,13 @@
         <v>4</v>
       </c>
       <c r="E41">
-        <v>44.50793768029413</v>
+        <v>44.18166565838968</v>
       </c>
       <c r="F41">
-        <v>-43.20951823663372</v>
+        <v>-42.91363595326208</v>
       </c>
       <c r="G41">
-        <v>1.298419443660409</v>
+        <v>1.268029705127599</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -8138,13 +8138,13 @@
         <v>5</v>
       </c>
       <c r="E42">
-        <v>-21.32636352126733</v>
+        <v>-20.25697487964863</v>
       </c>
       <c r="F42">
-        <v>21.3866185616839</v>
+        <v>20.31217804558037</v>
       </c>
       <c r="G42">
-        <v>0.06025504041657637</v>
+        <v>0.05520316593173591</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -8161,13 +8161,13 @@
         <v>11</v>
       </c>
       <c r="E43">
-        <v>12.53448063488328</v>
+        <v>12.27935721716702</v>
       </c>
       <c r="F43">
-        <v>-12.30514335315638</v>
+        <v>-12.0621367267745</v>
       </c>
       <c r="G43">
-        <v>0.2293372817268921</v>
+        <v>0.2172204903925182</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -8184,13 +8184,13 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>-5.382068751811494</v>
+        <v>-5.402710647601753</v>
       </c>
       <c r="F44">
-        <v>5.43043688632217</v>
+        <v>5.450862176616723</v>
       </c>
       <c r="G44">
-        <v>0.04836813451067554</v>
+        <v>0.04815152901497047</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8207,13 +8207,13 @@
         <v>13</v>
       </c>
       <c r="E45">
-        <v>-7.608318855557003</v>
+        <v>-7.728086086259475</v>
       </c>
       <c r="F45">
-        <v>7.711944087760639</v>
+        <v>7.830294862759047</v>
       </c>
       <c r="G45">
-        <v>0.1036252322036357</v>
+        <v>0.1022087764995711</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -8230,10 +8230,10 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>147.6327217309471</v>
+        <v>145.0385295834241</v>
       </c>
       <c r="F46">
-        <v>-147.6327217309471</v>
+        <v>-145.0385295834241</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>9</v>
       </c>
       <c r="E47">
-        <v>-84.59274818015946</v>
+        <v>-83.70601210422547</v>
       </c>
       <c r="F47">
-        <v>84.59274818015946</v>
+        <v>83.70601210422547</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -8276,13 +8276,13 @@
         <v>10</v>
       </c>
       <c r="E48">
-        <v>-25.28128334437006</v>
+        <v>-25.01529908124092</v>
       </c>
       <c r="F48">
-        <v>25.46781406357918</v>
+        <v>25.19721471518049</v>
       </c>
       <c r="G48">
-        <v>0.1865307192091159</v>
+        <v>0.1819156339395722</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -8299,13 +8299,13 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>-21.66427671128545</v>
+        <v>-21.51504143298331</v>
       </c>
       <c r="F49">
-        <v>22.22953487834524</v>
+        <v>22.07093363317655</v>
       </c>
       <c r="G49">
-        <v>0.5652581670597873</v>
+        <v>0.5558922001932448</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -8322,13 +8322,13 @@
         <v>11</v>
       </c>
       <c r="E50">
-        <v>-16.03448066986509</v>
+        <v>-15.77935725214883</v>
       </c>
       <c r="F50">
-        <v>16.28128325440038</v>
+        <v>16.01529899127122</v>
       </c>
       <c r="G50">
-        <v>0.2468025845352911</v>
+        <v>0.2359417391223945</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8345,13 +8345,13 @@
         <v>13</v>
       </c>
       <c r="E51">
-        <v>0.7282220151299234</v>
+        <v>0.7070515242760265</v>
       </c>
       <c r="F51">
-        <v>-0.7179313091657727</v>
+        <v>-0.6972894133755142</v>
       </c>
       <c r="G51">
-        <v>0.01029070596415054</v>
+        <v>0.009762110900512263</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8368,13 +8368,13 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>6.764276562298445</v>
+        <v>6.615041283996298</v>
       </c>
       <c r="F52">
-        <v>-6.619903294559931</v>
+        <v>-6.478965573003562</v>
       </c>
       <c r="G52">
-        <v>0.1443732677385137</v>
+        <v>0.1360757109927363</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8391,13 +8391,13 @@
         <v>2</v>
       </c>
       <c r="E53">
-        <v>-12.64465997187626</v>
+        <v>-12.64469218174731</v>
       </c>
       <c r="F53">
-        <v>12.67270665432621</v>
+        <v>12.67273900717617</v>
       </c>
       <c r="G53">
-        <v>0.02804668244995312</v>
+        <v>0.02804682542885406</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -8414,13 +8414,13 @@
         <v>5</v>
       </c>
       <c r="E54">
-        <v>-4.315083181810566</v>
+        <v>-4.315113665997978</v>
       </c>
       <c r="F54">
-        <v>4.348723695576954</v>
+        <v>4.348754283101572</v>
       </c>
       <c r="G54">
-        <v>0.03364051376638783</v>
+        <v>0.03364061710359398</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8437,13 +8437,13 @@
         <v>3</v>
       </c>
       <c r="E55">
-        <v>-21.84309565964729</v>
+        <v>-21.84311233642346</v>
       </c>
       <c r="F55">
-        <v>22.05099249263803</v>
+        <v>22.05100949300207</v>
       </c>
       <c r="G55">
-        <v>0.2078968329907449</v>
+        <v>0.2078971565786097</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -8460,13 +8460,13 @@
         <v>4</v>
       </c>
       <c r="E56">
-        <v>4.752361004429635</v>
+        <v>4.752325090090323</v>
       </c>
       <c r="F56">
-        <v>-4.716836695670254</v>
+        <v>-4.716801024145572</v>
       </c>
       <c r="G56">
-        <v>0.03552430875938123</v>
+        <v>0.03552406594475102</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8483,13 +8483,13 @@
         <v>5</v>
       </c>
       <c r="E57">
-        <v>-1.839543069990173</v>
+        <v>-1.83956995990039</v>
       </c>
       <c r="F57">
-        <v>1.87611722977524</v>
+        <v>1.876144108404996</v>
       </c>
       <c r="G57">
-        <v>0.03657415978506676</v>
+        <v>0.03657414850460547</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8506,13 +8506,13 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>28.70484854565689</v>
+        <v>28.70483119778531</v>
       </c>
       <c r="F58">
-        <v>-28.15690471596665</v>
+        <v>-28.1568880391907</v>
       </c>
       <c r="G58">
-        <v>0.547943829690245</v>
+        <v>0.547943158594616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -8529,13 +8529,13 @@
         <v>5</v>
       </c>
       <c r="E59">
-        <v>-27.19878816178624</v>
+        <v>-27.19875017411107</v>
       </c>
       <c r="F59">
-        <v>27.29501795529721</v>
+        <v>27.29497972296204</v>
       </c>
       <c r="G59">
-        <v>0.09622979351096572</v>
+        <v>0.09622954885097346</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -8552,13 +8552,13 @@
         <v>11</v>
       </c>
       <c r="E60">
-        <v>14.6833751768798</v>
+        <v>14.68336275511711</v>
       </c>
       <c r="F60">
-        <v>-14.41167986489963</v>
+        <v>-14.41166787993971</v>
       </c>
       <c r="G60">
-        <v>0.2716953119801691</v>
+        <v>0.2716948751774001</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8575,13 +8575,13 @@
         <v>12</v>
       </c>
       <c r="E61">
-        <v>-5.298391947067048</v>
+        <v>-5.298393280984291</v>
       </c>
       <c r="F61">
-        <v>5.345343425893795</v>
+        <v>5.345344765067171</v>
       </c>
       <c r="G61">
-        <v>0.04695147882674694</v>
+        <v>0.04695148408288066</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8598,13 +8598,13 @@
         <v>13</v>
       </c>
       <c r="E62">
-        <v>-7.321819934984697</v>
+        <v>-7.321825993331998</v>
       </c>
       <c r="F62">
-        <v>7.419750622847186</v>
+        <v>7.419756685136106</v>
       </c>
       <c r="G62">
-        <v>0.09793068786248943</v>
+        <v>0.09793069180410729</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8621,10 +8621,10 @@
         <v>8</v>
       </c>
       <c r="E63">
-        <v>136.9471853092647</v>
+        <v>136.9470727226605</v>
       </c>
       <c r="F63">
-        <v>-136.9471853092647</v>
+        <v>-136.9470727226605</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8644,10 +8644,10 @@
         <v>9</v>
       </c>
       <c r="E64">
-        <v>-76.74825512386289</v>
+        <v>-76.74821477070434</v>
       </c>
       <c r="F64">
-        <v>76.74825512386289</v>
+        <v>76.74821477070434</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8667,13 +8667,13 @@
         <v>10</v>
       </c>
       <c r="E65">
-        <v>-18.47865021942618</v>
+        <v>-18.47863737460629</v>
       </c>
       <c r="F65">
-        <v>18.57748238045813</v>
+        <v>18.57746939216151</v>
       </c>
       <c r="G65">
-        <v>0.09883216103195036</v>
+        <v>0.09883201755521709</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8690,13 +8690,13 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>-22.03609535734681</v>
+        <v>-22.03608767806832</v>
       </c>
       <c r="F66">
-        <v>22.61747507345405</v>
+        <v>22.61746696969246</v>
       </c>
       <c r="G66">
-        <v>0.5813797161072443</v>
+        <v>0.5813792916241373</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -8713,13 +8713,13 @@
         <v>11</v>
       </c>
       <c r="E67">
-        <v>-18.18337521186162</v>
+        <v>-18.18336279009893</v>
       </c>
       <c r="F67">
-        <v>18.47865021942618</v>
+        <v>18.47863737460629</v>
       </c>
       <c r="G67">
-        <v>0.2952750075645577</v>
+        <v>0.2952745845073657</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8736,13 +8736,13 @@
         <v>13</v>
       </c>
       <c r="E68">
-        <v>0.8117528418005353</v>
+        <v>0.8117514928078908</v>
       </c>
       <c r="F68">
-        <v>-0.8016081139102191</v>
+        <v>-0.8016067799929756</v>
       </c>
       <c r="G68">
-        <v>0.0101447278903162</v>
+        <v>0.0101447128149152</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8759,13 +8759,13 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>7.136095208359797</v>
+        <v>7.136087529081318</v>
       </c>
       <c r="F69">
-        <v>-6.989933041802848</v>
+        <v>-6.989925634462903</v>
       </c>
       <c r="G69">
-        <v>0.1461621665569485</v>
+        <v>0.1461618946184157</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -8782,13 +8782,13 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>-2.113671780268636</v>
+        <v>4.733203406791396</v>
       </c>
       <c r="F70">
-        <v>2.115406318668438</v>
+        <v>-4.727685877375809</v>
       </c>
       <c r="G70">
-        <v>0.001734538399801241</v>
+        <v>0.005517529415586392</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -8805,13 +8805,13 @@
         <v>5</v>
       </c>
       <c r="E71">
-        <v>4.473874300825898</v>
+        <v>4.782212332501897</v>
       </c>
       <c r="F71">
-        <v>-4.458462813224154</v>
+        <v>-4.766650258846716</v>
       </c>
       <c r="G71">
-        <v>0.01541148760174429</v>
+        <v>0.01556207365518217</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8828,13 +8828,13 @@
         <v>3</v>
       </c>
       <c r="E72">
-        <v>2.857179304249015</v>
+        <v>6.152997534047631</v>
       </c>
       <c r="F72">
-        <v>-2.853434330829118</v>
+        <v>-6.135726941262284</v>
       </c>
       <c r="G72">
-        <v>0.003744973419897435</v>
+        <v>0.01727059278534698</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -8851,13 +8851,13 @@
         <v>4</v>
       </c>
       <c r="E73">
-        <v>6.000483432943271</v>
+        <v>12.85486027755718</v>
       </c>
       <c r="F73">
-        <v>-5.97979394336859</v>
+        <v>-12.76248825129281</v>
       </c>
       <c r="G73">
-        <v>0.02068948957468161</v>
+        <v>0.09237202626437291</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -8874,13 +8874,13 @@
         <v>5</v>
       </c>
       <c r="E74">
-        <v>6.006105409060528</v>
+        <v>4.113450406485294</v>
       </c>
       <c r="F74">
-        <v>-5.979245423131322</v>
+        <v>-4.099650479624979</v>
       </c>
       <c r="G74">
-        <v>0.02685998592920694</v>
+        <v>0.01379992686031464</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8897,13 +8897,13 @@
         <v>4</v>
       </c>
       <c r="E75">
-        <v>2.862897330040687</v>
+        <v>6.177666813154361</v>
       </c>
       <c r="F75">
-        <v>-2.85717932311106</v>
+        <v>-6.152997590176914</v>
       </c>
       <c r="G75">
-        <v>0.00571800692962636</v>
+        <v>0.024669222977447</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -8920,13 +8920,13 @@
         <v>5</v>
       </c>
       <c r="E76">
-        <v>-0.1257557036531358</v>
+        <v>-36.33029761234834</v>
       </c>
       <c r="F76">
-        <v>0.1424649361226996</v>
+        <v>36.5257313521882</v>
       </c>
       <c r="G76">
-        <v>0.01670923246956382</v>
+        <v>0.1954337398398565</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -8943,13 +8943,13 @@
         <v>11</v>
       </c>
       <c r="E77">
-        <v>6.664101249424709</v>
+        <v>17.65099690123872</v>
       </c>
       <c r="F77">
-        <v>-6.598256353184606</v>
+        <v>-17.37220429261938</v>
       </c>
       <c r="G77">
-        <v>0.06584489624010259</v>
+        <v>0.278792608619341</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -8966,13 +8966,13 @@
         <v>12</v>
       </c>
       <c r="E78">
-        <v>-1.415458635343743</v>
+        <v>-1.102245553106335</v>
       </c>
       <c r="F78">
-        <v>1.425938457954037</v>
+        <v>1.111142942679097</v>
       </c>
       <c r="G78">
-        <v>0.01047982261029382</v>
+        <v>0.008897389572762142</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -8989,13 +8989,13 @@
         <v>13</v>
       </c>
       <c r="E79">
-        <v>-4.762534949522278</v>
+        <v>-3.652395286877443</v>
       </c>
       <c r="F79">
-        <v>4.81809348086149</v>
+        <v>3.695695782567822</v>
       </c>
       <c r="G79">
-        <v>0.05555853133921221</v>
+        <v>0.0433004956903793</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -9012,10 +9012,10 @@
         <v>8</v>
       </c>
       <c r="E80">
-        <v>61.7959833260127</v>
+        <v>21.27155856192387</v>
       </c>
       <c r="F80">
-        <v>-61.7959833260127</v>
+        <v>-21.27155856192387</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -9035,10 +9035,10 @@
         <v>9</v>
       </c>
       <c r="E81">
-        <v>-43.9531811443229</v>
+        <v>-10.70088111415441</v>
       </c>
       <c r="F81">
-        <v>43.9531811443229</v>
+        <v>10.70088111415441</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -9058,13 +9058,13 @@
         <v>10</v>
       </c>
       <c r="E82">
-        <v>-10.25332101693603</v>
+        <v>28.5117064283939</v>
       </c>
       <c r="F82">
-        <v>10.28592501690889</v>
+        <v>-28.2756050995619</v>
       </c>
       <c r="G82">
-        <v>0.03260399997286612</v>
+        <v>0.2361013288319946</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -9081,13 +9081,13 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>-7.433910540106019</v>
+        <v>-8.885417809664554</v>
       </c>
       <c r="F83">
-        <v>7.504212260028331</v>
+        <v>8.988904868617208</v>
       </c>
       <c r="G83">
-        <v>0.07030171992231243</v>
+        <v>0.1034870589526546</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -9104,13 +9104,13 @@
         <v>11</v>
       </c>
       <c r="E84">
-        <v>-10.16410128440652</v>
+        <v>-21.15099693622054</v>
       </c>
       <c r="F84">
-        <v>10.25332101693603</v>
+        <v>21.4882935716061</v>
       </c>
       <c r="G84">
-        <v>0.08921973252950244</v>
+        <v>0.3372966353855644</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -9127,13 +9127,13 @@
         <v>13</v>
       </c>
       <c r="E85">
-        <v>-1.408968121027218</v>
+        <v>-1.097873026498382</v>
       </c>
       <c r="F85">
-        <v>1.415458635343743</v>
+        <v>1.102245553106335</v>
       </c>
       <c r="G85">
-        <v>0.006490514316525621</v>
+        <v>0.004372526607952613</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -9150,13 +9150,13 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>7.433910540106019</v>
+        <v>8.885417809664554</v>
       </c>
       <c r="F86">
-        <v>-7.328497064437514</v>
+        <v>-8.749731821611185</v>
       </c>
       <c r="G86">
-        <v>0.1054134756685046</v>
+        <v>0.1356859880533703</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -9173,13 +9173,13 @@
         <v>2</v>
       </c>
       <c r="E87">
-        <v>0.8077669660694734</v>
+        <v>55.51708765422782</v>
       </c>
       <c r="F87">
-        <v>-0.8069006348438377</v>
+        <v>-54.89730844599083</v>
       </c>
       <c r="G87">
-        <v>0.0008663312256356956</v>
+        <v>0.6197792082369924</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -9196,13 +9196,13 @@
         <v>5</v>
       </c>
       <c r="E88">
-        <v>13.55005628537286</v>
+        <v>37.30085030212655</v>
       </c>
       <c r="F88">
-        <v>-13.45076195458799</v>
+        <v>-36.53125970086322</v>
       </c>
       <c r="G88">
-        <v>0.09929433078486871</v>
+        <v>0.7695906012633313</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -9219,13 +9219,13 @@
         <v>3</v>
       </c>
       <c r="E89">
-        <v>4.410008851984301</v>
+        <v>20.97742566815086</v>
       </c>
       <c r="F89">
-        <v>-4.401273940071509</v>
+        <v>-20.76690373110456</v>
       </c>
       <c r="G89">
-        <v>0.008734911912791632</v>
+        <v>0.2105219370463013</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -9242,13 +9242,13 @@
         <v>4</v>
       </c>
       <c r="E90">
-        <v>9.256144189146571</v>
+        <v>44.27572858568341</v>
       </c>
       <c r="F90">
-        <v>-9.207508522021767</v>
+        <v>-43.15047577823394</v>
       </c>
       <c r="G90">
-        <v>0.04863566712480505</v>
+        <v>1.125252807449473</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -9265,13 +9265,13 @@
         <v>5</v>
       </c>
       <c r="E91">
-        <v>16.35932702913242</v>
+        <v>27.56389973511099</v>
       </c>
       <c r="F91">
-        <v>-16.20339963169717</v>
+        <v>-27.10786770263082</v>
       </c>
       <c r="G91">
-        <v>0.1559273974352571</v>
+        <v>0.4560320324801748</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -9288,13 +9288,13 @@
         <v>4</v>
       </c>
       <c r="E92">
-        <v>4.423518627199251</v>
+        <v>21.27767444036457</v>
       </c>
       <c r="F92">
-        <v>-4.410008923907014</v>
+        <v>-20.97742609155341</v>
       </c>
       <c r="G92">
-        <v>0.01350970329223738</v>
+        <v>0.3002483488111579</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -9311,13 +9311,13 @@
         <v>5</v>
       </c>
       <c r="E93">
-        <v>28.9404170325113</v>
+        <v>-68.44692506386156</v>
       </c>
       <c r="F93">
-        <v>-28.8145344579368</v>
+        <v>69.13895873238305</v>
       </c>
       <c r="G93">
-        <v>0.125882574574504</v>
+        <v>0.6920336685214967</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -9334,13 +9334,13 @@
         <v>11</v>
       </c>
       <c r="E94">
-        <v>5.532867238413544</v>
+        <v>35.97275113441817</v>
       </c>
       <c r="F94">
-        <v>-5.480495195187913</v>
+        <v>-34.80560712762914</v>
       </c>
       <c r="G94">
-        <v>0.05237204322563124</v>
+        <v>1.167144006789023</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -9357,13 +9357,13 @@
         <v>12</v>
       </c>
       <c r="E95">
-        <v>0.5271495657927951</v>
+        <v>2.239503914089394</v>
       </c>
       <c r="F95">
-        <v>-0.5173600594189524</v>
+        <v>-2.223044983987287</v>
       </c>
       <c r="G95">
-        <v>0.009789506373842748</v>
+        <v>0.01645893010210793</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -9380,13 +9380,13 @@
         <v>13</v>
       </c>
       <c r="E96">
-        <v>2.893544325629407</v>
+        <v>9.476242176357838</v>
       </c>
       <c r="F96">
-        <v>-2.851945666012514</v>
+        <v>-9.389173782902246</v>
       </c>
       <c r="G96">
-        <v>0.04159865961689303</v>
+        <v>0.08706839345559297</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -9403,10 +9403,10 @@
         <v>8</v>
       </c>
       <c r="E97">
-        <v>-1.081364231431375</v>
+        <v>-9.999999568885118</v>
       </c>
       <c r="F97">
-        <v>1.081364231431375</v>
+        <v>9.999999568885118</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9426,10 +9426,10 @@
         <v>9</v>
       </c>
       <c r="E98">
-        <v>-4.274033486415392</v>
+        <v>35.03998345739638</v>
       </c>
       <c r="F98">
-        <v>4.274033486415392</v>
+        <v>-35.03998345739638</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9449,13 +9449,13 @@
         <v>10</v>
       </c>
       <c r="E99">
-        <v>-5.56578233943637</v>
+        <v>63.01706585892867</v>
       </c>
       <c r="F99">
-        <v>5.576000675366366</v>
+        <v>-61.86306765911546</v>
       </c>
       <c r="G99">
-        <v>0.01021833592999566</v>
+        <v>1.153998199813222</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -9472,13 +9472,13 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>-3.46016267947311</v>
+        <v>-11.97424721089934</v>
       </c>
       <c r="F100">
-        <v>3.47750668480622</v>
+        <v>12.1707062818123</v>
       </c>
       <c r="G100">
-        <v>0.01734400533310934</v>
+        <v>0.1964590709129549</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -9495,13 +9495,13 @@
         <v>11</v>
       </c>
       <c r="E101">
-        <v>-5.532867238413544</v>
+        <v>-35.97275113441817</v>
       </c>
       <c r="F101">
-        <v>5.56578233943637</v>
+        <v>36.98293414107133</v>
       </c>
       <c r="G101">
-        <v>0.03291510102282624</v>
+        <v>1.010183006653165</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -9518,13 +9518,13 @@
         <v>13</v>
       </c>
       <c r="E102">
-        <v>0.5312025948914695</v>
+        <v>2.254313385295376</v>
       </c>
       <c r="F102">
-        <v>-0.5271495657927951</v>
+        <v>-2.239503914089394</v>
       </c>
       <c r="G102">
-        <v>0.004053029098674381</v>
+        <v>0.01480947120598188</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -9541,13 +9541,13 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>3.46016267947311</v>
+        <v>11.97424721089934</v>
       </c>
       <c r="F103">
-        <v>-3.424746920520877</v>
+        <v>-11.73055556165321</v>
       </c>
       <c r="G103">
-        <v>0.03541575895223345</v>
+        <v>0.2436916492461305</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -9564,13 +9564,13 @@
         <v>2</v>
       </c>
       <c r="E104">
-        <v>48.24454440478741</v>
+        <v>55.30314722082799</v>
       </c>
       <c r="F104">
-        <v>-47.81404671010825</v>
+        <v>-54.69172602046659</v>
       </c>
       <c r="G104">
-        <v>0.4304976946791661</v>
+        <v>0.611421200361395</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -9587,13 +9587,13 @@
         <v>5</v>
       </c>
       <c r="E105">
-        <v>43.20260893642591</v>
+        <v>31.70177683595583</v>
       </c>
       <c r="F105">
-        <v>-42.22734659430933</v>
+        <v>-31.14470695150801</v>
       </c>
       <c r="G105">
-        <v>0.9752623421165785</v>
+        <v>0.5570698844478195</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9610,13 +9610,13 @@
         <v>3</v>
       </c>
       <c r="E106">
-        <v>10.97890828791997</v>
+        <v>18.55672038148922</v>
       </c>
       <c r="F106">
-        <v>-10.92477022252338</v>
+        <v>-18.39257157296049</v>
       </c>
       <c r="G106">
-        <v>0.05413806539659172</v>
+        <v>0.1641488085287357</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -9633,13 +9633,13 @@
         <v>4</v>
       </c>
       <c r="E107">
-        <v>23.14574285485238</v>
+        <v>39.09366311116564</v>
       </c>
       <c r="F107">
-        <v>-22.8231776307036</v>
+        <v>-38.21679474894096</v>
       </c>
       <c r="G107">
-        <v>0.3225652241487853</v>
+        <v>0.8768683622246809</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -9656,13 +9656,13 @@
         <v>5</v>
       </c>
       <c r="E108">
-        <v>37.00660149042806</v>
+        <v>20.65559923480941</v>
       </c>
       <c r="F108">
-        <v>-36.19662132405695</v>
+        <v>-20.39378595481387</v>
       </c>
       <c r="G108">
-        <v>0.8099801663711104</v>
+        <v>0.261813279995543</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -9679,13 +9679,13 @@
         <v>4</v>
       </c>
       <c r="E109">
-        <v>11.07694983562967</v>
+        <v>18.79091991378555</v>
       </c>
       <c r="F109">
-        <v>-10.97890866570854</v>
+        <v>-18.55672075632381</v>
       </c>
       <c r="G109">
-        <v>0.09804116992112311</v>
+        <v>0.2341991574617425</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -9702,13 +9702,13 @@
         <v>5</v>
       </c>
       <c r="E110">
-        <v>55.53483050469755</v>
+        <v>-75.52956398219834</v>
       </c>
       <c r="F110">
-        <v>-55.09669443910865</v>
+        <v>76.35982590639513</v>
       </c>
       <c r="G110">
-        <v>0.4381360655889011</v>
+        <v>0.8302619241967846</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -9725,13 +9725,13 @@
         <v>11</v>
       </c>
       <c r="E111">
-        <v>3.602549697990094</v>
+        <v>36.23588036469239</v>
       </c>
       <c r="F111">
-        <v>-3.57229240257182</v>
+        <v>-35.05081753973506</v>
       </c>
       <c r="G111">
-        <v>0.03025729541827407</v>
+        <v>1.185062824957334</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -9748,13 +9748,13 @@
         <v>12</v>
       </c>
       <c r="E112">
-        <v>0.3014270395913267</v>
+        <v>2.273359622335444</v>
       </c>
       <c r="F112">
-        <v>-0.2928190882131241</v>
+        <v>-2.256676764120427</v>
       </c>
       <c r="G112">
-        <v>0.008607951378202623</v>
+        <v>0.01668285821501726</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -9771,13 +9771,13 @@
         <v>13</v>
       </c>
       <c r="E113">
-        <v>1.913775306038747</v>
+        <v>9.609029139081109</v>
       </c>
       <c r="F113">
-        <v>-1.878930522442647</v>
+        <v>-9.520318854912464</v>
       </c>
       <c r="G113">
-        <v>0.03484478359610001</v>
+        <v>0.08871028416864435</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -9794,10 +9794,10 @@
         <v>8</v>
       </c>
       <c r="E114">
-        <v>-9.999999170772393</v>
+        <v>-9.999999183416545</v>
       </c>
       <c r="F114">
-        <v>9.999999170772393</v>
+        <v>9.999999183416545</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -9817,10 +9817,10 @@
         <v>9</v>
       </c>
       <c r="E115">
-        <v>-0.1149108499729859</v>
+        <v>34.75661255645925</v>
       </c>
       <c r="F115">
-        <v>0.1149108499729859</v>
+        <v>-34.75661255645925</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -9840,13 +9840,13 @@
         <v>10</v>
       </c>
       <c r="E116">
-        <v>-3.618493685323897</v>
+        <v>62.73831283671427</v>
       </c>
       <c r="F116">
-        <v>3.62467985225618</v>
+        <v>-61.5947446874586</v>
       </c>
       <c r="G116">
-        <v>0.00618616693228366</v>
+        <v>1.143568149255669</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -9863,13 +9863,13 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>-2.237488046319279</v>
+        <v>-12.14826976988585</v>
       </c>
       <c r="F117">
-        <v>2.249322675611012</v>
+        <v>12.35033652270873</v>
       </c>
       <c r="G117">
-        <v>0.01183462929173346</v>
+        <v>0.2020667528228784</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -9886,13 +9886,13 @@
         <v>11</v>
       </c>
       <c r="E118">
-        <v>-3.602549697990094</v>
+        <v>-36.23588036469239</v>
       </c>
       <c r="F118">
-        <v>3.618493685323897</v>
+        <v>37.26168716328574</v>
       </c>
       <c r="G118">
-        <v>0.01594398733380242</v>
+        <v>1.025806798593343</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -9909,13 +9909,13 @@
         <v>13</v>
       </c>
       <c r="E119">
-        <v>0.304341165852955</v>
+        <v>2.288541110250795</v>
       </c>
       <c r="F119">
-        <v>-0.3014270395913267</v>
+        <v>-2.273359622335444</v>
       </c>
       <c r="G119">
-        <v>0.002914126261628278</v>
+        <v>0.01518148791535105</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -9932,13 +9932,13 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>2.237488046319279</v>
+        <v>12.14826976988585</v>
       </c>
       <c r="F120">
-        <v>-2.218116471891702</v>
+        <v>-11.8975702493319</v>
       </c>
       <c r="G120">
-        <v>0.01937157442757666</v>
+        <v>0.2506995205539472</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -9955,13 +9955,13 @@
         <v>2</v>
       </c>
       <c r="E121">
-        <v>57.10491000672935</v>
+        <v>10.7158719614861</v>
       </c>
       <c r="F121">
-        <v>-56.50305634323747</v>
+        <v>-10.69315724930512</v>
       </c>
       <c r="G121">
-        <v>0.6018536634918803</v>
+        <v>0.02271471218098647</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -9978,13 +9978,13 @@
         <v>5</v>
       </c>
       <c r="E122">
-        <v>41.34549724486243</v>
+        <v>1.125477814046403</v>
       </c>
       <c r="F122">
-        <v>-40.44743793870793</v>
+        <v>-1.120723556193998</v>
       </c>
       <c r="G122">
-        <v>0.8980593061545028</v>
+        <v>0.004754257852405096</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -10001,13 +10001,13 @@
         <v>3</v>
       </c>
       <c r="E123">
-        <v>8.435159598740171</v>
+        <v>3.897026911801595</v>
       </c>
       <c r="F123">
-        <v>-8.402800501657367</v>
+        <v>-3.890095951386936</v>
       </c>
       <c r="G123">
-        <v>0.03235909708280277</v>
+        <v>0.006930960414659737</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -10024,13 +10024,13 @@
         <v>4</v>
       </c>
       <c r="E124">
-        <v>17.78645458464818</v>
+        <v>8.124888414211041</v>
       </c>
       <c r="F124">
-        <v>-17.58543135678049</v>
+        <v>-8.087812398774449</v>
       </c>
       <c r="G124">
-        <v>0.2010232278676971</v>
+        <v>0.03707601543659206</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -10047,13 +10047,13 @@
         <v>5</v>
       </c>
       <c r="E125">
-        <v>31.73134845778668</v>
+        <v>-2.488490081093606</v>
       </c>
       <c r="F125">
-        <v>-31.11670422638688</v>
+        <v>2.496233883018025</v>
       </c>
       <c r="G125">
-        <v>0.6146442313998024</v>
+        <v>0.007743801924419216</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -10070,13 +10070,13 @@
         <v>4</v>
       </c>
       <c r="E126">
-        <v>8.499582592317024</v>
+        <v>3.906997136195064</v>
       </c>
       <c r="F126">
-        <v>-8.435159976754319</v>
+        <v>-3.897026978039928</v>
       </c>
       <c r="G126">
-        <v>0.06442261556270507</v>
+        <v>0.009970158155136327</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -10093,13 +10093,13 @@
         <v>5</v>
       </c>
       <c r="E127">
-        <v>56.17502252519977</v>
+        <v>-43.96376639425143</v>
       </c>
       <c r="F127">
-        <v>-55.72738932580727</v>
+        <v>44.24206875060822</v>
       </c>
       <c r="G127">
-        <v>0.4476331993924942</v>
+        <v>0.278302356356791</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -10116,13 +10116,13 @@
         <v>11</v>
       </c>
       <c r="E128">
-        <v>3.069988496843898</v>
+        <v>22.26671184793023</v>
       </c>
       <c r="F128">
-        <v>-3.041047590416453</v>
+        <v>-21.8258554284496</v>
       </c>
       <c r="G128">
-        <v>0.02894090642744478</v>
+        <v>0.4408564194806286</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -10139,13 +10139,13 @@
         <v>12</v>
       </c>
       <c r="E129">
-        <v>-0.9049374471181773</v>
+        <v>0.4384949583393658</v>
       </c>
       <c r="F129">
-        <v>0.9134593870549573</v>
+        <v>-0.4291587485279854</v>
       </c>
       <c r="G129">
-        <v>0.008521939936780021</v>
+        <v>0.009336209811380402</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -10162,13 +10162,13 @@
         <v>13</v>
       </c>
       <c r="E130">
-        <v>-2.83592572382718</v>
+        <v>2.456286299791742</v>
       </c>
       <c r="F130">
-        <v>2.875718894181368</v>
+        <v>-2.418207904684641</v>
       </c>
       <c r="G130">
-        <v>0.03979317035418851</v>
+        <v>0.03807839510710093</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -10185,10 +10185,10 @@
         <v>8</v>
       </c>
       <c r="E131">
-        <v>-9.999999164510454</v>
+        <v>2.353190510306641</v>
       </c>
       <c r="F131">
-        <v>9.999999164510454</v>
+        <v>-2.353190510306641</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -10208,10 +10208,10 @@
         <v>9</v>
       </c>
       <c r="E132">
-        <v>-5.546571892246562</v>
+        <v>6.279804533865859</v>
       </c>
       <c r="F132">
-        <v>5.546571892246562</v>
+        <v>-6.279804533865859</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -10231,13 +10231,13 @@
         <v>10</v>
       </c>
       <c r="E133">
-        <v>-3.084239918728199</v>
+        <v>27.35873085082595</v>
       </c>
       <c r="F133">
-        <v>3.08907939101225</v>
+        <v>-27.14045553358806</v>
       </c>
       <c r="G133">
-        <v>0.004839472284050989</v>
+        <v>0.2182753172378871</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -10254,13 +10254,13 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>-11.19708350173236</v>
+        <v>-17.82423848095171</v>
       </c>
       <c r="F134">
-        <v>11.35227354333236</v>
+        <v>18.21969169289338</v>
       </c>
       <c r="G134">
-        <v>0.1551900416000035</v>
+        <v>0.3954532119416654</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10277,13 +10277,13 @@
         <v>11</v>
       </c>
       <c r="E135">
-        <v>-3.069988496843898</v>
+        <v>-22.26671184793023</v>
       </c>
       <c r="F135">
-        <v>3.084239918728199</v>
+        <v>22.64126914917405</v>
       </c>
       <c r="G135">
-        <v>0.0142514218843013</v>
+        <v>0.3745573012438191</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -10300,13 +10300,13 @@
         <v>13</v>
       </c>
       <c r="E136">
-        <v>-0.9012311937562254</v>
+        <v>0.4418785542938761</v>
       </c>
       <c r="F136">
-        <v>0.9049374471181773</v>
+        <v>-0.4384949583393658</v>
       </c>
       <c r="G136">
-        <v>0.003706253361951926</v>
+        <v>0.003383595954510252</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10323,13 +10323,13 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>-3.702916647254648</v>
+        <v>2.924238331964707</v>
       </c>
       <c r="F137">
-        <v>3.737156917583405</v>
+        <v>-2.898164854085618</v>
       </c>
       <c r="G137">
-        <v>0.03424027032875657</v>
+        <v>0.02607347787908949</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -10346,13 +10346,13 @@
         <v>2</v>
       </c>
       <c r="E138">
-        <v>-30.55081188635726</v>
+        <v>-40.16749724105316</v>
       </c>
       <c r="F138">
-        <v>30.72033071003478</v>
+        <v>40.453755259869</v>
       </c>
       <c r="G138">
-        <v>0.169518823677528</v>
+        <v>0.2862580188158381</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -10369,13 +10369,13 @@
         <v>5</v>
       </c>
       <c r="E139">
-        <v>0.4092226405780706</v>
+        <v>-9.240753666555255</v>
       </c>
       <c r="F139">
-        <v>-0.3905518713270054</v>
+        <v>9.312809277183142</v>
       </c>
       <c r="G139">
-        <v>0.01867076925106521</v>
+        <v>0.07205561062788718</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -10392,13 +10392,13 @@
         <v>3</v>
       </c>
       <c r="E140">
-        <v>7.530381305285672</v>
+        <v>6.15833949507298</v>
       </c>
       <c r="F140">
-        <v>-7.505567694590662</v>
+        <v>-6.142083758503306</v>
       </c>
       <c r="G140">
-        <v>0.02481361069500976</v>
+        <v>0.01625573656967305</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -10415,13 +10415,13 @@
         <v>4</v>
       </c>
       <c r="E141">
-        <v>15.94359253816335</v>
+        <v>13.16232640185016</v>
       </c>
       <c r="F141">
-        <v>-15.79367911008965</v>
+        <v>-13.04477339353476</v>
       </c>
       <c r="G141">
-        <v>0.1499134280736919</v>
+        <v>0.1175530083153936</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -10438,13 +10438,13 @@
         <v>5</v>
       </c>
       <c r="E142">
-        <v>10.24058574889698</v>
+        <v>1.193593310503201</v>
       </c>
       <c r="F142">
-        <v>-10.15499505260864</v>
+        <v>-1.154486430538309</v>
       </c>
       <c r="G142">
-        <v>0.08559069628833599</v>
+        <v>0.03910687996489231</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -10461,13 +10461,13 @@
         <v>4</v>
       </c>
       <c r="E143">
-        <v>7.579122033718452</v>
+        <v>6.208407246211687</v>
       </c>
       <c r="F143">
-        <v>-7.530381247649983</v>
+        <v>-6.158339398358155</v>
       </c>
       <c r="G143">
-        <v>0.04874078606846854</v>
+        <v>0.05006784785353199</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -10484,13 +10484,13 @@
         <v>5</v>
       </c>
       <c r="E144">
-        <v>-23.87490007364545</v>
+        <v>-49.34558097061999</v>
       </c>
       <c r="F144">
-        <v>23.96184741060034</v>
+        <v>49.65624427809779</v>
       </c>
       <c r="G144">
-        <v>0.08694733695489287</v>
+        <v>0.3106633074777987</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -10507,13 +10507,13 @@
         <v>11</v>
       </c>
       <c r="E145">
-        <v>21.39096751502592</v>
+        <v>25.14013311082507</v>
       </c>
       <c r="F145">
-        <v>-20.90877962393208</v>
+        <v>-24.48427294470601</v>
       </c>
       <c r="G145">
-        <v>0.4821878910938437</v>
+        <v>0.6558601661190488</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -10530,13 +10530,13 @@
         <v>12</v>
       </c>
       <c r="E146">
-        <v>-1.087260149297599</v>
+        <v>-0.6588920531631506</v>
       </c>
       <c r="F146">
-        <v>1.101920127567924</v>
+        <v>0.6749203556516227</v>
       </c>
       <c r="G146">
-        <v>0.01465997827032484</v>
+        <v>0.01602830248847208</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -10553,13 +10553,13 @@
         <v>13</v>
       </c>
       <c r="E147">
-        <v>-2.954130465209016</v>
+        <v>-1.11854126701044</v>
       </c>
       <c r="F147">
-        <v>3.031950474913995</v>
+        <v>1.202093272289929</v>
       </c>
       <c r="G147">
-        <v>0.0778200097049795</v>
+        <v>0.08355200527948911</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -10576,10 +10576,10 @@
         <v>8</v>
       </c>
       <c r="E148">
-        <v>99.71385570813285</v>
+        <v>127.7230172813927</v>
       </c>
       <c r="F148">
-        <v>-99.71385570813285</v>
+        <v>-127.7230172813927</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10599,10 +10599,10 @@
         <v>9</v>
       </c>
       <c r="E149">
-        <v>-52.71638053365916</v>
+        <v>-63.53265085932455</v>
       </c>
       <c r="F149">
-        <v>52.71638053365916</v>
+        <v>63.53265085932455</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10622,13 +10622,13 @@
         <v>10</v>
       </c>
       <c r="E150">
-        <v>-21.78262700228009</v>
+        <v>-25.67857977298055</v>
       </c>
       <c r="F150">
-        <v>21.91916306847066</v>
+        <v>25.86922474974431</v>
       </c>
       <c r="G150">
-        <v>0.1365360661905735</v>
+        <v>0.1906449767637541</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -10645,13 +10645,13 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>-24.58542349374987</v>
+        <v>-26.95067877549604</v>
       </c>
       <c r="F151">
-        <v>25.31013060719304</v>
+        <v>27.8268145555018</v>
       </c>
       <c r="G151">
-        <v>0.724707113443171</v>
+        <v>0.8761357800057545</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -10668,13 +10668,13 @@
         <v>11</v>
       </c>
       <c r="E152">
-        <v>-21.39096751502592</v>
+        <v>-25.14013311082507</v>
       </c>
       <c r="F152">
-        <v>21.78262700228009</v>
+        <v>25.67857977298055</v>
       </c>
       <c r="G152">
-        <v>0.3916594872541701</v>
+        <v>0.5384466621554895</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -10691,13 +10691,13 @@
         <v>13</v>
       </c>
       <c r="E153">
-        <v>-1.078019908081335</v>
+        <v>-0.6490044804064871</v>
       </c>
       <c r="F153">
-        <v>1.087260149297599</v>
+        <v>0.6588920531631506</v>
       </c>
       <c r="G153">
-        <v>0.00924024121626444</v>
+        <v>0.009887572756663542</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -10714,13 +10714,13 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>9.685423344762858</v>
+        <v>12.05067862650904</v>
       </c>
       <c r="F154">
-        <v>-9.467849761696661</v>
+        <v>-11.73245438757008</v>
       </c>
       <c r="G154">
-        <v>0.2175735830661982</v>
+        <v>0.3182242389389578</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -10737,13 +10737,13 @@
         <v>2</v>
       </c>
       <c r="E155">
-        <v>-5.221047316160119</v>
+        <v>-28.18493238825329</v>
       </c>
       <c r="F155">
-        <v>5.225830644605995</v>
+        <v>28.32620464933974</v>
       </c>
       <c r="G155">
-        <v>0.004783328445875923</v>
+        <v>0.1412722610864503</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -10760,13 +10760,13 @@
         <v>5</v>
       </c>
       <c r="E156">
-        <v>-29.83756899076906</v>
+        <v>-23.98520467520262</v>
       </c>
       <c r="F156">
-        <v>30.31014459173541</v>
+        <v>24.29492509256396</v>
       </c>
       <c r="G156">
-        <v>0.4725756009663462</v>
+        <v>0.3097204173613449</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10783,13 +10783,13 @@
         <v>3</v>
       </c>
       <c r="E157">
-        <v>-15.89231396168221</v>
+        <v>-7.155077042664019</v>
       </c>
       <c r="F157">
-        <v>16.00030463750672</v>
+        <v>7.177310864175788</v>
       </c>
       <c r="G157">
-        <v>0.1079906758245042</v>
+        <v>0.022233821511769</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -10806,13 +10806,13 @@
         <v>4</v>
       </c>
       <c r="E158">
-        <v>-32.50056629109834</v>
+        <v>-14.67025061382347</v>
       </c>
       <c r="F158">
-        <v>33.07773276864301</v>
+        <v>14.79007260807758</v>
       </c>
       <c r="G158">
-        <v>0.5771664775446661</v>
+        <v>0.1198219942541129</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -10829,13 +10829,13 @@
         <v>5</v>
       </c>
       <c r="E159">
-        <v>-36.1624287632843</v>
+        <v>-21.09741864878838</v>
       </c>
       <c r="F159">
-        <v>36.87890595376276</v>
+        <v>21.3500883176992</v>
       </c>
       <c r="G159">
-        <v>0.7164771904784539</v>
+        <v>0.2526696689108127</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -10852,13 +10852,13 @@
         <v>4</v>
       </c>
       <c r="E160">
-        <v>-15.73216547804535</v>
+        <v>-7.119886730920621</v>
       </c>
       <c r="F160">
-        <v>15.89231345359778</v>
+        <v>7.155077000651384</v>
       </c>
       <c r="G160">
-        <v>0.1601479755524354</v>
+        <v>0.03519026973076295</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -10875,13 +10875,13 @@
         <v>5</v>
       </c>
       <c r="E161">
-        <v>-13.8706994947512</v>
+        <v>-26.03522980064993</v>
       </c>
       <c r="F161">
-        <v>13.90824753158915</v>
+        <v>26.13582090729438</v>
       </c>
       <c r="G161">
-        <v>0.03754803683795604</v>
+        <v>0.1005911066444543</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -10898,13 +10898,13 @@
         <v>11</v>
       </c>
       <c r="E162">
-        <v>10.80603814351126</v>
+        <v>16.30065797919091</v>
       </c>
       <c r="F162">
-        <v>-10.67715747626723</v>
+        <v>-16.02738978175009</v>
       </c>
       <c r="G162">
-        <v>0.128880667244026</v>
+        <v>0.2732681974408208</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -10921,13 +10921,13 @@
         <v>12</v>
       </c>
       <c r="E163">
-        <v>-2.288097923093278</v>
+        <v>-1.633393042683548</v>
       </c>
       <c r="F163">
-        <v>2.301451400427334</v>
+        <v>1.645968633472763</v>
       </c>
       <c r="G163">
-        <v>0.01335347733405629</v>
+        <v>0.0125755907892159</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -10944,13 +10944,13 @@
         <v>13</v>
       </c>
       <c r="E164">
-        <v>-8.162678228204626</v>
+        <v>-5.429028852885383</v>
       </c>
       <c r="F164">
-        <v>8.246402018142787</v>
+        <v>5.499273471988288</v>
       </c>
       <c r="G164">
-        <v>0.08372378993816154</v>
+        <v>0.07024461910290422</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -10967,13 +10967,13 @@
         <v>8</v>
       </c>
       <c r="E165">
-        <v>7.42276034133725E-08</v>
+        <v>47.94224476238674</v>
       </c>
       <c r="F165">
-        <v>-7.422760341337231E-08</v>
+        <v>-47.94224476238674</v>
       </c>
       <c r="G165">
-        <v>1.861156378244312E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -10990,10 +10990,10 @@
         <v>9</v>
       </c>
       <c r="E166">
-        <v>-17.3701875246535</v>
+        <v>-34.77523811716413</v>
       </c>
       <c r="F166">
-        <v>17.3701875246535</v>
+        <v>34.77523811716413</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -11013,13 +11013,13 @@
         <v>10</v>
       </c>
       <c r="E167">
-        <v>-10.90427960802616</v>
+        <v>-16.51984515054956</v>
       </c>
       <c r="F167">
-        <v>10.93940906020479</v>
+        <v>16.59819075299925</v>
       </c>
       <c r="G167">
-        <v>0.0351294521786269</v>
+        <v>0.07834560244969757</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -11036,13 +11036,13 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>-17.99643311906982</v>
+        <v>-21.44765408553326</v>
       </c>
       <c r="F168">
-        <v>18.38507520159034</v>
+        <v>21.99837039685017</v>
       </c>
       <c r="G168">
-        <v>0.3886420825205211</v>
+        <v>0.5507163113169095</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -11059,13 +11059,13 @@
         <v>11</v>
       </c>
       <c r="E169">
-        <v>-10.80603814351126</v>
+        <v>-16.30065797919091</v>
       </c>
       <c r="F169">
-        <v>10.90427960802616</v>
+        <v>16.51984515054956</v>
       </c>
       <c r="G169">
-        <v>0.09824146451490184</v>
+        <v>0.2191871713586452</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -11082,13 +11082,13 @@
         <v>13</v>
       </c>
       <c r="E170">
-        <v>-2.275593287069904</v>
+        <v>-1.624499101959494</v>
       </c>
       <c r="F170">
-        <v>2.288097923093278</v>
+        <v>1.633393042683548</v>
       </c>
       <c r="G170">
-        <v>0.01250463602337423</v>
+        <v>0.008893940724053959</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -11105,13 +11105,13 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>3.096432970082814</v>
+        <v>6.547653936546253</v>
       </c>
       <c r="F171">
-        <v>-3.061728619712481</v>
+        <v>-6.446472180142131</v>
       </c>
       <c r="G171">
-        <v>0.03470435037033273</v>
+        <v>0.1011817564041229</v>
       </c>
     </row>
   </sheetData>
@@ -11161,10 +11161,10 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>73.66480370469408</v>
+        <v>62.78392658060148</v>
       </c>
       <c r="F2">
-        <v>-73.66480370469408</v>
+        <v>-62.78392658060148</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -11184,10 +11184,10 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>10.79937247720698</v>
+        <v>7.457159523466765</v>
       </c>
       <c r="F3">
-        <v>-10.79937247720698</v>
+        <v>-7.457159523466765</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -11207,10 +11207,10 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>-15.02129375609802</v>
+        <v>-15.36421610632911</v>
       </c>
       <c r="F4">
-        <v>15.02129375609802</v>
+        <v>15.36421610632911</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -11230,10 +11230,10 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>65.45195482866917</v>
+        <v>62.75347904358242</v>
       </c>
       <c r="F5">
-        <v>-65.45195482866917</v>
+        <v>-62.75347904358242</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -11253,10 +11253,10 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>8.178652455808921</v>
+        <v>7.450634822301698</v>
       </c>
       <c r="F6">
-        <v>-8.178652455808921</v>
+        <v>-7.450634822301698</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-14.77933284281731</v>
+        <v>-15.37915299845908</v>
       </c>
       <c r="F7">
-        <v>14.77933284281731</v>
+        <v>15.37915299845908</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -11299,10 +11299,10 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>63.03997355078759</v>
+        <v>61.33251747919864</v>
       </c>
       <c r="F8">
-        <v>-63.03997355078759</v>
+        <v>-61.33251747919864</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -11322,10 +11322,10 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>6.895398938253236</v>
+        <v>6.437863455886626</v>
       </c>
       <c r="F9">
-        <v>-6.895398938253236</v>
+        <v>-6.437863455886626</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -11345,10 +11345,10 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-20.83723767251166</v>
+        <v>-21.21902037768202</v>
       </c>
       <c r="F10">
-        <v>20.83723767251166</v>
+        <v>21.21902037768202</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>55.19893013541481</v>
+        <v>55.19885790196912</v>
       </c>
       <c r="F11">
-        <v>-55.19893013541481</v>
+        <v>-55.19885790196912</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -11391,10 +11391,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>5.553297369968911</v>
+        <v>5.553278108868555</v>
       </c>
       <c r="F12">
-        <v>-5.553297369968911</v>
+        <v>-5.553278108868555</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-23.35341431359217</v>
+        <v>-23.35343370001463</v>
       </c>
       <c r="F13">
-        <v>23.35341431359217</v>
+        <v>23.35343370001463</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -11437,10 +11437,10 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <v>12.84280213170279</v>
+        <v>5.570677397782456</v>
       </c>
       <c r="F14">
-        <v>-12.84280213170279</v>
+        <v>-5.570677397782456</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -11460,10 +11460,10 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-3.836956432596134</v>
+        <v>-0.01241895488271578</v>
       </c>
       <c r="F15">
-        <v>3.836956432596134</v>
+        <v>0.01241895488271578</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -11483,10 +11483,10 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-29.6457758937719</v>
+        <v>-17.43463477336634</v>
       </c>
       <c r="F16">
-        <v>29.6457758937719</v>
+        <v>17.43463477336634</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -11506,10 +11506,10 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-10.35539776783378</v>
+        <v>20.03998383852425</v>
       </c>
       <c r="F17">
-        <v>10.35539776783378</v>
+        <v>-20.03998383852425</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -11529,10 +11529,10 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>-4.779473873757195</v>
+        <v>14.65237791990678</v>
       </c>
       <c r="F18">
-        <v>4.779473873757195</v>
+        <v>-14.65237791990678</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>6</v>
       </c>
       <c r="E19">
-        <v>-31.15019955298862</v>
+        <v>6.417825073370792</v>
       </c>
       <c r="F19">
-        <v>31.15019955298862</v>
+        <v>-6.417825073370792</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -11575,10 +11575,10 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>-15.11491007073239</v>
+        <v>19.7566133230557</v>
       </c>
       <c r="F20">
-        <v>15.11491007073239</v>
+        <v>-19.7566133230557</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -11598,10 +11598,10 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-5.759091677894206</v>
+        <v>14.48779560829063</v>
       </c>
       <c r="F21">
-        <v>5.759091677894206</v>
+        <v>-14.48779560829063</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -11621,10 +11621,10 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-34.25595876846403</v>
+        <v>6.827812388551326</v>
       </c>
       <c r="F22">
-        <v>34.25595876846403</v>
+        <v>-6.827812388551326</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -11644,10 +11644,10 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-20.54657110674403</v>
+        <v>3.632994994185489</v>
       </c>
       <c r="F23">
-        <v>20.54657110674403</v>
+        <v>-3.632994994185489</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -11667,10 +11667,10 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-8.89478104209805</v>
+        <v>2.640959306828829</v>
       </c>
       <c r="F24">
-        <v>8.89478104209805</v>
+        <v>-2.640959306828829</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -11690,10 +11690,10 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-40.7481314721667</v>
+        <v>-15.3267783613142</v>
       </c>
       <c r="F25">
-        <v>40.7481314721667</v>
+        <v>15.3267783613142</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -11713,10 +11713,10 @@
         <v>7</v>
       </c>
       <c r="E26">
-        <v>41.99747512448668</v>
+        <v>59.19036637208118</v>
       </c>
       <c r="F26">
-        <v>-41.99747512448668</v>
+        <v>-59.19036637208118</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -11736,10 +11736,10 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>5.487086857995457</v>
+        <v>9.836611554078452</v>
       </c>
       <c r="F27">
-        <v>-5.487086857995457</v>
+        <v>-9.836611554078452</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -11759,10 +11759,10 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-33.22509138418598</v>
+        <v>-27.39274102668762</v>
       </c>
       <c r="F28">
-        <v>33.22509138418598</v>
+        <v>27.39274102668762</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -11782,10 +11782,10 @@
         <v>7</v>
       </c>
       <c r="E29">
-        <v>-22.3701875004129</v>
+        <v>8.167006595235602</v>
       </c>
       <c r="F29">
-        <v>22.3701875004129</v>
+        <v>-8.167006595235602</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -11805,10 +11805,10 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-11.95429673714164</v>
+        <v>-3.821323032685307</v>
       </c>
       <c r="F30">
-        <v>11.95429673714164</v>
+        <v>3.821323032685307</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-49.87069694882014</v>
+        <v>-41.11785282465651</v>
       </c>
       <c r="F31">
-        <v>49.87069694882014</v>
+        <v>41.11785282465651</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>5.136457834358195E-07</v>
+        <v>5.247375701421153E-07</v>
       </c>
       <c r="E2">
-        <v>46.04346386022202</v>
+        <v>15.37488859067988</v>
       </c>
       <c r="H2">
         <v>150</v>
@@ -11904,10 +11904,10 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3.215167865284645E-07</v>
+        <v>2.177199117614831E-07</v>
       </c>
       <c r="E3">
-        <v>4.454780898080777E-06</v>
+        <v>0.00148869930005675</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -11924,13 +11924,13 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>5.136460065499312E-07</v>
+        <v>5.247375656337099E-07</v>
       </c>
       <c r="E4">
-        <v>9.736761393236085</v>
+        <v>16.42172578627413</v>
       </c>
       <c r="H4">
-        <v>92.44567053427451</v>
+        <v>130.7813896289665</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -11944,13 +11944,13 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3.405045251461936E-07</v>
+        <v>2.171132816410747E-07</v>
       </c>
       <c r="E5">
-        <v>4.153473644591801E-06</v>
+        <v>0.004155330026580905</v>
       </c>
       <c r="H5">
-        <v>99.99999382893736</v>
+        <v>99.99787341734616</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -11964,13 +11964,13 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>5.136461140981497E-07</v>
+        <v>5.24737614277087E-07</v>
       </c>
       <c r="E6">
-        <v>8.219646697665889</v>
+        <v>13.45444448017138</v>
       </c>
       <c r="H6">
-        <v>80.27471915228162</v>
+        <v>110.2542327634401</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -11984,13 +11984,13 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>3.433208741742365E-07</v>
+        <v>2.203575140660786E-07</v>
       </c>
       <c r="E7">
-        <v>4.112268531190221E-06</v>
+        <v>0.0004071262055115495</v>
       </c>
       <c r="H7">
-        <v>99.9999880997063</v>
+        <v>99.99193736186184</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -12004,13 +12004,13 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>5.466631288363994E-07</v>
+        <v>5.3725294726605E-07</v>
       </c>
       <c r="E8">
-        <v>7.959801474669046E-05</v>
+        <v>0.0001862812451427639</v>
       </c>
       <c r="H8">
-        <v>70.00016113975154</v>
+        <v>93.43617753054221</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -12024,13 +12024,13 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>3.901935112956933E-07</v>
+        <v>2.424206953766904E-07</v>
       </c>
       <c r="E9">
-        <v>3.530886980467259E-06</v>
+        <v>5.7815722392714E-05</v>
       </c>
       <c r="H9">
-        <v>99.99998243102949</v>
+        <v>99.99135588521135</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -12044,13 +12044,13 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>7.842788397379599E-07</v>
+        <v>9.047379182881741E-07</v>
       </c>
       <c r="E10">
-        <v>9.621734549350827E-06</v>
+        <v>6.642690060554774E-06</v>
       </c>
       <c r="H10">
-        <v>70.00006202489729</v>
+        <v>93.43594505506285</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -12064,13 +12064,13 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>6.043617123660219E-07</v>
+        <v>4.8799006340851E-07</v>
       </c>
       <c r="E11">
-        <v>2.157255133310521E-06</v>
+        <v>5.674003259511623E-06</v>
       </c>
       <c r="H11">
-        <v>99.99997762102136</v>
+        <v>99.99127343677463</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12084,13 +12084,13 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>9.575373347201341E-07</v>
+        <v>71.42856883268044</v>
       </c>
       <c r="E12">
-        <v>6.224588276512666E-06</v>
+        <v>2.580227334437674E-07</v>
       </c>
       <c r="H12">
-        <v>70.0000505467243</v>
+        <v>93.43593738501681</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -12104,13 +12104,13 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7.66323312705271E-07</v>
+        <v>5.508160076203271</v>
       </c>
       <c r="E13">
-        <v>1.674627180388096E-06</v>
+        <v>2.16719049843715E-07</v>
       </c>
       <c r="H13">
-        <v>99.99997490184532</v>
+        <v>99.99126562384973</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12124,13 +12124,13 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>70.04139469387113</v>
+        <v>65.83643440074005</v>
       </c>
       <c r="E14">
-        <v>5.550322273611024E-07</v>
+        <v>5.247373144809818E-07</v>
       </c>
       <c r="H14">
-        <v>70.00004343626509</v>
+        <v>143.4359352453647</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12144,13 +12144,13 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>2.565849436241399E-05</v>
+        <v>6.345549839719694E-06</v>
       </c>
       <c r="E15">
-        <v>1.080085066507605E-07</v>
+        <v>4.582664165068018E-07</v>
       </c>
       <c r="H15">
-        <v>99.99997296931477</v>
+        <v>103.296161359973</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12164,13 +12164,13 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>76.95049567139888</v>
+        <v>9.454205908332691E-07</v>
       </c>
       <c r="E16">
-        <v>5.550322231011643E-07</v>
+        <v>6.051045488604843E-06</v>
       </c>
       <c r="H16">
-        <v>119.0290190281846</v>
+        <v>189.521438669961</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -12184,13 +12184,13 @@
         <v>2</v>
       </c>
       <c r="D17">
-        <v>2.717063345581718E-05</v>
+        <v>5.191428881749927E-07</v>
       </c>
       <c r="E17">
-        <v>1.055420409661669E-07</v>
+        <v>5.111846642381014E-06</v>
       </c>
       <c r="H17">
-        <v>99.99998821011353</v>
+        <v>103.2961645126367</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -12204,13 +12204,13 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>5.550323471322211E-07</v>
+        <v>5.247374730516362E-07</v>
       </c>
       <c r="E18">
-        <v>18.31549255431694</v>
+        <v>31.61714570821188</v>
       </c>
       <c r="H18">
-        <v>172.8943653043735</v>
+        <v>189.5214317679486</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -12224,13 +12224,13 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>4.211994429697548E-07</v>
+        <v>2.167194348213173E-07</v>
       </c>
       <c r="E19">
-        <v>3.230107244801888E-06</v>
+        <v>2.30731035606118</v>
       </c>
       <c r="H19">
-        <v>100.0000043617192</v>
+        <v>103.2961575214843</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -12244,10 +12244,10 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>5.060606125296497E-06</v>
+        <v>-1.234264666650371E-07</v>
       </c>
       <c r="E20">
-        <v>55.53598042741813</v>
+        <v>64.00000048760286</v>
       </c>
       <c r="H20">
         <v>150</v>
@@ -12264,10 +12264,10 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>5.060606139109879E-06</v>
+        <v>-1.307328216933409E-07</v>
       </c>
       <c r="E21">
-        <v>102.4359012518282</v>
+        <v>35.0000004925889</v>
       </c>
       <c r="H21">
         <v>100</v>
